--- a/excel_data/Website_mapping.xlsx
+++ b/excel_data/Website_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pixeltruth-my.sharepoint.com/personal/shubhankar_shukla_pixeltruth_com/Documents/Python_Codes/IS_Dashboard/excel_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pixeltruth-my.sharepoint.com/personal/shubhankar_shukla_pixeltruth_com/Documents/Python_Codes/Testing_Code/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{AB1C9699-5AD3-4A07-AFFC-BDB08EC9955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFEE7DAB-577D-45AB-BA91-6CBF63377D91}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{AB1C9699-5AD3-4A07-AFFC-BDB08EC9955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F7FDD99-54D6-469F-83E1-487DA1A1E7E7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44ED9281-8F1E-4DBD-9F57-CE2FABFA19EC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="617">
   <si>
     <t>website_url</t>
   </si>
@@ -72,9 +72,6 @@
     <t>https://ycstl.com</t>
   </si>
   <si>
-    <t>https://electronic-44.com</t>
-  </si>
-  <si>
     <t>https://et7india.com</t>
   </si>
   <si>
@@ -111,9 +108,6 @@
     <t>https://h5.lgzclub.com</t>
   </si>
   <si>
-    <t>https://future39.technology</t>
-  </si>
-  <si>
     <t>https://future-technologys.com</t>
   </si>
   <si>
@@ -132,12 +126,6 @@
     <t>https://www.holwin123.top</t>
   </si>
   <si>
-    <t>https://faak2011.xyz</t>
-  </si>
-  <si>
-    <t>https://fdakw2002.xyz</t>
-  </si>
-  <si>
     <t>https://letgou.vi</t>
   </si>
   <si>
@@ -177,45 +165,9 @@
     <t>https://xssokk.vip</t>
   </si>
   <si>
-    <t>https://flipdealsoff.shinchan.us.cc</t>
-  </si>
-  <si>
-    <t>https://deal.bestoffers-shop.cloud</t>
-  </si>
-  <si>
-    <t>https://flipkart-bbd-sale.wuaze.com</t>
-  </si>
-  <si>
-    <t>https://kitchenoffermel.store</t>
-  </si>
-  <si>
-    <t>https://kitchenone.xyz</t>
-  </si>
-  <si>
-    <t>https://wh1483107.ispot.cc</t>
-  </si>
-  <si>
-    <t>https://super.great-india-sale-day.shop</t>
-  </si>
-  <si>
-    <t>http://kitchenone.xyz</t>
-  </si>
-  <si>
-    <t>https://deals-flipakrt.netlify.ap</t>
-  </si>
-  <si>
     <t>https://balama.vip</t>
   </si>
   <si>
-    <t>https://fdegobal.net</t>
-  </si>
-  <si>
-    <t>https://tronhash.io</t>
-  </si>
-  <si>
-    <t>https://bnbhash.io</t>
-  </si>
-  <si>
     <t>https://timebucks.com</t>
   </si>
   <si>
@@ -231,12 +183,6 @@
     <t>https://24hwork.online</t>
   </si>
   <si>
-    <t>https://offer.sale-india.com</t>
-  </si>
-  <si>
-    <t>https://sjnkmss.myshopify.com</t>
-  </si>
-  <si>
     <t>https://ai24money.com</t>
   </si>
   <si>
@@ -249,162 +195,15 @@
     <t>https://bilera.vi</t>
   </si>
   <si>
-    <t>https://kurtii.newwyew.sho</t>
-  </si>
-  <si>
-    <t>https://new.india-sale.com</t>
-  </si>
-  <si>
-    <t>https://deals.discountsindia.xyz</t>
-  </si>
-  <si>
-    <t>https://offer.win-dhamaka.com</t>
-  </si>
-  <si>
-    <t>https://fkplus.gaming-offers.sho</t>
-  </si>
-  <si>
-    <t>https://flip-shop.gaming-offers.sho</t>
-  </si>
-  <si>
-    <t>https://www.instantwealth9.com</t>
-  </si>
-  <si>
-    <t>https://www.renownedbrands6.com</t>
-  </si>
-  <si>
-    <t>https://cozywearhub.netlify.ap</t>
-  </si>
-  <si>
-    <t>https://palevioletred-moose-958534.hostingersite.co</t>
-  </si>
-  <si>
-    <t>https://bigwinoffer.com.t</t>
-  </si>
-  <si>
-    <t>https://roaring-eclair-4ac4f0.netlify.ap</t>
-  </si>
-  <si>
-    <t>https://big-billion.flipkartx.com</t>
-  </si>
-  <si>
-    <t>https://diziebook.sho</t>
-  </si>
-  <si>
-    <t>https://apexatromining.online</t>
-  </si>
-  <si>
-    <t>https://dhamakaoffers.live</t>
-  </si>
-  <si>
-    <t>https://boltbank.live</t>
-  </si>
-  <si>
-    <t>https://en.ibminvst.com</t>
-  </si>
-  <si>
-    <t>https://big-billion-offer.shop</t>
-  </si>
-  <si>
-    <t>https://salez-india.in</t>
-  </si>
-  <si>
-    <t>https://crazydealsfk.site</t>
-  </si>
-  <si>
-    <t>https://deals.flipkart-salez.shop</t>
-  </si>
-  <si>
-    <t>https://flipkaart-offeers.netlify.ap</t>
-  </si>
-  <si>
-    <t>https://flpkrt-christmassale.shop</t>
-  </si>
-  <si>
-    <t>https://flippp-dealmart33.shop</t>
-  </si>
-  <si>
-    <t>https://flippp-surekart22.shop</t>
-  </si>
-  <si>
-    <t>https://endyearss.i</t>
-  </si>
-  <si>
-    <t>https://big.offer-indian.shop</t>
-  </si>
-  <si>
-    <t>http://winter.live-sale.xyz</t>
-  </si>
-  <si>
-    <t>https://christmass2025-sale.shop</t>
-  </si>
-  <si>
-    <t>https://india-offer-bazar.co</t>
-  </si>
-  <si>
-    <t>https://fillp-savings.shop</t>
-  </si>
-  <si>
-    <t>https://yearend-winter.shop</t>
-  </si>
-  <si>
-    <t>https://filppkortchristmaassdealz.shop</t>
-  </si>
-  <si>
-    <t>https://flip-flopdeals.shop</t>
-  </si>
-  <si>
-    <t>https://happy-25cristmassale.shop</t>
-  </si>
-  <si>
-    <t>https://x3f.35e.mytemp.website</t>
-  </si>
-  <si>
-    <t>https://energy09-longterm.com</t>
-  </si>
-  <si>
-    <t>https://www.powerfulprogram.ru</t>
-  </si>
-  <si>
-    <t>https://new.mainsale-market.com</t>
-  </si>
-  <si>
-    <t>https://dhamaka-deal.shop</t>
-  </si>
-  <si>
-    <t>https://new.offer-start.com</t>
-  </si>
-  <si>
-    <t>https://flipp-flopdealls.shop</t>
-  </si>
-  <si>
-    <t>https://money-todays.com</t>
-  </si>
-  <si>
     <t>https://hind-ware55.com</t>
   </si>
   <si>
-    <t>https://free-rwds.com</t>
-  </si>
-  <si>
-    <t>https://indian.igshx.xyz</t>
-  </si>
-  <si>
-    <t>https://flipkert.main-sales.com</t>
-  </si>
-  <si>
-    <t>https://jinpengyindu.alliedgd.cc</t>
-  </si>
-  <si>
     <t>https://www.jotform.com</t>
   </si>
   <si>
     <t>Germany</t>
   </si>
   <si>
-    <t>Ukraine</t>
-  </si>
-  <si>
     <t>Canada</t>
   </si>
   <si>
@@ -441,57 +240,6 @@
     <t>Loan Scam</t>
   </si>
   <si>
-    <t>https://www.lajiao-olg777.org</t>
-  </si>
-  <si>
-    <t>https://beandrivin.store</t>
-  </si>
-  <si>
-    <t>https://lacousxxyyuw2026.com</t>
-  </si>
-  <si>
-    <t>https://www.tata-namak58gc.com</t>
-  </si>
-  <si>
-    <t>https://vaultcines.com</t>
-  </si>
-  <si>
-    <t>https://www.powerprogram.ru</t>
-  </si>
-  <si>
-    <t>https://jhakkasoffer.xyz</t>
-  </si>
-  <si>
-    <t>https://lightsteelblue-chamois-269280.hostingersite.co</t>
-  </si>
-  <si>
-    <t>https://modhiya.sho</t>
-  </si>
-  <si>
-    <t>https://offer.megadeall.sho</t>
-  </si>
-  <si>
-    <t>https://offers.mainsale-market.com</t>
-  </si>
-  <si>
-    <t>https://lightgrey-termite-338705.hostingersite.co</t>
-  </si>
-  <si>
-    <t>https://231ss.outstend.sho</t>
-  </si>
-  <si>
-    <t>https://winter.megadeall.sho</t>
-  </si>
-  <si>
-    <t>https://shop.megadeall.sho</t>
-  </si>
-  <si>
-    <t>https://www.hara7ksm-ft11ye.cc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland </t>
-  </si>
-  <si>
     <t>Betting/Gambling</t>
   </si>
   <si>
@@ -504,14 +252,1649 @@
     <t>https://bdginfo.com</t>
   </si>
   <si>
-    <t>https://bdgclub.cc</t>
+    <t>https://www.bdgclub.cc</t>
+  </si>
+  <si>
+    <t>https://happy193.ru</t>
+  </si>
+  <si>
+    <t>https://www.qualityenergy4.com</t>
+  </si>
+  <si>
+    <t>https://droonnqlewaato.com</t>
+  </si>
+  <si>
+    <t>https://www.goodpower1.com</t>
+  </si>
+  <si>
+    <t>https://motonas09.com</t>
+  </si>
+  <si>
+    <t>https://www.avant-gardedesign7.com</t>
+  </si>
+  <si>
+    <t>https://yd22349.ru</t>
+  </si>
+  <si>
+    <t>https://yd22358.ru</t>
+  </si>
+  <si>
+    <t>https://www.meticulousdetails9.com</t>
+  </si>
+  <si>
+    <t>http://www.high-end4.ru</t>
+  </si>
+  <si>
+    <t>https://www.excellentpower9.cc</t>
+  </si>
+  <si>
+    <t>https://idealplatform.ru</t>
+  </si>
+  <si>
+    <t>https://dasmneakkddh2026.live</t>
+  </si>
+  <si>
+    <t>https://bsd6.com</t>
+  </si>
+  <si>
+    <t>https://yd22346.ru</t>
+  </si>
+  <si>
+    <t>https://vivo88669.ru</t>
+  </si>
+  <si>
+    <t>https://www.yellowdiamond-077.com</t>
+  </si>
+  <si>
+    <t>https://www.tangiblebenefits33.com</t>
+  </si>
+  <si>
+    <t>https://www.tatacreates66.com</t>
+  </si>
+  <si>
+    <t>https://www.provenexpertise22.com</t>
+  </si>
+  <si>
+    <t>https://www.globalbrands44.ru</t>
+  </si>
+  <si>
+    <t>https://www.optimalenergy.ru</t>
+  </si>
+  <si>
+    <t>https://www.tatabenefits33.com</t>
+  </si>
+  <si>
+    <t>https://www.optimalprograms11.com</t>
+  </si>
+  <si>
+    <t>https://vivo88668.ru</t>
+  </si>
+  <si>
+    <t>https://vivo999915.ru</t>
+  </si>
+  <si>
+    <t>https://livestockfarmingy.com</t>
+  </si>
+  <si>
+    <t>https://staarbuck-invest.in</t>
+  </si>
+  <si>
+    <t>https://fundingora.sbs</t>
+  </si>
+  <si>
+    <t>https://www.benz886688.ru</t>
+  </si>
+  <si>
+    <t>https://www.vivo888815.ru</t>
+  </si>
+  <si>
+    <t>https://www.yd667788.ru</t>
+  </si>
+  <si>
+    <t>https://shabiyindu666.ru</t>
+  </si>
+  <si>
+    <t>https://benz776688.ru</t>
+  </si>
+  <si>
+    <t>https://schneider-23electric.com</t>
+  </si>
+  <si>
+    <t>https://asean-peints333.com</t>
+  </si>
+  <si>
+    <t>https://benz667788.ru</t>
+  </si>
+  <si>
+    <t>https://yd776688.ru</t>
+  </si>
+  <si>
+    <t>https://www.roy-mmk999.org</t>
+  </si>
+  <si>
+    <t>https://www.freshlydelivered6.cc</t>
+  </si>
+  <si>
+    <t>https://www.discountedprices1.com</t>
+  </si>
+  <si>
+    <t>https://www.everythinghave5.com</t>
+  </si>
+  <si>
+    <t>https://www.kmhzushvvvdbjuuwiiaikis.com</t>
+  </si>
+  <si>
+    <t>https://ttxbrooabcom90.com</t>
+  </si>
+  <si>
+    <t>https://www.professionalthoughtful.ru</t>
+  </si>
+  <si>
+    <t>https://wheelxzuauesgwo2027.live</t>
+  </si>
+  <si>
+    <t>https://ev-electric88.com</t>
+  </si>
+  <si>
+    <t>https://www.freshquality3.com</t>
+  </si>
+  <si>
+    <t>https://www.wideselection2.com</t>
+  </si>
+  <si>
+    <t>https://www.attentiveservice.ru</t>
+  </si>
+  <si>
+    <t>https://www.efficientcheckout.ru</t>
+  </si>
+  <si>
+    <t>https://drone-x66.com</t>
+  </si>
+  <si>
+    <t>https://heriiiwwvoonvusw.com</t>
+  </si>
+  <si>
+    <t>https://ntpc-45light.com</t>
+  </si>
+  <si>
+    <t>https://www.b-ajajelectronics88.com</t>
+  </si>
+  <si>
+    <t>https://www.ai-artificial44.com</t>
+  </si>
+  <si>
+    <t>https://neztleiz-store22.com</t>
+  </si>
+  <si>
+    <t>https://britanixmart.com</t>
+  </si>
+  <si>
+    <t>https://begat-coms444.com</t>
+  </si>
+  <si>
+    <t>https://heriiwvoonvusw2029.com</t>
+  </si>
+  <si>
+    <t>https://windpower33.com</t>
+  </si>
+  <si>
+    <t>https://foszzzxtyy2026p40fito.ru</t>
+  </si>
+  <si>
+    <t>https://user.amul8.co</t>
+  </si>
+  <si>
+    <t>https://www.corrdeelia.com</t>
+  </si>
+  <si>
+    <t>https://greats-white.com</t>
+  </si>
+  <si>
+    <t>https://ardentmillons.com</t>
+  </si>
+  <si>
+    <t>https://www.biscoff-invest.com</t>
+  </si>
+  <si>
+    <t>https://h5.lypexchg.me</t>
+  </si>
+  <si>
+    <t>https://smartfarming77.com</t>
+  </si>
+  <si>
+    <t>https://scoaweggzxca.com</t>
+  </si>
+  <si>
+    <t>https://www.2026bisleri2026hou.com</t>
+  </si>
+  <si>
+    <t>https://www.tnelnsco.com</t>
+  </si>
+  <si>
+    <t>https://www.vansjxxhhjwkkajhs.com</t>
+  </si>
+  <si>
+    <t>https://goindigoofire2026dsgdfly.com</t>
+  </si>
+  <si>
+    <t>https://www.dha-zero-000.org</t>
+  </si>
+  <si>
+    <t>https://www.agrimachineryrenta.com</t>
+  </si>
+  <si>
+    <t>https://ingalaxyone.tech</t>
+  </si>
+  <si>
+    <t>https://newsnacks88.long-msworldnetwork.com</t>
+  </si>
+  <si>
+    <t>https://zara-zar.netlify.app</t>
+  </si>
+  <si>
+    <t>https://www.owslapumpingw-22.com</t>
+  </si>
+  <si>
+    <t>https://adani-35solar.com</t>
+  </si>
+  <si>
+    <t>https://www.pepsibeverage.com</t>
+  </si>
+  <si>
+    <t>https://www.ankurfund.com</t>
+  </si>
+  <si>
+    <t>https://www.fajktlauin-1ww.com</t>
+  </si>
+  <si>
+    <t>https://www.monsterv221p88vn.com</t>
+  </si>
+  <si>
+    <t>https://bhuytsh.long-term-application.com</t>
+  </si>
+  <si>
+    <t>https://binaryx.shop</t>
+  </si>
+  <si>
+    <t>https://www.bitmaine.live</t>
+  </si>
+  <si>
+    <t>https://intelligent823.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands </t>
+  </si>
+  <si>
+    <t>United States of America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">India </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany </t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>https://cozywearhub.netlify.app</t>
+  </si>
+  <si>
+    <t>https://bigwinoffer.com.tr</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/hmhf4/OFFER/modi-upi</t>
+  </si>
+  <si>
+    <t>https://salez-india.in/xvca/OFFER</t>
+  </si>
+  <si>
+    <t>https://flipkaart-offeers.netlify.app</t>
+  </si>
+  <si>
+    <t>https://super-festival-sale.com/scratch</t>
+  </si>
+  <si>
+    <t>https://dhamaka-deal.shop/aqj/sale/?i=1</t>
+  </si>
+  <si>
+    <t>https://sale.fkkart-yearending-offers.live/Error/OFFER</t>
+  </si>
+  <si>
+    <t>https://winter.dhamaka-deal.shop/aqj/sale/?i=1</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/VSKgwBR2Rz</t>
+  </si>
+  <si>
+    <t>https://techiedealxx.com/FK</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/6XijtYINoH</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/WsFuG33jS2</t>
+  </si>
+  <si>
+    <t>https://deals.flipkart-salez.shop/3738383838/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/uwjReiPKB2</t>
+  </si>
+  <si>
+    <t>https://flipcartsales.shop/ALL99</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/Kkjfnc/OFFER/flipkart-sale</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/ed5914f3</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/hnfvbr/OFFER/fk99-allupiDrone</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/5VLiTdFLzp</t>
+  </si>
+  <si>
+    <t>https://winterhub-stocks.com/winter</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/Upwsltj51y</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/4f8751b9</t>
+  </si>
+  <si>
+    <t>https://indisupport.online/S1</t>
+  </si>
+  <si>
+    <t>https://livebigdeals.shop/shop</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/9c94a48e76/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/mQYrrEtuSY</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Ncnjdj/OFFER/59cod-allupi</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/hncverv/OFFER/meesho-dress</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/hmecd/OFFER/modi-upi</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/295ac5cb</t>
+  </si>
+  <si>
+    <t>https://scrth-me-now.free.nf/?i=1</t>
+  </si>
+  <si>
+    <t>https://secret.india-sale.com/sellive</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/hnf4/OFFER/shoes-cashfree</t>
+  </si>
+  <si>
+    <t>https://flipcartsales.shop/PATHAN149</t>
+  </si>
+  <si>
+    <t>https://today-bestoffers-only.com/endsale</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/site-696c82a69507d</t>
+  </si>
+  <si>
+    <t>https://pm.bharatscratch.shop/b428d2a1</t>
+  </si>
+  <si>
+    <t>https://arbajft.in/pay.php</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/c7eb8845</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Sana25Jan/OFFER/99rs-allupi</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Onini13Feb/OFFER/kitchen</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/53d80332d2/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://dhamaka-deal.shop/aqj/sale</t>
+  </si>
+  <si>
+    <t>https://winter.dhamaka-deal.shop/aqj/sale</t>
+  </si>
+  <si>
+    <t>https://pm.bharatscratch.shop/Events</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/bcd7e69880/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://meeshosalemeesho.store</t>
+  </si>
+  <si>
+    <t>http://free-rwds.com/bcd7e69880/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/788ce5aeca/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://offer.sale-india.com/3223/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://me-esho.netlify.app</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/c4eb426f</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Mwplev/OFFER/99rs-allupi</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/b5346b02da/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/bfec361a63/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/g3sw2/OFFER/fk99-cash</t>
+  </si>
+  <si>
+    <t>https://offersdhamaka.xyz</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/9be0bef9</t>
+  </si>
+  <si>
+    <t>https://flipcartsales.shop/JBL</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/1b33549a</t>
+  </si>
+  <si>
+    <t>https://salez-india.in/90invz/OFFER/KITCHEN/index.html</t>
+  </si>
+  <si>
+    <t>https://sale.fkkart-yearending-offers.live/Rohan/OFFER/vivophone-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/WsFuG33jS2</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/bc92d043</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/hncd3/OFFER/59cod-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/2382fc34</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/2VthjZ3O8A</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/a771ca60</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Jxbvdv/OFFER/shoes-shop-allupi</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/bgtgf433/OFFER/fk99-allupi</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/fgbe3/OFFER/fk99-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/f43f86ca</t>
+  </si>
+  <si>
+    <t>https://meeshoo-bb.com/index</t>
+  </si>
+  <si>
+    <t>https://big.offer-indian.shop/usbs/OFFER</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/b85b0356</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/site-69836725b1709</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/fc30f6f3</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/c7eb8845</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/bf3fb234</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/Upwsltj51y</t>
+  </si>
+  <si>
+    <t>https://big.offer-indian.shop/ws3l/OFFER</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/hnr3/OFFER/fk99-cash</t>
+  </si>
+  <si>
+    <t>https://floralwhite-sandpiper-503211.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/14f10b81</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Gjfd/OFFER/earphone</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/ed5914f3</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/user_7593067a/fk99-bigbn</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Osoh/OFFER/KITCHEN-allupi</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/sajnw2/fk99-bigbn</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/d10ad634</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/k5R8Sx7Q1c</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/hnf433w/OFFER/buds-new</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Ozgv/OFFER/99-199</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/6XijtYINoH</t>
+  </si>
+  <si>
+    <t>https://new.main-sales.com/users/koml/earbudsnewdiwaliv2n</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/Pahfbb/OFFER/fk149-cash</t>
+  </si>
+  <si>
+    <t>https://flipcartsales.shop/PT149</t>
+  </si>
+  <si>
+    <t>https://meeshocom.sales-india.com/master</t>
+  </si>
+  <si>
+    <t>https://meeshocom.sales-india.com</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/75d0ee5d/fk99n</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/newoffer</t>
+  </si>
+  <si>
+    <t>https://flipcartsales.shop/MS149</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/jhmnfvfd/OFFER/leptop-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/2b34a1d7</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/cc0dd585</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/0646890a</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/14e1776a</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/c6b03bdf</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/5aa4f9b9/earbudsnewdiwaliv2n</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/a5a88db6</t>
+  </si>
+  <si>
+    <t>https://flpkart-offar.shop/new/18+</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/bnyde/OFFER/iphone16</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/user_58a7c447/fk99n</t>
+  </si>
+  <si>
+    <t>https://flpkart-offar.shop/prot</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/875646</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/d0fca48e</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/RohanOp/OFFER/buds-fk</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/user_d3d4579a/fk99n</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/fa5b1ee9</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/site-6986f936ce03f</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/bf6f8348</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Bhgvr/OFFER/iphone14r</t>
+  </si>
+  <si>
+    <t>https://new.india-sale.com/522f551b</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Psjsg/OFFER/fknew-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/site-697ebd9632b9e</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/4f8751b9</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/syco3/earbudsnewdiwaliv2n</t>
+  </si>
+  <si>
+    <t>https://peru-rhinoceros-710713.hostingersite.com/VU1D/OFFER/earphone</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Shenoy/OFFER/oneplus11r</t>
+  </si>
+  <si>
+    <t>https://offerxevent.shop/FK/buds/OFFER/fk99-allupi</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/user_0ace74f4/flipkart-wintern</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/daae5426</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/c2b1f825</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/user_da15074b/icncscn</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/93a65a17/shoesn</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/ufy0dqWVYI</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/user_a077a27e/icncscn</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Dracula/OFFER/fkvivov50</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/f7ed2efe</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/5778013d</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/df90182d/diwaliflipmixcf</t>
+  </si>
+  <si>
+    <t>https://flipcartsales.shop/MASTER2</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/Ksksg/OFFER/iphone16</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Lxjdb/OFFER/iphone16</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/295ac5cb</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/b1d29db5</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/cfdc7352</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/fa02b40e</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/mQYrrEtuSY</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/1c241825</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/fgbr31/OFFER/new</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/3b97f310</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/site-6982c673a2167</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/8eb46bfa</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/hmnfe3/OFFER/iphone14r</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/7176bcc7</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/9cd7f37f</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/6f91a8bf</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/cyYvZbyK/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/6df78438d5/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://flipcartsales.shop/Velentinespecial</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Kxnxbhc/OFFER/KITCHEN-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/1f14bd4b</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/Highlight</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/2c67d1c6</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/9431f55f58/OFFER/KITCHEN</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/1b467db1cf/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/5a574b09c3/OFFER/fkbuds</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/b10f1d5528/OFFER/fkbuds</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/c1e0d14bb1/OFFER/KITCHEN</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/ed306becc8/OFFER/18%2b</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/sukkJ5pxQ/OFFER/fkbuds</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/15e481b8</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/0d58240c</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/Holisale</t>
+  </si>
+  <si>
+    <t>https://lightyellow-alpaca-281866.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/eb0c358a8a/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/107286c4fe/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/dd6d0b7d7c/OFFER/watchog</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/fdf237b431/OFFER/watchog</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/98b8e5b4f3/OFFER/fkbuds</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/nyh5t/OFFER/shoes</t>
+  </si>
+  <si>
+    <t>https://flipcartsales.shop/ALL149</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/51dd07b44a/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/site-6990757ec9758</t>
+  </si>
+  <si>
+    <t>https://kichenoffers.shop</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/9028cbc8</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Ankit12Feb/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/ed306becc8/OFFER/18+</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/51dd07b44a/OFFER/speaker</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/sukkJ5pxQ/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/Pahfbb/OFFER/fk99-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/VSKgwBR2Rz</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/site-699586a2b92f0</t>
+  </si>
+  <si>
+    <t>http://new.deals-indian.com/1b33549a</t>
+  </si>
+  <si>
+    <t>https://feekart.shop/mysale</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/8642d87fa3/OFFER/speaker</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/gw0WgWJ6cH/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://flooxplip.shop/newshop</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/8d34e031</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/PPgg/OFFER/meesho-dress</t>
+  </si>
+  <si>
+    <t>https://dhamaka-offer.live/Nawab/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/hnht/OFFER/fk99-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/ec4c0e6c</t>
+  </si>
+  <si>
+    <t>https://yellow-emu-733093.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://meeshocom.sales-india.com/s</t>
+  </si>
+  <si>
+    <t>https://dhamaka-offer.live/XnLr01/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/fghg/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/dc4e10a9</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/Mccn/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/674592d5</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/4089bb03</t>
+  </si>
+  <si>
+    <t>https://sale-big-billion.shop/Kingop/OFFER/fk149-upi</t>
+  </si>
+  <si>
+    <t>https://sale-big-billion.shop/Rowdy/OFFER/fk149-upi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/Shoping</t>
+  </si>
+  <si>
+    <t>https://new.greatindiasale.live/users/harry/OFFER</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/user_7593067a/fksoundboxn</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Abhishek/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/1f3c4a27</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/cec00436</t>
+  </si>
+  <si>
+    <t>https://trolleys-flip.shop/newshop</t>
+  </si>
+  <si>
+    <t>https://new.hidden-discount.shop/dSTi/OFFER/fk-speaker</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/hncverv/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/9389eabd</t>
+  </si>
+  <si>
+    <t>https://new.hidden-discount.shop/wn7l/OFFER/kitchen</t>
+  </si>
+  <si>
+    <t>https://dmh.81b.mytemp.website/Pahfbb/OFFER/fk149-cash/fk149-cash</t>
+  </si>
+  <si>
+    <t>https://flipcart-limited-offer.myshopify.com</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/Osisg/OFFER/shoes</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/6df78438d5/OFFER/speaker</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/hger3/OFFER/meesho-dress</t>
+  </si>
+  <si>
+    <t>https://palegreen-pheasant-256949.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/5e315a93/kitchencf</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/gnce/OFFER/59cod-allupi</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/cgy/OFFER/meesho-dress</t>
+  </si>
+  <si>
+    <t>https://dailysoapupdate.com/mysale01/#/home</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/5067fd7c</t>
+  </si>
+  <si>
+    <t>https://new.main-sales.com/users/varish/fk149n</t>
+  </si>
+  <si>
+    <t>https://mast-deal.shop/Keshav</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/hnht/OFFER/fk149-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/site-699aeaba3f36b</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/628d14dd51/OFFER/JIO-MART</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/cbd4d5b4</t>
+  </si>
+  <si>
+    <t>https://snow-butterfly-347935.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://deals.indiasale.live/9ea05461</t>
+  </si>
+  <si>
+    <t>https://huntbar.site</t>
+  </si>
+  <si>
+    <t>https://big-discount-flipkar.com/OFFER/fk149-allupi</t>
+  </si>
+  <si>
+    <t>https://summersaleoffer.online</t>
+  </si>
+  <si>
+    <t>https://green-mantis-164394.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://biggest-trolleys.shop/newshop</t>
+  </si>
+  <si>
+    <t>https://new.hidden-discount.shop/HmiW/OFFER/kitchen</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/01e84b24</t>
+  </si>
+  <si>
+    <t>https://filpkarts.shop/mysale</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/hgt4/OFFER/fk99-allupi</t>
+  </si>
+  <si>
+    <t>https://meesho.onlinelehenga.com</t>
+  </si>
+  <si>
+    <t>https://saddlebrown-koala-214922.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/ac940285</t>
+  </si>
+  <si>
+    <t>https://big-discount-flipkar.com/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/ceo/meeshon</t>
+  </si>
+  <si>
+    <t>https://filpkeert.shop/mysale</t>
+  </si>
+  <si>
+    <t>https://lawngreen-kingfisher-980100.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/bc301819</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/df28058029/OFFER/fk-laptop</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/ebf98942ca/OFFER/99cod</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/51dd07b44a/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/788ce5aeca/OFFER/99-299pods</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/4512c362de/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/8ffe72ad8b/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/aca682fbc0/OFFER/99-299pods</t>
+  </si>
+  <si>
+    <t>https://mediumturquoise-peafowl-207676.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://lightgrey-quail-699092.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/f6e6bd47</t>
+  </si>
+  <si>
+    <t>https://khaki-stinkbug-900591.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://beige-scorpion-308566.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://measho003.vercel.app</t>
+  </si>
+  <si>
+    <t>https://royalblue-hare-879414.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://lightpink-cheetah-375413.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/ceo/meeshon</t>
+  </si>
+  <si>
+    <t>https://sale.fkkart-yearending-offers.live/Dom/OFFER/fk-kitchen-allupi</t>
+  </si>
+  <si>
+    <t>https://pm.bharatscratch.shop/HARISH</t>
+  </si>
+  <si>
+    <t>https://bigbangdeal.xyz/scratch</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/974f689c</t>
+  </si>
+  <si>
+    <t>https://scrth-me-now.free.nf/?i=2</t>
+  </si>
+  <si>
+    <t>http://offer.win-dhamaka.com/hmhf4/OFFER/modi-upi</t>
+  </si>
+  <si>
+    <t>https://lightslategray-echidna-984933.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/84558624</t>
+  </si>
+  <si>
+    <t>https://azure-coyote-363780.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/gbde3/OFFER/meesho-dress</t>
+  </si>
+  <si>
+    <t>https://mediumseagreen-walrus-145734.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://lightgoldenrodyellow-gaur-105068.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://olivedrab-pigeon-311026.hostingersite.com/?fbclid=IwY2xjawQR-phleHRuA2FlbQIxMABicmlkETFOWm9…</t>
+  </si>
+  <si>
+    <t>https://olivedrab-pigeon-311026.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://deals.indiasale.live/site-69a07efdaf69d</t>
+  </si>
+  <si>
+    <t>https://cyan-goldfish-531571.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/5a000e7a/meeshon</t>
+  </si>
+  <si>
+    <t>https://fillpkertts.shop/mysale</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/b7f63619</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/3e6b9e99bd/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/7874bfbdeb/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/5a574b09c3/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/53d80332d2/OFFER/fknew</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/406dc6557c/OFFER/KITCHEN</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/0a40e0a6c0/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/f66f11870d/OFFER/KITCHEN</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/996d707cd5/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/8cfbf96b13/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://free-rwds.com/dd73b0c710/OFFER/fk-buds99</t>
+  </si>
+  <si>
+    <t>https://bigbillion-day.shop/ss2/OFFER/fk149-upi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/a0db38c9</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/jh43/OFFER/fk149-allupi</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/user_a4496355/newfk99n</t>
+  </si>
+  <si>
+    <t>https://mediumorchid-chinchilla-133554.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/site-697738e6ddef4</t>
+  </si>
+  <si>
+    <t>https://dodgerblue-shark-135348.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://lightseagreen-kangaroo-320697.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://big.offer-indian.shop/vsge/OFFER</t>
+  </si>
+  <si>
+    <t>https://new.main-sales.com/users/varish/fkcustomsc</t>
+  </si>
+  <si>
+    <t>https://darkseagreen-ibex-492354.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://chocolate-starling-667762.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/9678395a</t>
+  </si>
+  <si>
+    <t>https://gray-reindeer-806195.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/919112b3</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/af6a2b2a</t>
+  </si>
+  <si>
+    <t>https://meem.blog</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/hnfvbr/OFFER/speaker-allupi</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/4e252be0</t>
+  </si>
+  <si>
+    <t>https://new.hidden-discount.shop/u1gl/OFFER/fk-speaker</t>
+  </si>
+  <si>
+    <t>https://darkorchid-crane-904709.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/dd3/OFFER/59cod-allupi</t>
+  </si>
+  <si>
+    <t>https://biggest-dhamaka-sale.xyz/7bf9ofca39</t>
+  </si>
+  <si>
+    <t>https://offer.win-dhamaka.com/fg22e/OFFER/meesho-dress</t>
+  </si>
+  <si>
+    <t>https://sienna-hyena-831771.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://filpkat-bajajcoolers.shop/newshop</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/ceo/holinewn</t>
+  </si>
+  <si>
+    <t>https://sale.festiveeseason.shop/Fjbfjifnmkfz/OFFER</t>
+  </si>
+  <si>
+    <t>https://dmh.81b.mytemp.website/kitchen/kichen.html</t>
+  </si>
+  <si>
+    <t>https://slategray-mandrill-919025.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://meeshom.sales-india.com</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/ghtgr3/OFFER/meesho-dress</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/7575d45c</t>
+  </si>
+  <si>
+    <t>https://gold-mink-565478.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://yellowgreen-quail-835557.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://fipkart-ekarts.shop/newshop</t>
+  </si>
+  <si>
+    <t>https://flipskart-offersale.shop/marchdeals</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/fe33x/OFFER/fk99-allupi</t>
+  </si>
+  <si>
+    <t>https://holi-flpkarts.shop/bigshop</t>
+  </si>
+  <si>
+    <t>https://betary.online</t>
+  </si>
+  <si>
+    <t>https://summersalefk.com/36e898b831/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://summersalefk.com/a83ed7cd5e/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://new.sale-lives.com/users/varish/fksoundboxn</t>
+  </si>
+  <si>
+    <t>https://dodgerblue-dragonfly-520818.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://summersalefk.com/f60f5cba9e/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://blanchedalmond-kudu-912286.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://mesho.diziebook.shop</t>
+  </si>
+  <si>
+    <t>https://violet-fish-896843.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://ivory-okapi-964506.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/804cc28d</t>
+  </si>
+  <si>
+    <t>https://fitshirt.store</t>
+  </si>
+  <si>
+    <t>https://fipkartbigsavings.shop/newsale</t>
+  </si>
+  <si>
+    <t>https://lightskyblue-quail-640026.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://aqua-guanaco-165107.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://biggest-dhamaka-sale.com/e8dcdb61b3</t>
+  </si>
+  <si>
+    <t>https://mistyrose-goshawk-231036.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://dhamaka-offer.live/Ankit/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://flipkert.us.cc/TtxM/OFFER/cmf126</t>
+  </si>
+  <si>
+    <t>https://phpstack-1593364-6254845.cloudwaysapps.com</t>
+  </si>
+  <si>
+    <t>https://phpstack-1593364-6264999.cloudwaysapps.com</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/MxrLn/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://phpstack-1598224-6264971.cloudwaysapps.com</t>
+  </si>
+  <si>
+    <t>https://buywear.online</t>
+  </si>
+  <si>
+    <t>https://bio-url.live/a12f20</t>
+  </si>
+  <si>
+    <t>https://offerbigsales.xyz/Rehan/OFFER/customize</t>
+  </si>
+  <si>
+    <t>https://flipkert.us.cc/SAGz/OFFER/cmf126</t>
+  </si>
+  <si>
+    <t>https://firebrick-woodcock-735806.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.megasaleoffers.shop/Triyo24Jan/OFFER/meesho-tshirt</t>
+  </si>
+  <si>
+    <t>https://new.greatindiasale.live/users/pankajbhai</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/91bf1e48</t>
+  </si>
+  <si>
+    <t>https://summersalefk.com/d7eacb0d5a/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://summersalefk.com/684d64a762/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://lavenderblush-hawk-375938.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://firebrick-gnu-648969.hostingersite.com/btmain</t>
+  </si>
+  <si>
+    <t>https://magenta-jellyfish-947816.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://trolleys-flip.shop/mydeals</t>
+  </si>
+  <si>
+    <t>https://flipcart-bigsavingdays.shop/savingdeals</t>
+  </si>
+  <si>
+    <t>https://flipskart-offersale.shop/savingdeals</t>
+  </si>
+  <si>
+    <t>https://new.greatindiasale.live/users/rony/OFFER</t>
+  </si>
+  <si>
+    <t>https://sale.festiveeseason.shop/Vkufhkfikbcj/OFFER</t>
+  </si>
+  <si>
+    <t>https://biggest-sale.com/bot</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/RohanOp/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://crazydealsfk.site/FLIPKART/Iconic</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Lnnxbbd/OFFER/meesho-dress</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Jxbvdv/OFFER/99-199</t>
+  </si>
+  <si>
+    <t>https://new.megasaleoffers.shop/Syco/OFFER/scratch-allupi</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/84254970/shoesn</t>
+  </si>
+  <si>
+    <t>https://new.get-1495.sbs</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/5a000e7a/fkcustomsc</t>
+  </si>
+  <si>
+    <t>https://betrady.online</t>
+  </si>
+  <si>
+    <t>https://fiipkart-summer.lovable.app</t>
+  </si>
+  <si>
+    <t>https://bgmieventslivee2025.shop/ftery</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Shrm/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://magenta-heron-153902.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/5ab0013e</t>
+  </si>
+  <si>
+    <t>https://flipkart-summer-sales.myshopify.com/collections/frontpage</t>
+  </si>
+  <si>
+    <t>https://www.flipkartmarchsale.in</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/67136b60/endsalebudsn</t>
+  </si>
+  <si>
+    <t>https://dhamaka-offer.live/Boss/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://papayawhip-squirrel-914037.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://salmon-mallard-890812.hostingersite.com/davat</t>
+  </si>
+  <si>
+    <t>https://new.offer-start.com/Psisgv/OFFER/meesho-dress</t>
+  </si>
+  <si>
+    <t>https://crazydealsfk.site/FLIPKART/152</t>
+  </si>
+  <si>
+    <t>https://bigsavings-filpkarts.shop/newstore</t>
+  </si>
+  <si>
+    <t>https://biggest-sale.com/watch</t>
+  </si>
+  <si>
+    <t>https://new.year-sales.xyz/f219078d29/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://offerbigsales.xyz/Toxic/OFFER/cmf126</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Sameer/OFFER/kitchen</t>
+  </si>
+  <si>
+    <t>https://foxship.shop/newshop</t>
+  </si>
+  <si>
+    <t>https://flipcart-summersale.shop/savingdeals</t>
+  </si>
+  <si>
+    <t>https://new.greatindiasale.live/users/pompom/OFFER</t>
+  </si>
+  <si>
+    <t>https://mediumvioletred-rail-865467.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://healthprime.fun</t>
+  </si>
+  <si>
+    <t>https://plum-lobster-541291.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://offers.sale-lives.com/users/7b83eedf/meeshon</t>
+  </si>
+  <si>
+    <t>https://new.year-sales.xyz/684d64a762/OFFER/holi-fk161</t>
+  </si>
+  <si>
+    <t>https://new.year-sales.xyz/f60f5cba9e/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://flipskart-summersale.shop/savingdeals</t>
+  </si>
+  <si>
+    <t>https://flipkart-summer-sale299.myshopify.com/collections/frontpage</t>
+  </si>
+  <si>
+    <t>https://crazydealsfk.site/FLIPKART/Yu1</t>
+  </si>
+  <si>
+    <t>https://sagnikgeek.com/product-category/DEF/page3/index.php</t>
+  </si>
+  <si>
+    <t>https://new.deals-indian.com/f8d83dba</t>
+  </si>
+  <si>
+    <t>https://seagreen-pony-608468.hostingersite.com/madis</t>
+  </si>
+  <si>
+    <t>https://new.year-sales.xyz/8caa0b5cdf/OFFER/earphone</t>
+  </si>
+  <si>
+    <t>https://new.year-sales.xyz/85a81dab97/OFFER/fknewbuds</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Sameer/OFFER/wintersale</t>
+  </si>
+  <si>
+    <t>https://new-year.bigsaleoffer.shop/Xwme/OFFER/kitchen</t>
+  </si>
+  <si>
+    <t>https://slategrey-deer-934291.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.year-sales.xyz/684d64a762/OFFER/99-299pods</t>
+  </si>
+  <si>
+    <t>https://peachpuff-lyrebird-264834.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://new.year-sales.xyz/3f4a2a74ef/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://summersalefk.com/8ffe72ad8b/OFFER/meesho</t>
+  </si>
+  <si>
+    <t>https://flpokrt-bigsale.shop/mydeals</t>
+  </si>
+  <si>
+    <t>https://flipcarts.shop/FLIPKART/Jbyx1buy9</t>
+  </si>
+  <si>
+    <t>https://live-sale.us.cc/prn/p/offer/99rsweb</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Seychelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithuania </t>
+  </si>
+  <si>
+    <t xml:space="preserve">France </t>
+  </si>
+  <si>
+    <t>Canada </t>
+  </si>
+  <si>
+    <t>Moldava</t>
+  </si>
+  <si>
+    <t>Sweden</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -523,21 +1906,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -575,11 +1943,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -587,15 +1954,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -908,10 +2268,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0B11C6-F16C-4224-840C-73479EB5E1E4}">
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C586"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="94.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.88671875" customWidth="1"/>
   </cols>
@@ -928,47 +2288,47 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>152</v>
+      <c r="A2" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>153</v>
+      <c r="A3" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>154</v>
+      <c r="A4" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>155</v>
+      <c r="A5" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>151</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -979,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -990,7 +2350,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1001,7 +2361,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1012,7 +2372,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1023,7 +2383,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1034,7 +2394,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1045,7 +2405,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1056,7 +2416,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1067,7 +2427,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1078,7 +2438,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -1089,7 +2449,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1100,7 +2460,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -1111,7 +2471,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -1122,7 +2482,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1133,7 +2493,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -1144,7 +2504,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -1155,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -1166,7 +2526,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -1177,7 +2537,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1185,1813 +2545,6382 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>124</v>
+        <v>3</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>126</v>
+        <v>3</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>125</v>
+        <v>3</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>111</v>
+        <v>169</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>124</v>
+        <v>3</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>122</v>
+        <v>56</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>3</v>
+        <v>609</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>76</v>
+        <v>191</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>118</v>
+        <v>193</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>128</v>
+        <v>3</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>128</v>
+        <v>3</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>128</v>
+        <v>3</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>71</v>
+        <v>207</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>71</v>
+        <v>208</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>71</v>
+        <v>209</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>108</v>
+        <v>210</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>130</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A327" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A328" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A329" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A330" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A331" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A332" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A333" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A334" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A335" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A336" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A337" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A338" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A339" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A340" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A341" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A342" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A343" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A344" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A345" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A346" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A347" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A348" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A349" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A350" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A351" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A352" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A353" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A354" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A355" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A356" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A357" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A358" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A359" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A360" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A361" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A362" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A363" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A364" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A365" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A366" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A367" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A368" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A369" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A370" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A371" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A372" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A373" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A374" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A375" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A376" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A377" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A378" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A379" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A380" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A381" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A382" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A383" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A384" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A385" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A386" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A387" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A388" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A389" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A390" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A391" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A392" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A393" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A394" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A395" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A396" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A397" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A398" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A399" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A400" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A401" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A402" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A403" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A404" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A405" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A406" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A407" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A408" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A409" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A410" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A411" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A412" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A413" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A414" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A415" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A416" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A417" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A418" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C421" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A422" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A423" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A424" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A425" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A426" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A427" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A428" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C428" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A429" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A430" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C430" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A431" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C431" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A432" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A433" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C433" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A434" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A435" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A436" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A437" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C437" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A438" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C438" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A439" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A440" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C440" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A441" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C441" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A442" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C442" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A443" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C443" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A444" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C444" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A445" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C445" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A446" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B446" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C446" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A447" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B447" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C447" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A448" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B448" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C448" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A449" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C449" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A450" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B450" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C450" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A451" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B451" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C451" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A452" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B452" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C452" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A453" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B453" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C453" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A454" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B454" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C454" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A455" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C455" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A456" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B456" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C456" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A457" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C457" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A458" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C458" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A459" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C459" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A460" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C460" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A461" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C461" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A462" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C462" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A463" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C463" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A464" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C464" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A465" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C465" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A466" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C466" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A467" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C467" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A468" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C468" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A469" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C469" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A470" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A471" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A472" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C472" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A473" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A474" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C474" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A475" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A476" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A477" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A478" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C478" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A479" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A480" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A481" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A482" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A483" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A484" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A485" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C485" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A486" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C486" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A487" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="C487" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A488" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C488" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A489" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C489" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A490" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A491" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C491" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A492" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C492" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A493" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C493" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A494" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C494" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A495" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C495" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A496" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C496" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A497" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C497" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A498" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C498" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A499" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C499" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A500" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C500" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A501" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C501" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A502" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C502" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A503" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C503" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A504" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C504" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A505" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A506" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C506" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A507" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A508" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C508" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A509" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A510" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C510" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A511" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C511" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A512" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C512" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A513" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A514" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A515" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C515" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A516" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C516" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A517" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A518" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C518" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A519" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C519" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A520" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A521" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C521" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A522" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A523" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A524" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A525" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A526" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A527" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A528" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A529" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C529" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A530" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C530" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A531" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C531" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A532" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C532" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A533" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C533" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A534" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C534" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A535" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C535" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A536" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C536" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A537" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C537" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A538" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C538" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A539" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C539" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A540" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A541" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C541" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A542" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A543" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A544" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C544" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A545" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C545" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A546" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A547" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C547" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A548" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C548" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A549" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C549" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A550" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C550" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A551" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C551" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A552" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C552" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A553" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C553" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A554" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C554" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A555" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C555" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A556" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C556" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A557" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C557" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A558" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C558" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A559" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C559" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A560" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C560" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A561" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C561" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A562" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C562" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A563" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C563" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A564" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C564" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A565" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C565" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A566" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C566" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A567" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C567" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A568" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C568" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A569" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C569" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A570" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C570" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A571" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C571" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A572" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C572" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A573" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A574" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C574" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A575" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A576" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C576" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A577" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C577" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A578" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C578" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A579" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C579" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A580" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C580" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A581" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C581" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A582" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C582" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A583" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C583" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A584" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C584" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A585" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A586" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A181" r:id="rId1" display="https://www.hara7ksm-ft11ye.cc/" xr:uid="{ABDB42CD-3598-4100-9239-B6F74345AE97}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{1742F09F-6D1A-4CDA-BB14-8BC64089397B}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{BD7EE5DE-FD8F-4CCD-BE03-23430A5C36F0}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{C9E2C1F4-5A90-4B76-9B2F-219AB9C62599}"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{1742F09F-6D1A-4CDA-BB14-8BC64089397B}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{BD7EE5DE-FD8F-4CCD-BE03-23430A5C36F0}"/>
+    <hyperlink ref="B100" r:id="rId3" display="https://myip.ms/view/countries/USA/Internet_Usage_Statistics_USA.html" xr:uid="{34B5AA4C-4000-4954-B025-EEB8547EDF72}"/>
+    <hyperlink ref="A146" r:id="rId4" display="https://bigwinoffer.com.tr/" xr:uid="{98C766A6-866D-407A-A703-A304F2271943}"/>
+    <hyperlink ref="A147" r:id="rId5" xr:uid="{BD339C4C-F3D6-4339-914A-629492FF0313}"/>
+    <hyperlink ref="A152" r:id="rId6" xr:uid="{170DE5A7-BE41-4BD8-A8E7-CDE00238162F}"/>
+    <hyperlink ref="A153" r:id="rId7" xr:uid="{8A69FD07-0DF7-4EDE-9E5F-DC8F506B570E}"/>
+    <hyperlink ref="A163" r:id="rId8" xr:uid="{C553ACF4-3781-492E-BD5B-E824E9FF5C3E}"/>
+    <hyperlink ref="A166" r:id="rId9" xr:uid="{5D8F5B3F-17AE-4DF2-AD5E-9613E48F65E0}"/>
+    <hyperlink ref="A167" r:id="rId10" xr:uid="{D4AF918A-E899-4C6A-8824-5157F7D247B1}"/>
+    <hyperlink ref="A168" r:id="rId11" xr:uid="{F554D08F-0620-410D-A203-70DF8D4BD8A7}"/>
+    <hyperlink ref="A169" r:id="rId12" xr:uid="{232A2CD1-646E-4812-AE7D-13AB9A95D539}"/>
+    <hyperlink ref="A175" r:id="rId13" xr:uid="{C70A6BA3-3B94-42A0-B1AC-0B1981DA4DBB}"/>
+    <hyperlink ref="A188" r:id="rId14" xr:uid="{4F7A26AB-5F2B-4F29-B785-A4AEAD3256FD}"/>
+    <hyperlink ref="A189" r:id="rId15" xr:uid="{6D4DCC2E-630E-4ECF-8711-194F3FF9F36B}"/>
+    <hyperlink ref="A190" r:id="rId16" xr:uid="{CDAAF86A-C222-4A2B-B805-935CDD2492ED}"/>
+    <hyperlink ref="A192" r:id="rId17" display="https://meeshosalemeesho.store/" xr:uid="{407D2E40-C398-454D-9CE1-60A818B99B53}"/>
+    <hyperlink ref="A193" r:id="rId18" xr:uid="{A9918901-20E2-44D9-A6E5-21293D85876A}"/>
+    <hyperlink ref="A196" r:id="rId19" display="https://me-esho.netlify.app/" xr:uid="{F642A9F9-6008-4571-8ADA-709AA1672F98}"/>
+    <hyperlink ref="A197" r:id="rId20" xr:uid="{6513F9F0-7F4F-4843-A74A-0CB4874E0599}"/>
+    <hyperlink ref="A201" r:id="rId21" xr:uid="{F62E82C0-1B21-4251-BCAC-E0323EB23981}"/>
+    <hyperlink ref="A218" r:id="rId22" xr:uid="{7E52A3D5-33B5-4025-8474-2362A1C0FC9C}"/>
+    <hyperlink ref="A273" r:id="rId23" xr:uid="{4EA6B28F-57D3-40EB-A1A6-6C25D45AFF06}"/>
+    <hyperlink ref="A274" r:id="rId24" xr:uid="{B1A637C6-B83A-4431-970F-AE1D781F7510}"/>
+    <hyperlink ref="A275" r:id="rId25" xr:uid="{45682F5A-A237-45C3-96BB-F43A9439BDD5}"/>
+    <hyperlink ref="A276" r:id="rId26" xr:uid="{DB9A5180-8F2B-419E-8B26-86E9E68F0555}"/>
+    <hyperlink ref="A279" r:id="rId27" xr:uid="{B08E4BBD-D132-42C5-83C7-A35E01B01762}"/>
+    <hyperlink ref="A326" r:id="rId28" xr:uid="{D442933B-7EFF-4840-B6C6-36CC50121D06}"/>
+    <hyperlink ref="A327" r:id="rId29" xr:uid="{3F8D3800-3C6B-417A-9353-AE42F2A981AC}"/>
+    <hyperlink ref="A330" r:id="rId30" xr:uid="{C1805AF2-D1A1-4825-AF0F-2AF3ED072F02}"/>
+    <hyperlink ref="A333" r:id="rId31" xr:uid="{8204F786-BE48-4C16-BEB2-D1D959C2BB89}"/>
+    <hyperlink ref="A337" r:id="rId32" xr:uid="{9719F79F-2C88-4611-894E-3ECDADE8E57E}"/>
+    <hyperlink ref="A338" r:id="rId33" xr:uid="{1A723955-4FB1-4C35-AFDE-721A2275A546}"/>
+    <hyperlink ref="A339" r:id="rId34" xr:uid="{130E758A-3D4D-419E-8236-C07151C99AD2}"/>
+    <hyperlink ref="A340" r:id="rId35" xr:uid="{77192F96-45E6-42AA-B872-F6A0E0472031}"/>
+    <hyperlink ref="A344" r:id="rId36" xr:uid="{4F1D3828-0567-48C5-A987-84FFE637D95C}"/>
+    <hyperlink ref="A345" r:id="rId37" xr:uid="{3D67BDCE-1DA2-447A-BA58-554F134B7C00}"/>
+    <hyperlink ref="A346" r:id="rId38" xr:uid="{C12B6E0A-9823-4426-B0FE-8BBFEA3835EB}"/>
+    <hyperlink ref="A349" r:id="rId39" xr:uid="{F82145D5-63AF-4BC4-A3A3-C7EFC7B659E2}"/>
+    <hyperlink ref="A350" r:id="rId40" display="https://yellow-emu-733093.hostingersite.com/" xr:uid="{498B7977-1C68-44F8-A612-C3FCDC6308DC}"/>
+    <hyperlink ref="A354" r:id="rId41" xr:uid="{AF1BAF98-1EA5-4501-8822-F9A4AEC9886A}"/>
+    <hyperlink ref="A355" r:id="rId42" xr:uid="{F24BB87D-B1D5-49AE-8CAF-22A7ED07F7EE}"/>
+    <hyperlink ref="A356" r:id="rId43" xr:uid="{F27DE639-C332-4C51-8BA7-BA96150BD1F9}"/>
+    <hyperlink ref="A361" r:id="rId44" xr:uid="{6B755285-6191-481C-8905-64260133B3ED}"/>
+    <hyperlink ref="A366" r:id="rId45" xr:uid="{39918188-4D6A-4CF0-A2EE-121BE4F7ACA0}"/>
+    <hyperlink ref="A367" r:id="rId46" xr:uid="{3F1A5270-1234-4BEE-96EC-59639650FCD1}"/>
+    <hyperlink ref="A370" r:id="rId47" xr:uid="{0F0E5898-D3C9-44F1-B399-4B5E1123A6FA}"/>
+    <hyperlink ref="A371" r:id="rId48" xr:uid="{86983A0A-DF54-4D82-8CFF-9D09324C1C04}"/>
+    <hyperlink ref="A372" r:id="rId49" display="https://flipcart-limited-offer.myshopify.com/" xr:uid="{2FB3D63C-F210-4F00-BE43-F63709ED29E3}"/>
+    <hyperlink ref="A373" r:id="rId50" xr:uid="{CF8F5958-57A0-4BA6-853C-30DBD1615E7E}"/>
+    <hyperlink ref="A374" r:id="rId51" xr:uid="{A1755E63-EBAB-4478-8E95-A721B0B2387B}"/>
+    <hyperlink ref="A377" r:id="rId52" xr:uid="{5FE0A41A-BEB0-4963-AE20-2F2F496105E5}"/>
+    <hyperlink ref="A378" r:id="rId53" xr:uid="{A162107B-41F3-4860-9DB5-3DE0A8603686}"/>
+    <hyperlink ref="A379" r:id="rId54" xr:uid="{88C77D28-0BED-401C-8791-020CF421822B}"/>
+    <hyperlink ref="A380" r:id="rId55" location="/home" display="https://dailysoapupdate.com/mysale01/ - /home" xr:uid="{ED445AD5-69EE-441C-8862-4D810E52DEC5}"/>
+    <hyperlink ref="A381" r:id="rId56" xr:uid="{1D6F2C4D-7C9C-4683-92F5-01BEB8099356}"/>
+    <hyperlink ref="A384" r:id="rId57" xr:uid="{19A630BA-D6C2-4E67-AEDE-DE86D518D7D5}"/>
+    <hyperlink ref="A385" r:id="rId58" xr:uid="{78101AA3-5C2E-4F84-83FA-2CB98D6D6CFB}"/>
+    <hyperlink ref="A387" r:id="rId59" xr:uid="{2B4761C7-50C1-4EDD-B96F-4F1787E1CBC8}"/>
+    <hyperlink ref="A393" r:id="rId60" display="https://green-mantis-164394.hostingersite.com/" xr:uid="{2B34A4E4-9398-403A-90EE-D85B9CA16F25}"/>
+    <hyperlink ref="A394" r:id="rId61" xr:uid="{E4560E2B-C78E-41C3-957D-D2BF080E03BE}"/>
+    <hyperlink ref="A395" r:id="rId62" xr:uid="{88BF5337-E77C-401E-8BC2-18E9BF59341E}"/>
+    <hyperlink ref="A396" r:id="rId63" xr:uid="{580A7D3E-475D-4E0A-ADE4-8349A3E3BBF7}"/>
+    <hyperlink ref="A397" r:id="rId64" xr:uid="{2D85C088-CC59-4C3B-AC6D-B0BB778648DF}"/>
+    <hyperlink ref="A398" r:id="rId65" xr:uid="{E4174A7C-DDDC-4B6C-8C39-0BFC26F53C7F}"/>
+    <hyperlink ref="A399" r:id="rId66" display="https://meesho.onlinelehenga.com/" xr:uid="{99E9B889-84BA-4CD1-BDD1-2110E9D84A11}"/>
+    <hyperlink ref="A400" r:id="rId67" display="https://saddlebrown-koala-214922.hostingersite.com/" xr:uid="{E1D58D6D-CC15-40C2-8C83-B5D97520250B}"/>
+    <hyperlink ref="A401" r:id="rId68" xr:uid="{B3CA8362-172B-456D-8124-441D397572CC}"/>
+    <hyperlink ref="A402" r:id="rId69" xr:uid="{A85E772E-58E3-417C-A8C7-546B587A8CD7}"/>
+    <hyperlink ref="A403" r:id="rId70" xr:uid="{A436E5C8-0361-4819-B3AB-8624CFA890A0}"/>
+    <hyperlink ref="A404" r:id="rId71" xr:uid="{265D5089-7AFF-42BB-810C-3D0086B4C577}"/>
+    <hyperlink ref="A414" r:id="rId72" display="https://mediumturquoise-peafowl-207676.hostingersite.com/" xr:uid="{272F65DF-8C9B-40EB-832D-D1D568C5C95F}"/>
+    <hyperlink ref="A415" r:id="rId73" display="https://lightgrey-quail-699092.hostingersite.com/" xr:uid="{9D26575C-F7EE-4EB9-A8D6-0B3DF183BD17}"/>
+    <hyperlink ref="A416" r:id="rId74" xr:uid="{AFAE0A08-FD6C-4564-BAF4-5EBE6A761042}"/>
+    <hyperlink ref="A417" r:id="rId75" display="https://khaki-stinkbug-900591.hostingersite.com/" xr:uid="{02F8DE61-3E76-4D62-A3D7-8E5DE7BFED51}"/>
+    <hyperlink ref="A418" r:id="rId76" display="https://beige-scorpion-308566.hostingersite.com/" xr:uid="{680EC066-7949-4C62-8DBA-371DF624B69D}"/>
+    <hyperlink ref="A419" r:id="rId77" display="https://measho003.vercel.app/" xr:uid="{0CB320BA-83FC-42A0-BD43-530D7E1C786B}"/>
+    <hyperlink ref="A420" r:id="rId78" display="https://royalblue-hare-879414.hostingersite.com/" xr:uid="{AE6E1953-24D9-4881-B883-9CCF98D52420}"/>
+    <hyperlink ref="A421" r:id="rId79" display="https://lightpink-cheetah-375413.hostingersite.com/" xr:uid="{EDD8458A-09FD-434E-A114-A5DD42EFD5C8}"/>
+    <hyperlink ref="A422" r:id="rId80" xr:uid="{BABCF7E5-06BB-4024-9D50-7591DB5C2F66}"/>
+    <hyperlink ref="A423" r:id="rId81" xr:uid="{3AF9AB90-2C4D-455F-AB73-188B9B5C1765}"/>
+    <hyperlink ref="A426" r:id="rId82" xr:uid="{8E97EC4A-2BBC-4615-B9AE-5C97992268F7}"/>
+    <hyperlink ref="A427" r:id="rId83" xr:uid="{13288E77-41EE-4E13-8F6E-DA18ABA2353D}"/>
+    <hyperlink ref="A428" r:id="rId84" xr:uid="{B34C83F0-9CBC-4244-8527-6EDB22B40A63}"/>
+    <hyperlink ref="A439" r:id="rId85" xr:uid="{8D07D963-0F10-4C7D-AF3E-10838F031EC0}"/>
+    <hyperlink ref="A440" r:id="rId86" xr:uid="{0F171A6F-4697-4B15-B75F-5C5B28FD8EBF}"/>
+    <hyperlink ref="A441" r:id="rId87" xr:uid="{86816317-97A1-4F97-B212-EAEF22EA4A46}"/>
+    <hyperlink ref="A446" r:id="rId88" xr:uid="{39B53F48-B091-4FDC-81D5-4040E21911B5}"/>
+    <hyperlink ref="A462" r:id="rId89" display="https://darkseagreen-ibex-492354.hostingersite.com/" xr:uid="{05BFAF4E-1D3D-4F3A-AFD6-3005F392BE91}"/>
+    <hyperlink ref="A463" r:id="rId90" display="https://chocolate-starling-667762.hostingersite.com/" xr:uid="{4D7990B0-A29A-485E-AD19-57AA461B7BE1}"/>
+    <hyperlink ref="A464" r:id="rId91" xr:uid="{BF1DB468-4452-4635-9DB4-EF97DF2F0196}"/>
+    <hyperlink ref="A465" r:id="rId92" display="https://gray-reindeer-806195.hostingersite.com/" xr:uid="{19DB1B5A-1E0E-4594-8096-1E5664BD5E13}"/>
+    <hyperlink ref="A469" r:id="rId93" xr:uid="{837BEB80-5076-4CEE-8D70-5AB707037F54}"/>
+    <hyperlink ref="A470" r:id="rId94" xr:uid="{5093A6EB-E127-4496-BA54-6236FECA25E8}"/>
+    <hyperlink ref="A471" r:id="rId95" xr:uid="{D630EA1D-B9F9-44C6-874E-0BF01DC4F8F4}"/>
+    <hyperlink ref="A473" r:id="rId96" xr:uid="{A9290627-01F9-44B1-A392-DC3DEF07BA62}"/>
+    <hyperlink ref="A474" r:id="rId97" xr:uid="{CC2CBEDC-4223-4E73-BB9A-F9F9C7B42DB6}"/>
+    <hyperlink ref="A475" r:id="rId98" xr:uid="{5D811E40-F96F-44B6-9611-A8E4AFBEB75F}"/>
+    <hyperlink ref="A476" r:id="rId99" display="https://sienna-hyena-831771.hostingersite.com/" xr:uid="{B75933FC-FE72-4DE4-85F7-653B5AEDEA88}"/>
+    <hyperlink ref="A477" r:id="rId100" xr:uid="{F90BADA9-FA80-4F18-9BE5-683A897A4160}"/>
+    <hyperlink ref="A478" r:id="rId101" xr:uid="{83D2B7E0-12D5-471C-99CA-E847A7C6E3CE}"/>
+    <hyperlink ref="A479" r:id="rId102" xr:uid="{858504A4-8AB9-4CC7-AA93-6EFA272E914F}"/>
+    <hyperlink ref="A480" r:id="rId103" xr:uid="{2B447FFF-9B8C-4DAC-91D7-40ABD5900586}"/>
+    <hyperlink ref="A481" r:id="rId104" display="https://slategray-mandrill-919025.hostingersite.com/" xr:uid="{AFAA1FDC-23E8-4EDB-B8A6-EEC5C04F21BC}"/>
+    <hyperlink ref="A482" r:id="rId105" display="https://meeshom.sales-india.com/" xr:uid="{1ADD0AA0-545F-481A-AE74-072B14FBA8DC}"/>
+    <hyperlink ref="A483" r:id="rId106" xr:uid="{4955BF0E-FEE6-49A9-8A8C-B04D55598E83}"/>
+    <hyperlink ref="A484" r:id="rId107" xr:uid="{B05DFDC5-31C7-4424-93BB-96A9D5711259}"/>
+    <hyperlink ref="A485" r:id="rId108" display="https://gold-mink-565478.hostingersite.com/" xr:uid="{1EF925E2-DD85-48AD-B845-2748723D0F6D}"/>
+    <hyperlink ref="A486" r:id="rId109" display="https://yellowgreen-quail-835557.hostingersite.com/" xr:uid="{F8C6920F-1BE6-40BD-8C13-0337251BAFD7}"/>
+    <hyperlink ref="A487" r:id="rId110" xr:uid="{3BC060C3-D665-473D-AFD2-134A1B636098}"/>
+    <hyperlink ref="A488" r:id="rId111" xr:uid="{265E54A1-8E84-4B1E-954C-58729FF53ADE}"/>
+    <hyperlink ref="A489" r:id="rId112" xr:uid="{A9C37654-D78B-4067-B340-544416D25FB9}"/>
+    <hyperlink ref="A490" r:id="rId113" xr:uid="{2E1A8F80-5088-449E-8854-68BA06CF22F3}"/>
+    <hyperlink ref="A491" r:id="rId114" display="https://betary.online/" xr:uid="{13B27B5E-0249-49C2-ABF1-7EFAF84CA62E}"/>
+    <hyperlink ref="A492" r:id="rId115" xr:uid="{C60B6BBE-9153-4861-B083-4410F52E47BD}"/>
+    <hyperlink ref="A494" r:id="rId116" xr:uid="{A21EB6CD-8244-4AB4-9DC9-C59EE0579158}"/>
+    <hyperlink ref="A495" r:id="rId117" display="https://dodgerblue-dragonfly-520818.hostingersite.com/" xr:uid="{B7C5A4F4-56BA-42A9-8300-3C4319185262}"/>
+    <hyperlink ref="A496" r:id="rId118" xr:uid="{60481478-3062-4963-A96B-669A3705D799}"/>
+    <hyperlink ref="A497" r:id="rId119" display="https://blanchedalmond-kudu-912286.hostingersite.com/" xr:uid="{9E025F2A-EBBF-4264-B849-104D36A319B3}"/>
+    <hyperlink ref="A498" r:id="rId120" display="https://mesho.diziebook.shop/" xr:uid="{B527BCB8-ED00-41FD-B7BF-C873F9955C15}"/>
+    <hyperlink ref="A499" r:id="rId121" display="https://violet-fish-896843.hostingersite.com/" xr:uid="{6B77CF77-71BB-4AE6-945A-4A609C2DF7A7}"/>
+    <hyperlink ref="A500" r:id="rId122" display="https://ivory-okapi-964506.hostingersite.com/" xr:uid="{BD2F584B-E6C8-40BB-8281-AF3AAF43B155}"/>
+    <hyperlink ref="A501" r:id="rId123" xr:uid="{F935201D-6921-4D4C-A839-C1A4740FB122}"/>
+    <hyperlink ref="A502" r:id="rId124" display="https://fitshirt.store/" xr:uid="{655157C1-1463-4610-A1CE-BC91506AC59B}"/>
+    <hyperlink ref="A503" r:id="rId125" xr:uid="{4A653EA3-A56F-4612-A850-CEF323C97FD2}"/>
+    <hyperlink ref="A504" r:id="rId126" display="https://lightskyblue-quail-640026.hostingersite.com/" xr:uid="{2F421E40-D20D-4779-9F0A-B36600202033}"/>
+    <hyperlink ref="A505" r:id="rId127" display="https://aqua-guanaco-165107.hostingersite.com/" xr:uid="{4F02A28F-F315-48D3-9543-5F22AC4584E0}"/>
+    <hyperlink ref="A506" r:id="rId128" xr:uid="{44B2E1F3-6BDA-4611-B6B6-1DCFC567A78A}"/>
+    <hyperlink ref="A507" r:id="rId129" display="https://mistyrose-goshawk-231036.hostingersite.com/" xr:uid="{80F782E1-C019-4E0A-8996-06E0C4F05076}"/>
+    <hyperlink ref="A508" r:id="rId130" xr:uid="{84D53771-AA31-47F3-9B6E-10B34EAE07EB}"/>
+    <hyperlink ref="A509" r:id="rId131" xr:uid="{2C0C7C83-EE83-4F93-8791-ED56E1135CE9}"/>
+    <hyperlink ref="A510" r:id="rId132" display="https://phpstack-1593364-6254845.cloudwaysapps.com/" xr:uid="{AC1AE79A-32B2-43CA-9A47-451A4B229199}"/>
+    <hyperlink ref="A511" r:id="rId133" display="https://phpstack-1593364-6264999.cloudwaysapps.com/" xr:uid="{6A5B5E2F-66F7-4049-B8DA-60B77EFB39F5}"/>
+    <hyperlink ref="A512" r:id="rId134" xr:uid="{731A7782-6787-4E11-81B3-33A0F36DBF18}"/>
+    <hyperlink ref="A513" r:id="rId135" display="https://phpstack-1598224-6264971.cloudwaysapps.com/" xr:uid="{F7E37C8C-9436-48AB-A8B9-681375E0D9D9}"/>
+    <hyperlink ref="A514" r:id="rId136" display="https://buywear.online/" xr:uid="{3CE13E3F-A7B1-41B1-8C58-C63315B0F0FB}"/>
+    <hyperlink ref="A515" r:id="rId137" xr:uid="{FF2CAB0F-C32B-4402-8C0D-9957313869DE}"/>
+    <hyperlink ref="A516" r:id="rId138" xr:uid="{46E41F23-D317-4750-BB34-954DD9B02D0C}"/>
+    <hyperlink ref="A517" r:id="rId139" xr:uid="{24FC14A7-66DE-46B1-ABBB-7577B3A29580}"/>
+    <hyperlink ref="A518" r:id="rId140" display="https://firebrick-woodcock-735806.hostingersite.com/" xr:uid="{FB5A83CF-0EB1-47C3-9F0A-0813120DCA1E}"/>
+    <hyperlink ref="A519" r:id="rId141" xr:uid="{404AF3F9-710D-4784-877C-CF27CC2605A2}"/>
+    <hyperlink ref="A520" r:id="rId142" xr:uid="{A13682AD-69BF-4672-BB57-B7C4CAE56BAF}"/>
+    <hyperlink ref="A521" r:id="rId143" xr:uid="{42694ADB-0527-4ECB-820B-DB9CBF023394}"/>
+    <hyperlink ref="A529" r:id="rId144" xr:uid="{903E3CD7-2290-460A-AB98-DA9882E5A2E7}"/>
+    <hyperlink ref="A530" r:id="rId145" xr:uid="{22C76230-701D-4560-AB16-3858D1E6FE64}"/>
+    <hyperlink ref="A531" r:id="rId146" xr:uid="{5075D533-79C7-42B0-860F-ED51B85EF0FE}"/>
+    <hyperlink ref="A532" r:id="rId147" xr:uid="{96868CF8-4501-4D6A-A2BA-49ABB2904F00}"/>
+    <hyperlink ref="A533" r:id="rId148" xr:uid="{E181E12E-2ABE-4340-99F9-C064A7FE2B0F}"/>
+    <hyperlink ref="A534" r:id="rId149" xr:uid="{39E2B466-C829-4724-B8AB-B2E58455EBB5}"/>
+    <hyperlink ref="A535" r:id="rId150" xr:uid="{C2CE0306-0B8C-44BD-970C-0F207A06CBF3}"/>
+    <hyperlink ref="A541" r:id="rId151" display="https://betrady.online/" xr:uid="{1B9B1187-BE58-4AB6-AB58-E032E28ADEC2}"/>
+    <hyperlink ref="A542" r:id="rId152" display="https://fiipkart-summer.lovable.app/" xr:uid="{6D4BCADB-A456-440C-B244-61F3AC515CD7}"/>
+    <hyperlink ref="A544" r:id="rId153" xr:uid="{E198A9E9-F98A-4474-AECE-3016ED06D033}"/>
+    <hyperlink ref="A545" r:id="rId154" display="https://magenta-heron-153902.hostingersite.com/" xr:uid="{F04AC313-32A4-49F6-9735-B56B7053A1F8}"/>
+    <hyperlink ref="A546" r:id="rId155" xr:uid="{5A477327-F60A-4B1F-B201-985D79BD8775}"/>
+    <hyperlink ref="A547" r:id="rId156" xr:uid="{47158B01-1788-4192-8FB3-7A642C701780}"/>
+    <hyperlink ref="A548" r:id="rId157" display="https://www.flipkartmarchsale.in/" xr:uid="{66220ACB-1093-460E-8519-74761A1EE8DF}"/>
+    <hyperlink ref="A549" r:id="rId158" xr:uid="{40B37356-0F0E-4569-9A60-304ACDF5E8A9}"/>
+    <hyperlink ref="A556" r:id="rId159" xr:uid="{2246594F-0BFC-491A-8335-11CD82E66C33}"/>
+    <hyperlink ref="A557" r:id="rId160" xr:uid="{B6269A59-A82A-4306-A5C0-CBD5DB5A5FB9}"/>
+    <hyperlink ref="A559" r:id="rId161" xr:uid="{A15407B8-DE2D-4645-A5CF-EBDB2C3D2CFD}"/>
+    <hyperlink ref="A560" r:id="rId162" xr:uid="{50A935C0-2F94-447E-808F-C62582CFC903}"/>
+    <hyperlink ref="A561" r:id="rId163" xr:uid="{66AEAB67-754E-47D8-A494-F586E1829510}"/>
+    <hyperlink ref="A562" r:id="rId164" xr:uid="{98E3B68A-B453-4DC2-B479-E5AE0A00A948}"/>
+    <hyperlink ref="A563" r:id="rId165" display="https://mediumvioletred-rail-865467.hostingersite.com/" xr:uid="{99E68E58-217B-4B07-8846-6371FE797D0A}"/>
+    <hyperlink ref="A564" r:id="rId166" display="https://healthprime.fun/" xr:uid="{A9EF7D20-8E71-474A-B08A-B6511D70993E}"/>
+    <hyperlink ref="A565" r:id="rId167" display="https://plum-lobster-541291.hostingersite.com/" xr:uid="{9C48409B-A44C-41AE-9A3B-C5C3608FC8FD}"/>
+    <hyperlink ref="A566" r:id="rId168" xr:uid="{C83AEB37-67C2-4A5A-86EE-F382DE5AB006}"/>
+    <hyperlink ref="A567" r:id="rId169" xr:uid="{CBE2175F-9647-442F-B51F-0C361C71F97B}"/>
+    <hyperlink ref="A569" r:id="rId170" xr:uid="{02252EC6-FF65-4C04-9EB0-78BA914777F3}"/>
+    <hyperlink ref="A570" r:id="rId171" xr:uid="{A027763B-6966-4A9E-B434-73705A78E6E2}"/>
+    <hyperlink ref="A571" r:id="rId172" xr:uid="{12870190-F4E8-4ACC-B5CD-138A52774920}"/>
+    <hyperlink ref="A572" r:id="rId173" xr:uid="{DEEEF48B-486C-4467-9F0A-703940D111C2}"/>
+    <hyperlink ref="A573" r:id="rId174" xr:uid="{F6DFFAEE-62E9-484B-A82D-D05D9E0473EA}"/>
+    <hyperlink ref="A574" r:id="rId175" xr:uid="{2FAADB78-55BF-408D-A4F5-035D4491F8AA}"/>
+    <hyperlink ref="A575" r:id="rId176" xr:uid="{20E948BE-7EB3-41D3-99F2-FB061E2C655D}"/>
+    <hyperlink ref="A576" r:id="rId177" xr:uid="{F3BDF017-D2C3-4D8F-ADDD-419BC5E7D6F5}"/>
+    <hyperlink ref="A577" r:id="rId178" xr:uid="{AFD9F105-D09C-41D4-91FA-A1ADD6F83C5A}"/>
+    <hyperlink ref="A578" r:id="rId179" xr:uid="{2A0A0FE5-B9BD-418E-86DD-D2F425CC69AD}"/>
+    <hyperlink ref="A584" r:id="rId180" xr:uid="{D3582409-A6AC-4F71-8F92-E8C7883AB73A}"/>
+    <hyperlink ref="A585" r:id="rId181" xr:uid="{6D91B0E3-2F1B-49C0-8976-178186AF1A70}"/>
+    <hyperlink ref="A586" r:id="rId182" xr:uid="{08480B4A-B583-4D2A-9A92-0CA262A70CBE}"/>
+    <hyperlink ref="B429" r:id="rId183" display="https://myip.ms/view/countries/FRA/Internet_Usage_Statistics_France.html" xr:uid="{F2737594-B0B1-499C-9C64-78091118CFA5}"/>
+    <hyperlink ref="B432" r:id="rId184" display="https://myip.ms/view/countries/USA/Internet_Usage_Statistics_USA.html" xr:uid="{384CEC91-81BC-4D52-ADA5-6DFC320BB9BA}"/>
+    <hyperlink ref="B462" r:id="rId185" display="https://myip.ms/view/countries/DEU/Internet_Usage_Statistics_Germany.html" xr:uid="{C49C907F-14E8-414C-96AB-FD6ADD032D1C}"/>
+    <hyperlink ref="B463" r:id="rId186" display="https://myip.ms/view/countries/FRA/Internet_Usage_Statistics_France.html" xr:uid="{67204D82-5BF6-4BB8-8FB5-CFD5EBC0EDB5}"/>
+    <hyperlink ref="B464" r:id="rId187" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{78B1A8AA-423F-42D7-8447-1330B01412D1}"/>
+    <hyperlink ref="B465" r:id="rId188" display="https://myip.ms/view/countries/FRA/Internet_Usage_Statistics_France.html" xr:uid="{DD02A525-310A-4583-BE2D-405D08E5E12F}"/>
+    <hyperlink ref="B466" r:id="rId189" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{A13066FC-25B6-4351-BF2B-A87618F35853}"/>
+    <hyperlink ref="B467" r:id="rId190" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{5CF2DBA8-8FE4-4A82-85FB-7841BCE823F5}"/>
+    <hyperlink ref="B470" r:id="rId191" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{B25FA224-1524-4E9B-AE27-41143DF6223E}"/>
+    <hyperlink ref="B471" r:id="rId192" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{E8571A1D-2B16-4088-8D7C-5E6CB2018ECC}"/>
+    <hyperlink ref="B520" r:id="rId193" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{4BD7D44C-BEF7-47A4-99B5-16D6479FAC76}"/>
+    <hyperlink ref="B521" r:id="rId194" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{38D270BC-DEEE-468E-9B8A-ED46E9ECA658}"/>
+    <hyperlink ref="B522" r:id="rId195" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{FB8153D6-CBA3-48AF-8F83-1FB69AC94C53}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId196"/>
 </worksheet>
 </file>
--- a/excel_data/Website_mapping.xlsx
+++ b/excel_data/Website_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pixeltruth-my.sharepoint.com/personal/shubhankar_shukla_pixeltruth_com/Documents/Python_Codes/Testing_Code/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{AB1C9699-5AD3-4A07-AFFC-BDB08EC9955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F7FDD99-54D6-469F-83E1-487DA1A1E7E7}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{AB1C9699-5AD3-4A07-AFFC-BDB08EC9955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E493A1FE-1875-4ADC-B6A7-A3436D91854C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44ED9281-8F1E-4DBD-9F57-CE2FABFA19EC}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$307</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$494</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="627">
   <si>
     <t>website_url</t>
   </si>
@@ -411,9 +411,6 @@
     <t>https://drone-x66.com</t>
   </si>
   <si>
-    <t>https://heriiiwwvoonvusw.com</t>
-  </si>
-  <si>
     <t>https://ntpc-45light.com</t>
   </si>
   <si>
@@ -489,9 +486,6 @@
     <t>https://newsnacks88.long-msworldnetwork.com</t>
   </si>
   <si>
-    <t>https://zara-zar.netlify.app</t>
-  </si>
-  <si>
     <t>https://www.owslapumpingw-22.com</t>
   </si>
   <si>
@@ -519,9 +513,6 @@
     <t>https://www.bitmaine.live</t>
   </si>
   <si>
-    <t>https://intelligent823.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">Netherlands </t>
   </si>
   <si>
@@ -534,9 +525,6 @@
     <t xml:space="preserve">India </t>
   </si>
   <si>
-    <t xml:space="preserve">Germany </t>
-  </si>
-  <si>
     <t>Brazil</t>
   </si>
   <si>
@@ -1888,13 +1876,55 @@
   </si>
   <si>
     <t>Sweden</t>
+  </si>
+  <si>
+    <t>https://www.zonlasglk.com</t>
+  </si>
+  <si>
+    <t>https://www.jktyreffshd.com</t>
+  </si>
+  <si>
+    <t>https://safe-trade7.com</t>
+  </si>
+  <si>
+    <t>https://www.dairymilksales.com</t>
+  </si>
+  <si>
+    <t>https://ttnamaksaaltpukch.us.cc</t>
+  </si>
+  <si>
+    <t>https://www.hdappsjzbxbhsjjsbd.com</t>
+  </si>
+  <si>
+    <t>https://zara-zar-3.netlify.app</t>
+  </si>
+  <si>
+    <t>https://www.backtobasics1.ru</t>
+  </si>
+  <si>
+    <t>https://www.industrybenchmark.ru</t>
+  </si>
+  <si>
+    <t>https://vanillix-store22.com</t>
+  </si>
+  <si>
+    <t>https://www.morehighlights.ru</t>
+  </si>
+  <si>
+    <t>https://www.premiumquality1.ru</t>
+  </si>
+  <si>
+    <t>https://www.authenticreproduction.ru</t>
+  </si>
+  <si>
+    <t>Finland</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1910,13 +1940,51 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1943,10 +2011,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1954,8 +2023,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2268,7 +2356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0B11C6-F16C-4224-840C-73479EB5E1E4}">
-  <dimension ref="A1:C586"/>
+  <dimension ref="A1:C596"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="94.88671875" bestFit="1" customWidth="1"/>
@@ -2542,21 +2630,21 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>62</v>
@@ -2564,10 +2652,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>62</v>
@@ -2575,7 +2663,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>3</v>
@@ -2586,7 +2674,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>3</v>
@@ -2597,7 +2685,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>3</v>
@@ -2608,7 +2696,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>3</v>
@@ -2619,7 +2707,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>3</v>
@@ -2630,7 +2718,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>3</v>
@@ -2641,7 +2729,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>3</v>
@@ -2652,7 +2740,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>3</v>
@@ -2663,7 +2751,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>3</v>
@@ -2674,7 +2762,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>3</v>
@@ -2685,7 +2773,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>3</v>
@@ -2696,7 +2784,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>3</v>
@@ -2707,7 +2795,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>3</v>
@@ -2718,7 +2806,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>3</v>
@@ -2729,7 +2817,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>3</v>
@@ -2740,7 +2828,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>3</v>
@@ -2751,10 +2839,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>62</v>
@@ -2762,10 +2850,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>62</v>
@@ -2773,10 +2861,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>62</v>
@@ -2784,29 +2872,29 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>3</v>
@@ -2817,7 +2905,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>3</v>
@@ -2828,7 +2916,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>3</v>
@@ -2839,1030 +2927,1030 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>163</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>85</v>
+        <v>178</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>87</v>
+        <v>180</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>93</v>
+        <v>186</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>60</v>
+        <v>605</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>99</v>
+        <v>192</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>106</v>
+        <v>199</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>109</v>
+        <v>202</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>113</v>
+        <v>206</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>117</v>
+        <v>210</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>118</v>
+        <v>211</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>119</v>
+        <v>212</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>122</v>
+        <v>215</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>123</v>
+        <v>216</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>124</v>
+        <v>217</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>125</v>
+        <v>218</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>126</v>
+        <v>219</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>127</v>
+        <v>220</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>128</v>
+        <v>221</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>129</v>
+        <v>222</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>131</v>
+        <v>224</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>133</v>
+        <v>226</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>134</v>
+        <v>227</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>135</v>
+        <v>228</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>136</v>
+        <v>229</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>138</v>
+        <v>231</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>140</v>
+        <v>233</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>141</v>
+        <v>235</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>142</v>
+        <v>236</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>144</v>
+        <v>238</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>163</v>
+        <v>56</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>147</v>
+        <v>241</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>149</v>
+        <v>243</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>161</v>
+        <v>3</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>156</v>
+        <v>250</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>157</v>
+        <v>251</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>166</v>
+        <v>3</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>159</v>
+        <v>253</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>167</v>
+        <v>255</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>3</v>
@@ -3873,7 +3961,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>168</v>
+        <v>256</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>3</v>
@@ -3884,10 +3972,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>169</v>
+        <v>257</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>64</v>
@@ -3895,10 +3983,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>170</v>
+        <v>258</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>64</v>
@@ -3906,7 +3994,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>171</v>
+        <v>259</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>3</v>
@@ -3917,7 +4005,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>172</v>
+        <v>260</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>3</v>
@@ -3928,10 +4016,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>64</v>
@@ -3939,10 +4027,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>64</v>
@@ -3950,10 +4038,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>175</v>
+        <v>263</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>64</v>
@@ -3961,7 +4049,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>56</v>
@@ -3972,10 +4060,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>177</v>
+        <v>265</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>162</v>
+        <v>55</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>64</v>
@@ -3983,10 +4071,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>178</v>
+        <v>266</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>64</v>
@@ -3994,7 +4082,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>56</v>
@@ -4005,10 +4093,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>180</v>
+        <v>268</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>64</v>
@@ -4016,7 +4104,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>181</v>
+        <v>269</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>56</v>
@@ -4027,10 +4115,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>182</v>
+        <v>270</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>64</v>
@@ -4038,10 +4126,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>183</v>
+        <v>271</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>64</v>
@@ -4049,7 +4137,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>184</v>
+        <v>272</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>56</v>
@@ -4060,10 +4148,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>185</v>
+        <v>273</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>64</v>
@@ -4071,10 +4159,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>186</v>
+        <v>274</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>64</v>
@@ -4082,10 +4170,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>64</v>
@@ -4093,7 +4181,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>56</v>
@@ -4104,10 +4192,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>64</v>
@@ -4115,10 +4203,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>190</v>
+        <v>278</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>609</v>
+        <v>56</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>64</v>
@@ -4126,10 +4214,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>64</v>
@@ -4137,10 +4225,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>64</v>
@@ -4148,7 +4236,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>193</v>
+        <v>281</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>56</v>
@@ -4159,10 +4247,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>194</v>
+        <v>282</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>64</v>
@@ -4170,10 +4258,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>195</v>
+        <v>283</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>64</v>
@@ -4181,10 +4269,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>196</v>
+        <v>284</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>64</v>
@@ -4192,10 +4280,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>197</v>
+        <v>285</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>64</v>
@@ -4203,10 +4291,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>64</v>
@@ -4214,10 +4302,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>64</v>
@@ -4225,10 +4313,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>64</v>
@@ -4236,10 +4324,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>64</v>
@@ -4247,10 +4335,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>64</v>
@@ -4258,10 +4346,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>64</v>
@@ -4269,7 +4357,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>204</v>
+        <v>292</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>56</v>
@@ -4280,10 +4368,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>64</v>
@@ -4291,7 +4379,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>206</v>
+        <v>294</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>56</v>
@@ -4302,10 +4390,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>207</v>
+        <v>295</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>64</v>
@@ -4313,7 +4401,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>208</v>
+        <v>296</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>56</v>
@@ -4324,10 +4412,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>209</v>
+        <v>297</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>64</v>
@@ -4335,10 +4423,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>64</v>
@@ -4346,10 +4434,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>211</v>
+        <v>299</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>64</v>
@@ -4357,7 +4445,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>212</v>
+        <v>300</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>56</v>
@@ -4368,10 +4456,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>213</v>
+        <v>301</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>64</v>
@@ -4379,10 +4467,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>214</v>
+        <v>302</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>64</v>
@@ -4390,10 +4478,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>215</v>
+        <v>303</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>64</v>
@@ -4401,10 +4489,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>64</v>
@@ -4412,10 +4500,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>217</v>
+        <v>305</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>64</v>
@@ -4423,10 +4511,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>218</v>
+        <v>306</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>64</v>
@@ -4434,10 +4522,10 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>219</v>
+        <v>307</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>64</v>
@@ -4445,7 +4533,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>56</v>
@@ -4456,10 +4544,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>221</v>
+        <v>309</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>64</v>
@@ -4467,10 +4555,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>222</v>
+        <v>310</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>64</v>
@@ -4478,10 +4566,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>223</v>
+        <v>311</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>64</v>
@@ -4489,7 +4577,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>224</v>
+        <v>312</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>56</v>
@@ -4500,7 +4588,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>225</v>
+        <v>313</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>56</v>
@@ -4511,10 +4599,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>226</v>
+        <v>314</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>64</v>
@@ -4522,7 +4610,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>227</v>
+        <v>315</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>56</v>
@@ -4533,10 +4621,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>64</v>
@@ -4544,10 +4632,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>229</v>
+        <v>317</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>64</v>
@@ -4555,10 +4643,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>230</v>
+        <v>318</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>64</v>
@@ -4566,7 +4654,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>231</v>
+        <v>319</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>56</v>
@@ -4577,10 +4665,10 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>232</v>
+        <v>320</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>64</v>
@@ -4588,7 +4676,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>233</v>
+        <v>321</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>56</v>
@@ -4599,10 +4687,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>234</v>
+        <v>322</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>64</v>
@@ -4610,10 +4698,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
-        <v>235</v>
+        <v>323</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>64</v>
@@ -4621,7 +4709,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>236</v>
+        <v>324</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>3</v>
@@ -4632,7 +4720,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>237</v>
+        <v>325</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>3</v>
@@ -4643,10 +4731,10 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>64</v>
@@ -4654,7 +4742,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>239</v>
+        <v>327</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>56</v>
@@ -4665,10 +4753,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>240</v>
+        <v>328</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>64</v>
@@ -4676,10 +4764,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>64</v>
@@ -4687,10 +4775,10 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>242</v>
+        <v>330</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>64</v>
@@ -4698,10 +4786,10 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>243</v>
+        <v>331</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>64</v>
@@ -4709,10 +4797,10 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>244</v>
+        <v>332</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>64</v>
@@ -4720,10 +4808,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>245</v>
+        <v>333</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>64</v>
@@ -4731,10 +4819,10 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>246</v>
+        <v>334</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>64</v>
@@ -4742,10 +4830,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>247</v>
+        <v>335</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>64</v>
@@ -4753,7 +4841,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>56</v>
@@ -4764,10 +4852,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>249</v>
+        <v>337</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>64</v>
@@ -4775,10 +4863,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>250</v>
+        <v>338</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>64</v>
@@ -4786,10 +4874,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>251</v>
+        <v>339</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>64</v>
@@ -4797,10 +4885,10 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>252</v>
+        <v>340</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>64</v>
@@ -4808,10 +4896,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>64</v>
@@ -4819,10 +4907,10 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>254</v>
+        <v>342</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>64</v>
@@ -4830,10 +4918,10 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>255</v>
+        <v>343</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>64</v>
@@ -4841,10 +4929,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>256</v>
+        <v>344</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>64</v>
@@ -4852,10 +4940,10 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>257</v>
+        <v>345</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>64</v>
@@ -4863,10 +4951,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>258</v>
+        <v>346</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>64</v>
@@ -4874,7 +4962,7 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>259</v>
+        <v>347</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>3</v>
@@ -4885,10 +4973,10 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>260</v>
+        <v>348</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>64</v>
@@ -4896,10 +4984,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>261</v>
+        <v>349</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>64</v>
@@ -4907,7 +4995,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>262</v>
+        <v>350</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>56</v>
@@ -4918,10 +5006,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>263</v>
+        <v>351</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>64</v>
@@ -4929,7 +5017,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>264</v>
+        <v>352</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>3</v>
@@ -4940,10 +5028,10 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>265</v>
+        <v>353</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>64</v>
@@ -4951,10 +5039,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>266</v>
+        <v>354</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>64</v>
@@ -4962,10 +5050,10 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>267</v>
+        <v>355</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>64</v>
@@ -4973,7 +5061,7 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>268</v>
+        <v>356</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>56</v>
@@ -4984,10 +5072,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>269</v>
+        <v>357</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>64</v>
@@ -4995,10 +5083,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>270</v>
+        <v>358</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>64</v>
@@ -5006,10 +5094,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>271</v>
+        <v>359</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>64</v>
@@ -5017,10 +5105,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>272</v>
+        <v>360</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>64</v>
@@ -5028,10 +5116,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>273</v>
+        <v>361</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>64</v>
@@ -5039,10 +5127,10 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>64</v>
@@ -5050,7 +5138,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>56</v>
@@ -5061,10 +5149,10 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>276</v>
+        <v>364</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>64</v>
@@ -5072,7 +5160,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>56</v>
@@ -5083,7 +5171,7 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>278</v>
+        <v>366</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>55</v>
@@ -5094,10 +5182,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>279</v>
+        <v>367</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>64</v>
@@ -5105,10 +5193,10 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>280</v>
+        <v>368</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>64</v>
@@ -5116,10 +5204,10 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>281</v>
+        <v>369</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>64</v>
@@ -5127,7 +5215,7 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>282</v>
+        <v>370</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>56</v>
@@ -5138,10 +5226,10 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
-        <v>283</v>
+        <v>371</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>64</v>
@@ -5149,7 +5237,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>284</v>
+        <v>372</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>56</v>
@@ -5160,10 +5248,10 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>64</v>
@@ -5171,7 +5259,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>286</v>
+        <v>374</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>56</v>
@@ -5182,7 +5270,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>287</v>
+        <v>375</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>56</v>
@@ -5193,10 +5281,10 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>288</v>
+        <v>376</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>64</v>
@@ -5204,10 +5292,10 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>289</v>
+        <v>377</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>64</v>
@@ -5215,7 +5303,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>290</v>
+        <v>378</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>56</v>
@@ -5226,10 +5314,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
-        <v>291</v>
+        <v>379</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>55</v>
+        <v>606</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>64</v>
@@ -5237,7 +5325,7 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>56</v>
@@ -5248,7 +5336,7 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>293</v>
+        <v>381</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>56</v>
@@ -5259,7 +5347,7 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>294</v>
+        <v>382</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>56</v>
@@ -5270,10 +5358,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
-        <v>295</v>
+        <v>383</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>64</v>
@@ -5281,10 +5369,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>296</v>
+        <v>384</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>64</v>
@@ -5292,7 +5380,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>297</v>
+        <v>385</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>56</v>
@@ -5303,10 +5391,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>298</v>
+        <v>386</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>64</v>
@@ -5314,7 +5402,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
-        <v>299</v>
+        <v>387</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>56</v>
@@ -5325,10 +5413,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>300</v>
+        <v>388</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>56</v>
+        <v>607</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>64</v>
@@ -5336,10 +5424,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
-        <v>301</v>
+        <v>389</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>64</v>
@@ -5347,10 +5435,10 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>302</v>
+        <v>390</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>64</v>
@@ -5358,10 +5446,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
-        <v>303</v>
+        <v>391</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>64</v>
@@ -5369,10 +5457,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>304</v>
+        <v>392</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>64</v>
@@ -5380,10 +5468,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
-        <v>305</v>
+        <v>393</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>64</v>
@@ -5391,10 +5479,10 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>306</v>
+        <v>394</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>64</v>
@@ -5402,7 +5490,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>307</v>
+        <v>395</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>56</v>
@@ -5413,10 +5501,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>308</v>
+        <v>396</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>64</v>
@@ -5424,10 +5512,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>309</v>
+        <v>397</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>64</v>
@@ -5435,7 +5523,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>310</v>
+        <v>398</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>3</v>
@@ -5446,10 +5534,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>311</v>
+        <v>399</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>64</v>
@@ -5457,7 +5545,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>312</v>
+        <v>400</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>56</v>
@@ -5468,7 +5556,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>313</v>
+        <v>401</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>56</v>
@@ -5479,10 +5567,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>314</v>
+        <v>402</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>64</v>
@@ -5490,7 +5578,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>315</v>
+        <v>403</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>56</v>
@@ -5501,10 +5589,10 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>316</v>
+        <v>404</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>64</v>
@@ -5512,7 +5600,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>317</v>
+        <v>405</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>56</v>
@@ -5523,10 +5611,10 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>318</v>
+        <v>406</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>64</v>
@@ -5534,7 +5622,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>319</v>
+        <v>407</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>56</v>
@@ -5545,7 +5633,7 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>320</v>
+        <v>408</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>56</v>
@@ -5556,10 +5644,10 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
-        <v>321</v>
+        <v>409</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>64</v>
@@ -5567,10 +5655,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>64</v>
@@ -5578,10 +5666,10 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
-        <v>323</v>
+        <v>411</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>64</v>
@@ -5589,10 +5677,10 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>324</v>
+        <v>412</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>64</v>
@@ -5600,7 +5688,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
-        <v>325</v>
+        <v>413</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>56</v>
@@ -5611,10 +5699,10 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>326</v>
+        <v>414</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>64</v>
@@ -5622,10 +5710,10 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
-        <v>327</v>
+        <v>415</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>64</v>
@@ -5633,10 +5721,10 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>328</v>
+        <v>416</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>64</v>
@@ -5644,10 +5732,10 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
-        <v>329</v>
+        <v>417</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>64</v>
@@ -5655,10 +5743,10 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>330</v>
+        <v>418</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>64</v>
@@ -5666,7 +5754,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
-        <v>331</v>
+        <v>419</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>56</v>
@@ -5677,10 +5765,10 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>332</v>
+        <v>420</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>64</v>
@@ -5688,10 +5776,10 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>333</v>
+        <v>421</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>64</v>
@@ -5699,10 +5787,10 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>334</v>
+        <v>422</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>64</v>
@@ -5710,10 +5798,10 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>335</v>
+        <v>423</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>64</v>
@@ -5721,10 +5809,10 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>336</v>
+        <v>424</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>64</v>
@@ -5732,10 +5820,10 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
-        <v>337</v>
+        <v>425</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>64</v>
@@ -5743,10 +5831,10 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>338</v>
+        <v>426</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>64</v>
@@ -5754,10 +5842,10 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
-        <v>339</v>
+        <v>427</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>64</v>
@@ -5765,10 +5853,10 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>340</v>
+        <v>428</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>64</v>
@@ -5776,10 +5864,10 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>341</v>
+        <v>429</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>64</v>
@@ -5787,10 +5875,10 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>342</v>
+        <v>430</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>64</v>
@@ -5798,10 +5886,10 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
-        <v>343</v>
+        <v>431</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>64</v>
@@ -5809,10 +5897,10 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>344</v>
+        <v>432</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>55</v>
+        <v>608</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>64</v>
@@ -5820,10 +5908,10 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
-        <v>345</v>
+        <v>433</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>55</v>
+        <v>609</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>64</v>
@@ -5831,10 +5919,10 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>346</v>
+        <v>434</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>64</v>
@@ -5842,10 +5930,10 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>347</v>
+        <v>435</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>64</v>
@@ -5853,10 +5941,10 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>348</v>
+        <v>436</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>64</v>
@@ -5864,10 +5952,10 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>349</v>
+        <v>437</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>64</v>
@@ -5875,10 +5963,10 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>350</v>
+        <v>438</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>64</v>
@@ -5886,10 +5974,10 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>351</v>
+        <v>439</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>3</v>
+        <v>608</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>64</v>
@@ -5897,7 +5985,7 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>352</v>
+        <v>440</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>56</v>
@@ -5908,10 +5996,10 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>3</v>
+        <v>610</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>64</v>
@@ -5919,7 +6007,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>354</v>
+        <v>442</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>56</v>
@@ -5930,10 +6018,10 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
-        <v>355</v>
+        <v>443</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>64</v>
@@ -5941,10 +6029,10 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>356</v>
+        <v>444</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>64</v>
@@ -5952,10 +6040,10 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
-        <v>357</v>
+        <v>445</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>64</v>
@@ -5963,10 +6051,10 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>358</v>
+        <v>446</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>64</v>
@@ -5974,10 +6062,10 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
-        <v>359</v>
+        <v>447</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>64</v>
@@ -5985,7 +6073,7 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>360</v>
+        <v>448</v>
       </c>
       <c r="B338" s="1" t="s">
         <v>56</v>
@@ -5996,10 +6084,10 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
-        <v>361</v>
+        <v>449</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>64</v>
@@ -6007,10 +6095,10 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>362</v>
+        <v>450</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>64</v>
@@ -6018,10 +6106,10 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
-        <v>363</v>
+        <v>451</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>64</v>
@@ -6029,10 +6117,10 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>364</v>
+        <v>452</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>64</v>
@@ -6040,10 +6128,10 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
-        <v>365</v>
+        <v>453</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>64</v>
@@ -6051,10 +6139,10 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>366</v>
+        <v>454</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>64</v>
@@ -6062,7 +6150,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
-        <v>367</v>
+        <v>455</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>56</v>
@@ -6073,10 +6161,10 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>368</v>
+        <v>456</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>64</v>
@@ -6084,7 +6172,7 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
-        <v>369</v>
+        <v>457</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>56</v>
@@ -6095,7 +6183,7 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>370</v>
+        <v>458</v>
       </c>
       <c r="B348" s="1" t="s">
         <v>55</v>
@@ -6106,7 +6194,7 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
-        <v>371</v>
+        <v>459</v>
       </c>
       <c r="B349" s="1" t="s">
         <v>56</v>
@@ -6117,10 +6205,10 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>372</v>
+        <v>460</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>64</v>
@@ -6128,10 +6216,10 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
-        <v>373</v>
+        <v>461</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>64</v>
@@ -6139,10 +6227,10 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>374</v>
+        <v>462</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>64</v>
@@ -6150,7 +6238,7 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
-        <v>375</v>
+        <v>463</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>55</v>
@@ -6161,10 +6249,10 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>376</v>
+        <v>464</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>64</v>
@@ -6172,7 +6260,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
-        <v>377</v>
+        <v>465</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>55</v>
@@ -6183,10 +6271,10 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>378</v>
+        <v>466</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>64</v>
@@ -6194,10 +6282,10 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
-        <v>379</v>
+        <v>467</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>64</v>
@@ -6205,7 +6293,7 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>380</v>
+        <v>468</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>3</v>
@@ -6216,7 +6304,7 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
-        <v>381</v>
+        <v>469</v>
       </c>
       <c r="B359" s="1" t="s">
         <v>3</v>
@@ -6227,7 +6315,7 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>382</v>
+        <v>470</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>56</v>
@@ -6238,10 +6326,10 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
-        <v>383</v>
+        <v>471</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>610</v>
+        <v>56</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>64</v>
@@ -6249,10 +6337,10 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>384</v>
+        <v>472</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>64</v>
@@ -6260,7 +6348,7 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
-        <v>385</v>
+        <v>473</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>56</v>
@@ -6271,10 +6359,10 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>386</v>
+        <v>474</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>64</v>
@@ -6282,7 +6370,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
-        <v>387</v>
+        <v>475</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>56</v>
@@ -6293,7 +6381,7 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>388</v>
+        <v>476</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>55</v>
@@ -6304,10 +6392,10 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
-        <v>389</v>
+        <v>477</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>64</v>
@@ -6315,10 +6403,10 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>390</v>
+        <v>478</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>64</v>
@@ -6326,7 +6414,7 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
-        <v>391</v>
+        <v>479</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>56</v>
@@ -6337,10 +6425,10 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>392</v>
+        <v>480</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>611</v>
+        <v>54</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>64</v>
@@ -6348,10 +6436,10 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
-        <v>393</v>
+        <v>481</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>64</v>
@@ -6359,10 +6447,10 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>394</v>
+        <v>482</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>64</v>
@@ -6370,10 +6458,10 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
-        <v>395</v>
+        <v>483</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>64</v>
@@ -6381,10 +6469,10 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>396</v>
+        <v>484</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>64</v>
@@ -6392,10 +6480,10 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
-        <v>397</v>
+        <v>485</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>64</v>
@@ -6403,7 +6491,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>398</v>
+        <v>486</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>58</v>
@@ -6414,10 +6502,10 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
-        <v>399</v>
+        <v>487</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>64</v>
@@ -6425,10 +6513,10 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>400</v>
+        <v>488</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>64</v>
@@ -6436,10 +6524,10 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
-        <v>401</v>
+        <v>489</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>64</v>
@@ -6447,10 +6535,10 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>402</v>
+        <v>490</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>64</v>
@@ -6458,10 +6546,10 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
-        <v>403</v>
+        <v>491</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>64</v>
@@ -6469,7 +6557,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>404</v>
+        <v>492</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>56</v>
@@ -6480,10 +6568,10 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
-        <v>405</v>
+        <v>493</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>64</v>
@@ -6491,10 +6579,10 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>406</v>
+        <v>494</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>64</v>
@@ -6502,10 +6590,10 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
-        <v>407</v>
+        <v>495</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>64</v>
@@ -6513,10 +6601,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>408</v>
+        <v>496</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>64</v>
@@ -6524,10 +6612,10 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
-        <v>409</v>
+        <v>497</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>64</v>
@@ -6535,10 +6623,10 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>410</v>
+        <v>498</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>64</v>
@@ -6546,10 +6634,10 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
-        <v>411</v>
+        <v>499</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>64</v>
@@ -6557,7 +6645,7 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>412</v>
+        <v>500</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>56</v>
@@ -6568,7 +6656,7 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
-        <v>413</v>
+        <v>501</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>55</v>
@@ -6579,10 +6667,10 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>414</v>
+        <v>502</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>64</v>
@@ -6590,10 +6678,10 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
-        <v>415</v>
+        <v>503</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>64</v>
@@ -6601,10 +6689,10 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>416</v>
+        <v>504</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>64</v>
@@ -6612,10 +6700,10 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
-        <v>417</v>
+        <v>505</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>56</v>
+        <v>611</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>64</v>
@@ -6623,10 +6711,10 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>418</v>
+        <v>506</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>64</v>
@@ -6634,7 +6722,7 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
-        <v>419</v>
+        <v>507</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>55</v>
@@ -6645,7 +6733,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>420</v>
+        <v>508</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>55</v>
@@ -6656,10 +6744,10 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
-        <v>421</v>
+        <v>509</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>64</v>
@@ -6667,10 +6755,10 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>422</v>
+        <v>510</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>64</v>
@@ -6678,10 +6766,10 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
-        <v>423</v>
+        <v>511</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>64</v>
@@ -6689,10 +6777,10 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>424</v>
+        <v>512</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>64</v>
@@ -6700,10 +6788,10 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
-        <v>425</v>
+        <v>513</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>64</v>
@@ -6711,7 +6799,7 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>426</v>
+        <v>514</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>55</v>
@@ -6722,10 +6810,10 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
-        <v>427</v>
+        <v>515</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>64</v>
@@ -6733,10 +6821,10 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>428</v>
+        <v>516</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>64</v>
@@ -6744,10 +6832,10 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
-        <v>429</v>
+        <v>517</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>64</v>
@@ -6755,10 +6843,10 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>430</v>
+        <v>518</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>55</v>
+        <v>608</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>64</v>
@@ -6766,10 +6854,10 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
-        <v>431</v>
+        <v>519</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>64</v>
@@ -6777,10 +6865,10 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>432</v>
+        <v>520</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>55</v>
+        <v>609</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>64</v>
@@ -6788,10 +6876,10 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
-        <v>433</v>
+        <v>521</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>64</v>
@@ -6799,10 +6887,10 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>434</v>
+        <v>522</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>55</v>
+        <v>609</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>64</v>
@@ -6810,10 +6898,10 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
-        <v>435</v>
+        <v>523</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>55</v>
+        <v>609</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>64</v>
@@ -6821,10 +6909,10 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>436</v>
+        <v>524</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>612</v>
+        <v>161</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>64</v>
@@ -6832,10 +6920,10 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
-        <v>437</v>
+        <v>525</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>64</v>
@@ -6843,10 +6931,10 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>438</v>
+        <v>526</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>64</v>
@@ -6854,10 +6942,10 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
-        <v>439</v>
+        <v>527</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>64</v>
@@ -6865,7 +6953,7 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>440</v>
+        <v>528</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>58</v>
@@ -6876,10 +6964,10 @@
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
-        <v>441</v>
+        <v>529</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>64</v>
@@ -6887,10 +6975,10 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>442</v>
+        <v>530</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>58</v>
+        <v>606</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>64</v>
@@ -6898,10 +6986,10 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
-        <v>443</v>
+        <v>531</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>612</v>
+        <v>56</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>64</v>
@@ -6909,10 +6997,10 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>444</v>
+        <v>532</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>64</v>
@@ -6920,10 +7008,10 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
-        <v>445</v>
+        <v>533</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>614</v>
+        <v>3</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>64</v>
@@ -6931,10 +7019,10 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>446</v>
+        <v>534</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>64</v>
@@ -6942,10 +7030,10 @@
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
-        <v>447</v>
+        <v>535</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>64</v>
@@ -6953,10 +7041,10 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>448</v>
+        <v>536</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>64</v>
@@ -6964,10 +7052,10 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
-        <v>449</v>
+        <v>537</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>64</v>
@@ -6975,7 +7063,7 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>450</v>
+        <v>538</v>
       </c>
       <c r="B428" s="1" t="s">
         <v>56</v>
@@ -6986,10 +7074,10 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
-        <v>451</v>
+        <v>539</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>64</v>
@@ -6997,10 +7085,10 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>452</v>
+        <v>540</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>64</v>
@@ -7008,10 +7096,10 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
-        <v>453</v>
+        <v>541</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>64</v>
@@ -7019,10 +7107,10 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>454</v>
+        <v>542</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>64</v>
@@ -7030,7 +7118,7 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
-        <v>455</v>
+        <v>543</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>58</v>
@@ -7041,7 +7129,7 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>456</v>
+        <v>544</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>58</v>
@@ -7052,10 +7140,10 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
-        <v>457</v>
+        <v>545</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>64</v>
@@ -7063,10 +7151,10 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>458</v>
+        <v>546</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>64</v>
@@ -7074,10 +7162,10 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
-        <v>459</v>
+        <v>547</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>64</v>
@@ -7085,10 +7173,10 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>460</v>
+        <v>548</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>64</v>
@@ -7096,10 +7184,10 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
-        <v>461</v>
+        <v>549</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>64</v>
@@ -7107,10 +7195,10 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>462</v>
+        <v>550</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>64</v>
@@ -7118,10 +7206,10 @@
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
-        <v>463</v>
+        <v>551</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>64</v>
@@ -7129,7 +7217,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>464</v>
+        <v>552</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>55</v>
@@ -7140,7 +7228,7 @@
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
-        <v>465</v>
+        <v>553</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>55</v>
@@ -7151,7 +7239,7 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>466</v>
+        <v>554</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>55</v>
@@ -7162,10 +7250,10 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
-        <v>467</v>
+        <v>555</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>64</v>
@@ -7173,10 +7261,10 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>468</v>
+        <v>556</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>64</v>
@@ -7184,7 +7272,7 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
-        <v>469</v>
+        <v>557</v>
       </c>
       <c r="B447" s="1" t="s">
         <v>55</v>
@@ -7195,10 +7283,10 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>470</v>
+        <v>558</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>64</v>
@@ -7206,10 +7294,10 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
-        <v>471</v>
+        <v>559</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>64</v>
@@ -7217,10 +7305,10 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>472</v>
+        <v>560</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>3</v>
+        <v>612</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>64</v>
@@ -7228,7 +7316,7 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
-        <v>473</v>
+        <v>561</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>3</v>
@@ -7239,7 +7327,7 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>474</v>
+        <v>562</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>56</v>
@@ -7250,10 +7338,10 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
-        <v>475</v>
+        <v>563</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>64</v>
@@ -7261,10 +7349,10 @@
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>476</v>
+        <v>564</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>64</v>
@@ -7272,10 +7360,10 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
-        <v>477</v>
+        <v>565</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>64</v>
@@ -7283,7 +7371,7 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>478</v>
+        <v>566</v>
       </c>
       <c r="B456" s="1" t="s">
         <v>3</v>
@@ -7294,7 +7382,7 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
-        <v>479</v>
+        <v>567</v>
       </c>
       <c r="B457" s="1" t="s">
         <v>56</v>
@@ -7305,10 +7393,10 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>480</v>
+        <v>568</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>64</v>
@@ -7316,10 +7404,10 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
-        <v>481</v>
+        <v>569</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>64</v>
@@ -7327,10 +7415,10 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>482</v>
+        <v>570</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>64</v>
@@ -7338,10 +7426,10 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
-        <v>483</v>
+        <v>571</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>64</v>
@@ -7349,10 +7437,10 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>484</v>
+        <v>572</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>64</v>
@@ -7360,10 +7448,10 @@
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
-        <v>485</v>
+        <v>573</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>64</v>
@@ -7371,7 +7459,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>486</v>
+        <v>574</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>56</v>
@@ -7382,10 +7470,10 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
-        <v>487</v>
+        <v>575</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>64</v>
@@ -7393,7 +7481,7 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>488</v>
+        <v>576</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>56</v>
@@ -7404,7 +7492,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
-        <v>489</v>
+        <v>577</v>
       </c>
       <c r="B467" s="1" t="s">
         <v>56</v>
@@ -7415,10 +7503,10 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>490</v>
+        <v>578</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>64</v>
@@ -7426,10 +7514,10 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
-        <v>491</v>
+        <v>579</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>64</v>
@@ -7437,7 +7525,7 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>492</v>
+        <v>580</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>56</v>
@@ -7448,10 +7536,10 @@
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
-        <v>493</v>
+        <v>581</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>64</v>
@@ -7459,10 +7547,10 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>494</v>
+        <v>582</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>64</v>
@@ -7470,10 +7558,10 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
-        <v>495</v>
+        <v>583</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>64</v>
@@ -7481,7 +7569,7 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>496</v>
+        <v>584</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>56</v>
@@ -7492,10 +7580,10 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
-        <v>497</v>
+        <v>585</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>64</v>
@@ -7503,10 +7591,10 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>498</v>
+        <v>586</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>64</v>
@@ -7514,10 +7602,10 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
-        <v>499</v>
+        <v>587</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>64</v>
@@ -7525,10 +7613,10 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>500</v>
+        <v>588</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>64</v>
@@ -7536,7 +7624,7 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
-        <v>501</v>
+        <v>589</v>
       </c>
       <c r="B479" s="1" t="s">
         <v>55</v>
@@ -7547,10 +7635,10 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>502</v>
+        <v>590</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>64</v>
@@ -7558,10 +7646,10 @@
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
-        <v>503</v>
+        <v>591</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>64</v>
@@ -7569,10 +7657,10 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>504</v>
+        <v>592</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>64</v>
@@ -7580,7 +7668,7 @@
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
-        <v>505</v>
+        <v>593</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>55</v>
@@ -7591,10 +7679,10 @@
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>506</v>
+        <v>594</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>64</v>
@@ -7602,10 +7690,10 @@
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
-        <v>507</v>
+        <v>595</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>64</v>
@@ -7613,10 +7701,10 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>508</v>
+        <v>596</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>64</v>
@@ -7624,10 +7712,10 @@
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
-        <v>509</v>
+        <v>597</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>615</v>
+        <v>58</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>64</v>
@@ -7635,7 +7723,7 @@
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>510</v>
+        <v>598</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>55</v>
@@ -7646,10 +7734,10 @@
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
-        <v>511</v>
+        <v>599</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>64</v>
@@ -7657,7 +7745,7 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>512</v>
+        <v>600</v>
       </c>
       <c r="B490" s="1" t="s">
         <v>55</v>
@@ -7668,7 +7756,7 @@
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
-        <v>513</v>
+        <v>601</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>55</v>
@@ -7679,7 +7767,7 @@
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>514</v>
+        <v>602</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>55</v>
@@ -7690,10 +7778,10 @@
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
-        <v>515</v>
+        <v>603</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>64</v>
@@ -7701,7 +7789,7 @@
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>516</v>
+        <v>604</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>56</v>
@@ -7711,1214 +7799,1325 @@
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A495" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="B495" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C495" s="1" t="s">
-        <v>64</v>
+      <c r="A495" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B495" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C495" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A496" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="B496" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>64</v>
+      <c r="A496" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B496" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C496" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A497" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="B497" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C497" s="1" t="s">
-        <v>64</v>
+      <c r="A497" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B497" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C497" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A498" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="B498" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C498" s="1" t="s">
-        <v>64</v>
+      <c r="A498" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B498" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C498" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A499" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="B499" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C499" s="1" t="s">
-        <v>64</v>
+      <c r="A499" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B499" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A500" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="B500" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="C500" s="1" t="s">
-        <v>64</v>
+      <c r="A500" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B500" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C500" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A501" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="B501" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C501" s="1" t="s">
-        <v>64</v>
+      <c r="A501" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B501" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C501" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A502" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="B502" s="1" t="s">
+      <c r="A502" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B502" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C502" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A503" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B503" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C503" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A504" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B504" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C504" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A505" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B505" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A506" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B506" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C506" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A507" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B507" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C507" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A508" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B508" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C508" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A509" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B509" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C509" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A510" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B510" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C510" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A511" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B511" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C511" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A512" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B512" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C512" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A513" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B513" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C513" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A514" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B514" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C514" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A515" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B515" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C515" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A516" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B516" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C516" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A517" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B517" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C517" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A518" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B518" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C518" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A519" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B519" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C519" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A520" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B520" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C520" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A521" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B521" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A522" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B522" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C522" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A523" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B523" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A524" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B524" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C524" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A525" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B525" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C525" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A526" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B526" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C526" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A527" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B527" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C527" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A528" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B528" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A529" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B529" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A530" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B530" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A531" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B531" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A532" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B532" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A533" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B533" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A534" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B534" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A535" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B535" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A536" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B536" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A537" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B537" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A538" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B538" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C538" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A539" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B539" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C539" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A540" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B540" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C540" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A541" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B541" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C541" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A542" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B542" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C542" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A543" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B543" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A544" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B544" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C544" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A545" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B545" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C545" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A546" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B546" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C546" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A547" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B547" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A548" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B548" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C548" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A549" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B549" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C549" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A550" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B550" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C550" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A551" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B551" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C551" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A552" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B552" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C552" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A553" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B553" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C553" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A554" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B554" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C554" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A555" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B555" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A556" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B556" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C556" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A557" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B557" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A558" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B558" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C558" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A559" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B559" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A560" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B560" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C560" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A561" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B561" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C561" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A562" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B562" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C562" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A563" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B563" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A564" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B564" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A565" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B565" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A566" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B566" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A567" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B567" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A568" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B568" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C568" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A569" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B569" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A570" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B570" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A571" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B571" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A572" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B572" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C572" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A573" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B573" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A574" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B574" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C574" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A575" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B575" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A576" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B576" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A577" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B577" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A578" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B578" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C578" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A579" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B579" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C579" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A580" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B580" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C580" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A581" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B581" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A582" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B582" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C582" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A583" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B583" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C583" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A584" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="C502" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A503" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="B503" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A504" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="B504" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="C504" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A505" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="B505" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="C505" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A506" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="B506" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C506" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A507" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="B507" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="C507" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A508" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="B508" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C508" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A509" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="B509" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C509" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A510" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="B510" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C510" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A511" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="B511" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C511" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A512" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="B512" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="C512" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A513" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="B513" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C513" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A514" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="B514" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C514" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A515" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="B515" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C515" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A516" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B516" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C516" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A517" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="B517" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C517" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A518" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="B518" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C518" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A519" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="B519" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C519" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A520" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="B520" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C520" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A521" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="B521" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C521" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A522" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="B522" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C522" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A523" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="B523" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A524" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="B524" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A525" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="B525" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C525" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A526" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="B526" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C526" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A527" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="B527" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C527" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A528" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="B528" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C528" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A529" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="B529" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C529" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A530" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="B530" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C530" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A531" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="B531" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C531" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A532" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B532" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C532" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A533" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="B533" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C533" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A534" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="B534" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C534" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A535" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="B535" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C535" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A536" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="B536" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C536" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A537" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="B537" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C537" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A538" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="B538" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C538" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A539" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="B539" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C539" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A540" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="B540" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C540" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A541" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="B541" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C541" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A542" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="B542" s="1" t="s">
+      <c r="B584" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C584" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A585" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B585" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A586" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B586" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C586" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A587" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="C542" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A543" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="B543" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C543" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A544" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="B544" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C544" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A545" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="B545" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C545" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A546" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="B546" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C546" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A547" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="B547" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C547" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A548" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="B548" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C548" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A549" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="B549" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C549" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A550" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="B550" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C550" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A551" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="B551" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C551" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A552" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="B552" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C552" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A553" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="B553" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C553" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A554" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B554" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C554" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A555" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="B555" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C555" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A556" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="B556" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C556" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A557" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="B557" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C557" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A558" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="B558" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C558" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A559" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="B559" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C559" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A560" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="B560" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C560" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A561" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="B561" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C561" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A562" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="B562" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C562" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A563" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="B563" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C563" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A564" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="B564" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C564" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A565" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="B565" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C565" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A566" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="B566" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C566" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A567" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="B567" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C567" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A568" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="B568" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C568" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A569" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="B569" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C569" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A570" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="B570" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C570" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A571" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="B571" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C571" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A572" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="B572" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C572" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A573" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="B573" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C573" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A574" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="B574" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C574" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A575" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="B575" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C575" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A576" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="B576" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C576" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A577" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="B577" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C577" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A578" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="B578" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C578" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A579" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="B579" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C579" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A580" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="B580" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C580" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A581" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="B581" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C581" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A582" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="B582" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C582" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A583" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="B583" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C583" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A584" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="B584" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C584" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A585" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="B585" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C585" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A586" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="B586" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C586" s="1" t="s">
-        <v>64</v>
+      <c r="B587" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A588" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B588" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="C588" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A589" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B589" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C589" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A590" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="B590" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C590" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A591" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B591" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C591" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A592" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B592" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A593" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="B593" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A594" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B594" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C594" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A595" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B595" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C595" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A596" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B596" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C596" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C494" xr:uid="{BD0B11C6-F16C-4224-840C-73479EB5E1E4}"/>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{1742F09F-6D1A-4CDA-BB14-8BC64089397B}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{BD7EE5DE-FD8F-4CCD-BE03-23430A5C36F0}"/>
-    <hyperlink ref="B100" r:id="rId3" display="https://myip.ms/view/countries/USA/Internet_Usage_Statistics_USA.html" xr:uid="{34B5AA4C-4000-4954-B025-EEB8547EDF72}"/>
-    <hyperlink ref="A146" r:id="rId4" display="https://bigwinoffer.com.tr/" xr:uid="{98C766A6-866D-407A-A703-A304F2271943}"/>
-    <hyperlink ref="A147" r:id="rId5" xr:uid="{BD339C4C-F3D6-4339-914A-629492FF0313}"/>
-    <hyperlink ref="A152" r:id="rId6" xr:uid="{170DE5A7-BE41-4BD8-A8E7-CDE00238162F}"/>
-    <hyperlink ref="A153" r:id="rId7" xr:uid="{8A69FD07-0DF7-4EDE-9E5F-DC8F506B570E}"/>
-    <hyperlink ref="A163" r:id="rId8" xr:uid="{C553ACF4-3781-492E-BD5B-E824E9FF5C3E}"/>
-    <hyperlink ref="A166" r:id="rId9" xr:uid="{5D8F5B3F-17AE-4DF2-AD5E-9613E48F65E0}"/>
-    <hyperlink ref="A167" r:id="rId10" xr:uid="{D4AF918A-E899-4C6A-8824-5157F7D247B1}"/>
-    <hyperlink ref="A168" r:id="rId11" xr:uid="{F554D08F-0620-410D-A203-70DF8D4BD8A7}"/>
-    <hyperlink ref="A169" r:id="rId12" xr:uid="{232A2CD1-646E-4812-AE7D-13AB9A95D539}"/>
-    <hyperlink ref="A175" r:id="rId13" xr:uid="{C70A6BA3-3B94-42A0-B1AC-0B1981DA4DBB}"/>
-    <hyperlink ref="A188" r:id="rId14" xr:uid="{4F7A26AB-5F2B-4F29-B785-A4AEAD3256FD}"/>
-    <hyperlink ref="A189" r:id="rId15" xr:uid="{6D4DCC2E-630E-4ECF-8711-194F3FF9F36B}"/>
-    <hyperlink ref="A190" r:id="rId16" xr:uid="{CDAAF86A-C222-4A2B-B805-935CDD2492ED}"/>
-    <hyperlink ref="A192" r:id="rId17" display="https://meeshosalemeesho.store/" xr:uid="{407D2E40-C398-454D-9CE1-60A818B99B53}"/>
-    <hyperlink ref="A193" r:id="rId18" xr:uid="{A9918901-20E2-44D9-A6E5-21293D85876A}"/>
-    <hyperlink ref="A196" r:id="rId19" display="https://me-esho.netlify.app/" xr:uid="{F642A9F9-6008-4571-8ADA-709AA1672F98}"/>
-    <hyperlink ref="A197" r:id="rId20" xr:uid="{6513F9F0-7F4F-4843-A74A-0CB4874E0599}"/>
-    <hyperlink ref="A201" r:id="rId21" xr:uid="{F62E82C0-1B21-4251-BCAC-E0323EB23981}"/>
-    <hyperlink ref="A218" r:id="rId22" xr:uid="{7E52A3D5-33B5-4025-8474-2362A1C0FC9C}"/>
-    <hyperlink ref="A273" r:id="rId23" xr:uid="{4EA6B28F-57D3-40EB-A1A6-6C25D45AFF06}"/>
-    <hyperlink ref="A274" r:id="rId24" xr:uid="{B1A637C6-B83A-4431-970F-AE1D781F7510}"/>
-    <hyperlink ref="A275" r:id="rId25" xr:uid="{45682F5A-A237-45C3-96BB-F43A9439BDD5}"/>
-    <hyperlink ref="A276" r:id="rId26" xr:uid="{DB9A5180-8F2B-419E-8B26-86E9E68F0555}"/>
-    <hyperlink ref="A279" r:id="rId27" xr:uid="{B08E4BBD-D132-42C5-83C7-A35E01B01762}"/>
-    <hyperlink ref="A326" r:id="rId28" xr:uid="{D442933B-7EFF-4840-B6C6-36CC50121D06}"/>
-    <hyperlink ref="A327" r:id="rId29" xr:uid="{3F8D3800-3C6B-417A-9353-AE42F2A981AC}"/>
-    <hyperlink ref="A330" r:id="rId30" xr:uid="{C1805AF2-D1A1-4825-AF0F-2AF3ED072F02}"/>
-    <hyperlink ref="A333" r:id="rId31" xr:uid="{8204F786-BE48-4C16-BEB2-D1D959C2BB89}"/>
-    <hyperlink ref="A337" r:id="rId32" xr:uid="{9719F79F-2C88-4611-894E-3ECDADE8E57E}"/>
-    <hyperlink ref="A338" r:id="rId33" xr:uid="{1A723955-4FB1-4C35-AFDE-721A2275A546}"/>
-    <hyperlink ref="A339" r:id="rId34" xr:uid="{130E758A-3D4D-419E-8236-C07151C99AD2}"/>
-    <hyperlink ref="A340" r:id="rId35" xr:uid="{77192F96-45E6-42AA-B872-F6A0E0472031}"/>
-    <hyperlink ref="A344" r:id="rId36" xr:uid="{4F1D3828-0567-48C5-A987-84FFE637D95C}"/>
-    <hyperlink ref="A345" r:id="rId37" xr:uid="{3D67BDCE-1DA2-447A-BA58-554F134B7C00}"/>
-    <hyperlink ref="A346" r:id="rId38" xr:uid="{C12B6E0A-9823-4426-B0FE-8BBFEA3835EB}"/>
-    <hyperlink ref="A349" r:id="rId39" xr:uid="{F82145D5-63AF-4BC4-A3A3-C7EFC7B659E2}"/>
-    <hyperlink ref="A350" r:id="rId40" display="https://yellow-emu-733093.hostingersite.com/" xr:uid="{498B7977-1C68-44F8-A612-C3FCDC6308DC}"/>
-    <hyperlink ref="A354" r:id="rId41" xr:uid="{AF1BAF98-1EA5-4501-8822-F9A4AEC9886A}"/>
-    <hyperlink ref="A355" r:id="rId42" xr:uid="{F24BB87D-B1D5-49AE-8CAF-22A7ED07F7EE}"/>
-    <hyperlink ref="A356" r:id="rId43" xr:uid="{F27DE639-C332-4C51-8BA7-BA96150BD1F9}"/>
-    <hyperlink ref="A361" r:id="rId44" xr:uid="{6B755285-6191-481C-8905-64260133B3ED}"/>
-    <hyperlink ref="A366" r:id="rId45" xr:uid="{39918188-4D6A-4CF0-A2EE-121BE4F7ACA0}"/>
-    <hyperlink ref="A367" r:id="rId46" xr:uid="{3F1A5270-1234-4BEE-96EC-59639650FCD1}"/>
-    <hyperlink ref="A370" r:id="rId47" xr:uid="{0F0E5898-D3C9-44F1-B399-4B5E1123A6FA}"/>
-    <hyperlink ref="A371" r:id="rId48" xr:uid="{86983A0A-DF54-4D82-8CFF-9D09324C1C04}"/>
-    <hyperlink ref="A372" r:id="rId49" display="https://flipcart-limited-offer.myshopify.com/" xr:uid="{2FB3D63C-F210-4F00-BE43-F63709ED29E3}"/>
-    <hyperlink ref="A373" r:id="rId50" xr:uid="{CF8F5958-57A0-4BA6-853C-30DBD1615E7E}"/>
-    <hyperlink ref="A374" r:id="rId51" xr:uid="{A1755E63-EBAB-4478-8E95-A721B0B2387B}"/>
-    <hyperlink ref="A377" r:id="rId52" xr:uid="{5FE0A41A-BEB0-4963-AE20-2F2F496105E5}"/>
-    <hyperlink ref="A378" r:id="rId53" xr:uid="{A162107B-41F3-4860-9DB5-3DE0A8603686}"/>
-    <hyperlink ref="A379" r:id="rId54" xr:uid="{88C77D28-0BED-401C-8791-020CF421822B}"/>
-    <hyperlink ref="A380" r:id="rId55" location="/home" display="https://dailysoapupdate.com/mysale01/ - /home" xr:uid="{ED445AD5-69EE-441C-8862-4D810E52DEC5}"/>
-    <hyperlink ref="A381" r:id="rId56" xr:uid="{1D6F2C4D-7C9C-4683-92F5-01BEB8099356}"/>
-    <hyperlink ref="A384" r:id="rId57" xr:uid="{19A630BA-D6C2-4E67-AEDE-DE86D518D7D5}"/>
-    <hyperlink ref="A385" r:id="rId58" xr:uid="{78101AA3-5C2E-4F84-83FA-2CB98D6D6CFB}"/>
-    <hyperlink ref="A387" r:id="rId59" xr:uid="{2B4761C7-50C1-4EDD-B96F-4F1787E1CBC8}"/>
-    <hyperlink ref="A393" r:id="rId60" display="https://green-mantis-164394.hostingersite.com/" xr:uid="{2B34A4E4-9398-403A-90EE-D85B9CA16F25}"/>
-    <hyperlink ref="A394" r:id="rId61" xr:uid="{E4560E2B-C78E-41C3-957D-D2BF080E03BE}"/>
-    <hyperlink ref="A395" r:id="rId62" xr:uid="{88BF5337-E77C-401E-8BC2-18E9BF59341E}"/>
-    <hyperlink ref="A396" r:id="rId63" xr:uid="{580A7D3E-475D-4E0A-ADE4-8349A3E3BBF7}"/>
-    <hyperlink ref="A397" r:id="rId64" xr:uid="{2D85C088-CC59-4C3B-AC6D-B0BB778648DF}"/>
-    <hyperlink ref="A398" r:id="rId65" xr:uid="{E4174A7C-DDDC-4B6C-8C39-0BFC26F53C7F}"/>
-    <hyperlink ref="A399" r:id="rId66" display="https://meesho.onlinelehenga.com/" xr:uid="{99E9B889-84BA-4CD1-BDD1-2110E9D84A11}"/>
-    <hyperlink ref="A400" r:id="rId67" display="https://saddlebrown-koala-214922.hostingersite.com/" xr:uid="{E1D58D6D-CC15-40C2-8C83-B5D97520250B}"/>
-    <hyperlink ref="A401" r:id="rId68" xr:uid="{B3CA8362-172B-456D-8124-441D397572CC}"/>
-    <hyperlink ref="A402" r:id="rId69" xr:uid="{A85E772E-58E3-417C-A8C7-546B587A8CD7}"/>
-    <hyperlink ref="A403" r:id="rId70" xr:uid="{A436E5C8-0361-4819-B3AB-8624CFA890A0}"/>
-    <hyperlink ref="A404" r:id="rId71" xr:uid="{265D5089-7AFF-42BB-810C-3D0086B4C577}"/>
-    <hyperlink ref="A414" r:id="rId72" display="https://mediumturquoise-peafowl-207676.hostingersite.com/" xr:uid="{272F65DF-8C9B-40EB-832D-D1D568C5C95F}"/>
-    <hyperlink ref="A415" r:id="rId73" display="https://lightgrey-quail-699092.hostingersite.com/" xr:uid="{9D26575C-F7EE-4EB9-A8D6-0B3DF183BD17}"/>
-    <hyperlink ref="A416" r:id="rId74" xr:uid="{AFAE0A08-FD6C-4564-BAF4-5EBE6A761042}"/>
-    <hyperlink ref="A417" r:id="rId75" display="https://khaki-stinkbug-900591.hostingersite.com/" xr:uid="{02F8DE61-3E76-4D62-A3D7-8E5DE7BFED51}"/>
-    <hyperlink ref="A418" r:id="rId76" display="https://beige-scorpion-308566.hostingersite.com/" xr:uid="{680EC066-7949-4C62-8DBA-371DF624B69D}"/>
-    <hyperlink ref="A419" r:id="rId77" display="https://measho003.vercel.app/" xr:uid="{0CB320BA-83FC-42A0-BD43-530D7E1C786B}"/>
-    <hyperlink ref="A420" r:id="rId78" display="https://royalblue-hare-879414.hostingersite.com/" xr:uid="{AE6E1953-24D9-4881-B883-9CCF98D52420}"/>
-    <hyperlink ref="A421" r:id="rId79" display="https://lightpink-cheetah-375413.hostingersite.com/" xr:uid="{EDD8458A-09FD-434E-A114-A5DD42EFD5C8}"/>
-    <hyperlink ref="A422" r:id="rId80" xr:uid="{BABCF7E5-06BB-4024-9D50-7591DB5C2F66}"/>
-    <hyperlink ref="A423" r:id="rId81" xr:uid="{3AF9AB90-2C4D-455F-AB73-188B9B5C1765}"/>
-    <hyperlink ref="A426" r:id="rId82" xr:uid="{8E97EC4A-2BBC-4615-B9AE-5C97992268F7}"/>
-    <hyperlink ref="A427" r:id="rId83" xr:uid="{13288E77-41EE-4E13-8F6E-DA18ABA2353D}"/>
-    <hyperlink ref="A428" r:id="rId84" xr:uid="{B34C83F0-9CBC-4244-8527-6EDB22B40A63}"/>
-    <hyperlink ref="A439" r:id="rId85" xr:uid="{8D07D963-0F10-4C7D-AF3E-10838F031EC0}"/>
-    <hyperlink ref="A440" r:id="rId86" xr:uid="{0F171A6F-4697-4B15-B75F-5C5B28FD8EBF}"/>
-    <hyperlink ref="A441" r:id="rId87" xr:uid="{86816317-97A1-4F97-B212-EAEF22EA4A46}"/>
-    <hyperlink ref="A446" r:id="rId88" xr:uid="{39B53F48-B091-4FDC-81D5-4040E21911B5}"/>
-    <hyperlink ref="A462" r:id="rId89" display="https://darkseagreen-ibex-492354.hostingersite.com/" xr:uid="{05BFAF4E-1D3D-4F3A-AFD6-3005F392BE91}"/>
-    <hyperlink ref="A463" r:id="rId90" display="https://chocolate-starling-667762.hostingersite.com/" xr:uid="{4D7990B0-A29A-485E-AD19-57AA461B7BE1}"/>
-    <hyperlink ref="A464" r:id="rId91" xr:uid="{BF1DB468-4452-4635-9DB4-EF97DF2F0196}"/>
-    <hyperlink ref="A465" r:id="rId92" display="https://gray-reindeer-806195.hostingersite.com/" xr:uid="{19DB1B5A-1E0E-4594-8096-1E5664BD5E13}"/>
-    <hyperlink ref="A469" r:id="rId93" xr:uid="{837BEB80-5076-4CEE-8D70-5AB707037F54}"/>
-    <hyperlink ref="A470" r:id="rId94" xr:uid="{5093A6EB-E127-4496-BA54-6236FECA25E8}"/>
-    <hyperlink ref="A471" r:id="rId95" xr:uid="{D630EA1D-B9F9-44C6-874E-0BF01DC4F8F4}"/>
-    <hyperlink ref="A473" r:id="rId96" xr:uid="{A9290627-01F9-44B1-A392-DC3DEF07BA62}"/>
-    <hyperlink ref="A474" r:id="rId97" xr:uid="{CC2CBEDC-4223-4E73-BB9A-F9F9C7B42DB6}"/>
-    <hyperlink ref="A475" r:id="rId98" xr:uid="{5D811E40-F96F-44B6-9611-A8E4AFBEB75F}"/>
-    <hyperlink ref="A476" r:id="rId99" display="https://sienna-hyena-831771.hostingersite.com/" xr:uid="{B75933FC-FE72-4DE4-85F7-653B5AEDEA88}"/>
-    <hyperlink ref="A477" r:id="rId100" xr:uid="{F90BADA9-FA80-4F18-9BE5-683A897A4160}"/>
-    <hyperlink ref="A478" r:id="rId101" xr:uid="{83D2B7E0-12D5-471C-99CA-E847A7C6E3CE}"/>
-    <hyperlink ref="A479" r:id="rId102" xr:uid="{858504A4-8AB9-4CC7-AA93-6EFA272E914F}"/>
-    <hyperlink ref="A480" r:id="rId103" xr:uid="{2B447FFF-9B8C-4DAC-91D7-40ABD5900586}"/>
-    <hyperlink ref="A481" r:id="rId104" display="https://slategray-mandrill-919025.hostingersite.com/" xr:uid="{AFAA1FDC-23E8-4EDB-B8A6-EEC5C04F21BC}"/>
-    <hyperlink ref="A482" r:id="rId105" display="https://meeshom.sales-india.com/" xr:uid="{1ADD0AA0-545F-481A-AE74-072B14FBA8DC}"/>
-    <hyperlink ref="A483" r:id="rId106" xr:uid="{4955BF0E-FEE6-49A9-8A8C-B04D55598E83}"/>
-    <hyperlink ref="A484" r:id="rId107" xr:uid="{B05DFDC5-31C7-4424-93BB-96A9D5711259}"/>
-    <hyperlink ref="A485" r:id="rId108" display="https://gold-mink-565478.hostingersite.com/" xr:uid="{1EF925E2-DD85-48AD-B845-2748723D0F6D}"/>
-    <hyperlink ref="A486" r:id="rId109" display="https://yellowgreen-quail-835557.hostingersite.com/" xr:uid="{F8C6920F-1BE6-40BD-8C13-0337251BAFD7}"/>
-    <hyperlink ref="A487" r:id="rId110" xr:uid="{3BC060C3-D665-473D-AFD2-134A1B636098}"/>
-    <hyperlink ref="A488" r:id="rId111" xr:uid="{265E54A1-8E84-4B1E-954C-58729FF53ADE}"/>
-    <hyperlink ref="A489" r:id="rId112" xr:uid="{A9C37654-D78B-4067-B340-544416D25FB9}"/>
-    <hyperlink ref="A490" r:id="rId113" xr:uid="{2E1A8F80-5088-449E-8854-68BA06CF22F3}"/>
-    <hyperlink ref="A491" r:id="rId114" display="https://betary.online/" xr:uid="{13B27B5E-0249-49C2-ABF1-7EFAF84CA62E}"/>
-    <hyperlink ref="A492" r:id="rId115" xr:uid="{C60B6BBE-9153-4861-B083-4410F52E47BD}"/>
-    <hyperlink ref="A494" r:id="rId116" xr:uid="{A21EB6CD-8244-4AB4-9DC9-C59EE0579158}"/>
-    <hyperlink ref="A495" r:id="rId117" display="https://dodgerblue-dragonfly-520818.hostingersite.com/" xr:uid="{B7C5A4F4-56BA-42A9-8300-3C4319185262}"/>
-    <hyperlink ref="A496" r:id="rId118" xr:uid="{60481478-3062-4963-A96B-669A3705D799}"/>
-    <hyperlink ref="A497" r:id="rId119" display="https://blanchedalmond-kudu-912286.hostingersite.com/" xr:uid="{9E025F2A-EBBF-4264-B849-104D36A319B3}"/>
-    <hyperlink ref="A498" r:id="rId120" display="https://mesho.diziebook.shop/" xr:uid="{B527BCB8-ED00-41FD-B7BF-C873F9955C15}"/>
-    <hyperlink ref="A499" r:id="rId121" display="https://violet-fish-896843.hostingersite.com/" xr:uid="{6B77CF77-71BB-4AE6-945A-4A609C2DF7A7}"/>
-    <hyperlink ref="A500" r:id="rId122" display="https://ivory-okapi-964506.hostingersite.com/" xr:uid="{BD2F584B-E6C8-40BB-8281-AF3AAF43B155}"/>
-    <hyperlink ref="A501" r:id="rId123" xr:uid="{F935201D-6921-4D4C-A839-C1A4740FB122}"/>
-    <hyperlink ref="A502" r:id="rId124" display="https://fitshirt.store/" xr:uid="{655157C1-1463-4610-A1CE-BC91506AC59B}"/>
-    <hyperlink ref="A503" r:id="rId125" xr:uid="{4A653EA3-A56F-4612-A850-CEF323C97FD2}"/>
-    <hyperlink ref="A504" r:id="rId126" display="https://lightskyblue-quail-640026.hostingersite.com/" xr:uid="{2F421E40-D20D-4779-9F0A-B36600202033}"/>
-    <hyperlink ref="A505" r:id="rId127" display="https://aqua-guanaco-165107.hostingersite.com/" xr:uid="{4F02A28F-F315-48D3-9543-5F22AC4584E0}"/>
-    <hyperlink ref="A506" r:id="rId128" xr:uid="{44B2E1F3-6BDA-4611-B6B6-1DCFC567A78A}"/>
-    <hyperlink ref="A507" r:id="rId129" display="https://mistyrose-goshawk-231036.hostingersite.com/" xr:uid="{80F782E1-C019-4E0A-8996-06E0C4F05076}"/>
-    <hyperlink ref="A508" r:id="rId130" xr:uid="{84D53771-AA31-47F3-9B6E-10B34EAE07EB}"/>
-    <hyperlink ref="A509" r:id="rId131" xr:uid="{2C0C7C83-EE83-4F93-8791-ED56E1135CE9}"/>
-    <hyperlink ref="A510" r:id="rId132" display="https://phpstack-1593364-6254845.cloudwaysapps.com/" xr:uid="{AC1AE79A-32B2-43CA-9A47-451A4B229199}"/>
-    <hyperlink ref="A511" r:id="rId133" display="https://phpstack-1593364-6264999.cloudwaysapps.com/" xr:uid="{6A5B5E2F-66F7-4049-B8DA-60B77EFB39F5}"/>
-    <hyperlink ref="A512" r:id="rId134" xr:uid="{731A7782-6787-4E11-81B3-33A0F36DBF18}"/>
-    <hyperlink ref="A513" r:id="rId135" display="https://phpstack-1598224-6264971.cloudwaysapps.com/" xr:uid="{F7E37C8C-9436-48AB-A8B9-681375E0D9D9}"/>
-    <hyperlink ref="A514" r:id="rId136" display="https://buywear.online/" xr:uid="{3CE13E3F-A7B1-41B1-8C58-C63315B0F0FB}"/>
-    <hyperlink ref="A515" r:id="rId137" xr:uid="{FF2CAB0F-C32B-4402-8C0D-9957313869DE}"/>
-    <hyperlink ref="A516" r:id="rId138" xr:uid="{46E41F23-D317-4750-BB34-954DD9B02D0C}"/>
-    <hyperlink ref="A517" r:id="rId139" xr:uid="{24FC14A7-66DE-46B1-ABBB-7577B3A29580}"/>
-    <hyperlink ref="A518" r:id="rId140" display="https://firebrick-woodcock-735806.hostingersite.com/" xr:uid="{FB5A83CF-0EB1-47C3-9F0A-0813120DCA1E}"/>
-    <hyperlink ref="A519" r:id="rId141" xr:uid="{404AF3F9-710D-4784-877C-CF27CC2605A2}"/>
-    <hyperlink ref="A520" r:id="rId142" xr:uid="{A13682AD-69BF-4672-BB57-B7C4CAE56BAF}"/>
-    <hyperlink ref="A521" r:id="rId143" xr:uid="{42694ADB-0527-4ECB-820B-DB9CBF023394}"/>
-    <hyperlink ref="A529" r:id="rId144" xr:uid="{903E3CD7-2290-460A-AB98-DA9882E5A2E7}"/>
-    <hyperlink ref="A530" r:id="rId145" xr:uid="{22C76230-701D-4560-AB16-3858D1E6FE64}"/>
-    <hyperlink ref="A531" r:id="rId146" xr:uid="{5075D533-79C7-42B0-860F-ED51B85EF0FE}"/>
-    <hyperlink ref="A532" r:id="rId147" xr:uid="{96868CF8-4501-4D6A-A2BA-49ABB2904F00}"/>
-    <hyperlink ref="A533" r:id="rId148" xr:uid="{E181E12E-2ABE-4340-99F9-C064A7FE2B0F}"/>
-    <hyperlink ref="A534" r:id="rId149" xr:uid="{39E2B466-C829-4724-B8AB-B2E58455EBB5}"/>
-    <hyperlink ref="A535" r:id="rId150" xr:uid="{C2CE0306-0B8C-44BD-970C-0F207A06CBF3}"/>
-    <hyperlink ref="A541" r:id="rId151" display="https://betrady.online/" xr:uid="{1B9B1187-BE58-4AB6-AB58-E032E28ADEC2}"/>
-    <hyperlink ref="A542" r:id="rId152" display="https://fiipkart-summer.lovable.app/" xr:uid="{6D4BCADB-A456-440C-B244-61F3AC515CD7}"/>
-    <hyperlink ref="A544" r:id="rId153" xr:uid="{E198A9E9-F98A-4474-AECE-3016ED06D033}"/>
-    <hyperlink ref="A545" r:id="rId154" display="https://magenta-heron-153902.hostingersite.com/" xr:uid="{F04AC313-32A4-49F6-9735-B56B7053A1F8}"/>
-    <hyperlink ref="A546" r:id="rId155" xr:uid="{5A477327-F60A-4B1F-B201-985D79BD8775}"/>
-    <hyperlink ref="A547" r:id="rId156" xr:uid="{47158B01-1788-4192-8FB3-7A642C701780}"/>
-    <hyperlink ref="A548" r:id="rId157" display="https://www.flipkartmarchsale.in/" xr:uid="{66220ACB-1093-460E-8519-74761A1EE8DF}"/>
-    <hyperlink ref="A549" r:id="rId158" xr:uid="{40B37356-0F0E-4569-9A60-304ACDF5E8A9}"/>
-    <hyperlink ref="A556" r:id="rId159" xr:uid="{2246594F-0BFC-491A-8335-11CD82E66C33}"/>
-    <hyperlink ref="A557" r:id="rId160" xr:uid="{B6269A59-A82A-4306-A5C0-CBD5DB5A5FB9}"/>
-    <hyperlink ref="A559" r:id="rId161" xr:uid="{A15407B8-DE2D-4645-A5CF-EBDB2C3D2CFD}"/>
-    <hyperlink ref="A560" r:id="rId162" xr:uid="{50A935C0-2F94-447E-808F-C62582CFC903}"/>
-    <hyperlink ref="A561" r:id="rId163" xr:uid="{66AEAB67-754E-47D8-A494-F586E1829510}"/>
-    <hyperlink ref="A562" r:id="rId164" xr:uid="{98E3B68A-B453-4DC2-B479-E5AE0A00A948}"/>
-    <hyperlink ref="A563" r:id="rId165" display="https://mediumvioletred-rail-865467.hostingersite.com/" xr:uid="{99E68E58-217B-4B07-8846-6371FE797D0A}"/>
-    <hyperlink ref="A564" r:id="rId166" display="https://healthprime.fun/" xr:uid="{A9EF7D20-8E71-474A-B08A-B6511D70993E}"/>
-    <hyperlink ref="A565" r:id="rId167" display="https://plum-lobster-541291.hostingersite.com/" xr:uid="{9C48409B-A44C-41AE-9A3B-C5C3608FC8FD}"/>
-    <hyperlink ref="A566" r:id="rId168" xr:uid="{C83AEB37-67C2-4A5A-86EE-F382DE5AB006}"/>
-    <hyperlink ref="A567" r:id="rId169" xr:uid="{CBE2175F-9647-442F-B51F-0C361C71F97B}"/>
-    <hyperlink ref="A569" r:id="rId170" xr:uid="{02252EC6-FF65-4C04-9EB0-78BA914777F3}"/>
-    <hyperlink ref="A570" r:id="rId171" xr:uid="{A027763B-6966-4A9E-B434-73705A78E6E2}"/>
-    <hyperlink ref="A571" r:id="rId172" xr:uid="{12870190-F4E8-4ACC-B5CD-138A52774920}"/>
-    <hyperlink ref="A572" r:id="rId173" xr:uid="{DEEEF48B-486C-4467-9F0A-703940D111C2}"/>
-    <hyperlink ref="A573" r:id="rId174" xr:uid="{F6DFFAEE-62E9-484B-A82D-D05D9E0473EA}"/>
-    <hyperlink ref="A574" r:id="rId175" xr:uid="{2FAADB78-55BF-408D-A4F5-035D4491F8AA}"/>
-    <hyperlink ref="A575" r:id="rId176" xr:uid="{20E948BE-7EB3-41D3-99F2-FB061E2C655D}"/>
-    <hyperlink ref="A576" r:id="rId177" xr:uid="{F3BDF017-D2C3-4D8F-ADDD-419BC5E7D6F5}"/>
-    <hyperlink ref="A577" r:id="rId178" xr:uid="{AFD9F105-D09C-41D4-91FA-A1ADD6F83C5A}"/>
-    <hyperlink ref="A578" r:id="rId179" xr:uid="{2A0A0FE5-B9BD-418E-86DD-D2F425CC69AD}"/>
-    <hyperlink ref="A584" r:id="rId180" xr:uid="{D3582409-A6AC-4F71-8F92-E8C7883AB73A}"/>
-    <hyperlink ref="A585" r:id="rId181" xr:uid="{6D91B0E3-2F1B-49C0-8976-178186AF1A70}"/>
-    <hyperlink ref="A586" r:id="rId182" xr:uid="{08480B4A-B583-4D2A-9A92-0CA262A70CBE}"/>
-    <hyperlink ref="B429" r:id="rId183" display="https://myip.ms/view/countries/FRA/Internet_Usage_Statistics_France.html" xr:uid="{F2737594-B0B1-499C-9C64-78091118CFA5}"/>
-    <hyperlink ref="B432" r:id="rId184" display="https://myip.ms/view/countries/USA/Internet_Usage_Statistics_USA.html" xr:uid="{384CEC91-81BC-4D52-ADA5-6DFC320BB9BA}"/>
-    <hyperlink ref="B462" r:id="rId185" display="https://myip.ms/view/countries/DEU/Internet_Usage_Statistics_Germany.html" xr:uid="{C49C907F-14E8-414C-96AB-FD6ADD032D1C}"/>
-    <hyperlink ref="B463" r:id="rId186" display="https://myip.ms/view/countries/FRA/Internet_Usage_Statistics_France.html" xr:uid="{67204D82-5BF6-4BB8-8FB5-CFD5EBC0EDB5}"/>
-    <hyperlink ref="B464" r:id="rId187" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{78B1A8AA-423F-42D7-8447-1330B01412D1}"/>
-    <hyperlink ref="B465" r:id="rId188" display="https://myip.ms/view/countries/FRA/Internet_Usage_Statistics_France.html" xr:uid="{DD02A525-310A-4583-BE2D-405D08E5E12F}"/>
-    <hyperlink ref="B466" r:id="rId189" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{A13066FC-25B6-4351-BF2B-A87618F35853}"/>
-    <hyperlink ref="B467" r:id="rId190" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{5CF2DBA8-8FE4-4A82-85FB-7841BCE823F5}"/>
-    <hyperlink ref="B470" r:id="rId191" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{B25FA224-1524-4E9B-AE27-41143DF6223E}"/>
-    <hyperlink ref="B471" r:id="rId192" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{E8571A1D-2B16-4088-8D7C-5E6CB2018ECC}"/>
-    <hyperlink ref="B520" r:id="rId193" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{4BD7D44C-BEF7-47A4-99B5-16D6479FAC76}"/>
-    <hyperlink ref="B521" r:id="rId194" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{38D270BC-DEEE-468E-9B8A-ED46E9ECA658}"/>
-    <hyperlink ref="B522" r:id="rId195" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{FB8153D6-CBA3-48AF-8F83-1FB69AC94C53}"/>
+    <hyperlink ref="A54" r:id="rId3" display="https://bigwinoffer.com.tr/" xr:uid="{98C766A6-866D-407A-A703-A304F2271943}"/>
+    <hyperlink ref="A55" r:id="rId4" xr:uid="{BD339C4C-F3D6-4339-914A-629492FF0313}"/>
+    <hyperlink ref="A60" r:id="rId5" xr:uid="{170DE5A7-BE41-4BD8-A8E7-CDE00238162F}"/>
+    <hyperlink ref="A61" r:id="rId6" xr:uid="{8A69FD07-0DF7-4EDE-9E5F-DC8F506B570E}"/>
+    <hyperlink ref="A71" r:id="rId7" xr:uid="{C553ACF4-3781-492E-BD5B-E824E9FF5C3E}"/>
+    <hyperlink ref="A74" r:id="rId8" xr:uid="{5D8F5B3F-17AE-4DF2-AD5E-9613E48F65E0}"/>
+    <hyperlink ref="A75" r:id="rId9" xr:uid="{D4AF918A-E899-4C6A-8824-5157F7D247B1}"/>
+    <hyperlink ref="A76" r:id="rId10" xr:uid="{F554D08F-0620-410D-A203-70DF8D4BD8A7}"/>
+    <hyperlink ref="A77" r:id="rId11" xr:uid="{232A2CD1-646E-4812-AE7D-13AB9A95D539}"/>
+    <hyperlink ref="A83" r:id="rId12" xr:uid="{C70A6BA3-3B94-42A0-B1AC-0B1981DA4DBB}"/>
+    <hyperlink ref="A96" r:id="rId13" xr:uid="{4F7A26AB-5F2B-4F29-B785-A4AEAD3256FD}"/>
+    <hyperlink ref="A97" r:id="rId14" xr:uid="{6D4DCC2E-630E-4ECF-8711-194F3FF9F36B}"/>
+    <hyperlink ref="A98" r:id="rId15" xr:uid="{CDAAF86A-C222-4A2B-B805-935CDD2492ED}"/>
+    <hyperlink ref="A100" r:id="rId16" display="https://meeshosalemeesho.store/" xr:uid="{407D2E40-C398-454D-9CE1-60A818B99B53}"/>
+    <hyperlink ref="A101" r:id="rId17" xr:uid="{A9918901-20E2-44D9-A6E5-21293D85876A}"/>
+    <hyperlink ref="A104" r:id="rId18" display="https://me-esho.netlify.app/" xr:uid="{F642A9F9-6008-4571-8ADA-709AA1672F98}"/>
+    <hyperlink ref="A105" r:id="rId19" xr:uid="{6513F9F0-7F4F-4843-A74A-0CB4874E0599}"/>
+    <hyperlink ref="A109" r:id="rId20" xr:uid="{F62E82C0-1B21-4251-BCAC-E0323EB23981}"/>
+    <hyperlink ref="A126" r:id="rId21" xr:uid="{7E52A3D5-33B5-4025-8474-2362A1C0FC9C}"/>
+    <hyperlink ref="A181" r:id="rId22" xr:uid="{4EA6B28F-57D3-40EB-A1A6-6C25D45AFF06}"/>
+    <hyperlink ref="A182" r:id="rId23" xr:uid="{B1A637C6-B83A-4431-970F-AE1D781F7510}"/>
+    <hyperlink ref="A183" r:id="rId24" xr:uid="{45682F5A-A237-45C3-96BB-F43A9439BDD5}"/>
+    <hyperlink ref="A184" r:id="rId25" xr:uid="{DB9A5180-8F2B-419E-8B26-86E9E68F0555}"/>
+    <hyperlink ref="A187" r:id="rId26" xr:uid="{B08E4BBD-D132-42C5-83C7-A35E01B01762}"/>
+    <hyperlink ref="A234" r:id="rId27" xr:uid="{D442933B-7EFF-4840-B6C6-36CC50121D06}"/>
+    <hyperlink ref="A235" r:id="rId28" xr:uid="{3F8D3800-3C6B-417A-9353-AE42F2A981AC}"/>
+    <hyperlink ref="A238" r:id="rId29" xr:uid="{C1805AF2-D1A1-4825-AF0F-2AF3ED072F02}"/>
+    <hyperlink ref="A241" r:id="rId30" xr:uid="{8204F786-BE48-4C16-BEB2-D1D959C2BB89}"/>
+    <hyperlink ref="A245" r:id="rId31" xr:uid="{9719F79F-2C88-4611-894E-3ECDADE8E57E}"/>
+    <hyperlink ref="A246" r:id="rId32" xr:uid="{1A723955-4FB1-4C35-AFDE-721A2275A546}"/>
+    <hyperlink ref="A247" r:id="rId33" xr:uid="{130E758A-3D4D-419E-8236-C07151C99AD2}"/>
+    <hyperlink ref="A248" r:id="rId34" xr:uid="{77192F96-45E6-42AA-B872-F6A0E0472031}"/>
+    <hyperlink ref="A252" r:id="rId35" xr:uid="{4F1D3828-0567-48C5-A987-84FFE637D95C}"/>
+    <hyperlink ref="A253" r:id="rId36" xr:uid="{3D67BDCE-1DA2-447A-BA58-554F134B7C00}"/>
+    <hyperlink ref="A254" r:id="rId37" xr:uid="{C12B6E0A-9823-4426-B0FE-8BBFEA3835EB}"/>
+    <hyperlink ref="A257" r:id="rId38" xr:uid="{F82145D5-63AF-4BC4-A3A3-C7EFC7B659E2}"/>
+    <hyperlink ref="A258" r:id="rId39" display="https://yellow-emu-733093.hostingersite.com/" xr:uid="{498B7977-1C68-44F8-A612-C3FCDC6308DC}"/>
+    <hyperlink ref="A262" r:id="rId40" xr:uid="{AF1BAF98-1EA5-4501-8822-F9A4AEC9886A}"/>
+    <hyperlink ref="A263" r:id="rId41" xr:uid="{F24BB87D-B1D5-49AE-8CAF-22A7ED07F7EE}"/>
+    <hyperlink ref="A264" r:id="rId42" xr:uid="{F27DE639-C332-4C51-8BA7-BA96150BD1F9}"/>
+    <hyperlink ref="A269" r:id="rId43" xr:uid="{6B755285-6191-481C-8905-64260133B3ED}"/>
+    <hyperlink ref="A274" r:id="rId44" xr:uid="{39918188-4D6A-4CF0-A2EE-121BE4F7ACA0}"/>
+    <hyperlink ref="A275" r:id="rId45" xr:uid="{3F1A5270-1234-4BEE-96EC-59639650FCD1}"/>
+    <hyperlink ref="A278" r:id="rId46" xr:uid="{0F0E5898-D3C9-44F1-B399-4B5E1123A6FA}"/>
+    <hyperlink ref="A279" r:id="rId47" xr:uid="{86983A0A-DF54-4D82-8CFF-9D09324C1C04}"/>
+    <hyperlink ref="A280" r:id="rId48" display="https://flipcart-limited-offer.myshopify.com/" xr:uid="{2FB3D63C-F210-4F00-BE43-F63709ED29E3}"/>
+    <hyperlink ref="A281" r:id="rId49" xr:uid="{CF8F5958-57A0-4BA6-853C-30DBD1615E7E}"/>
+    <hyperlink ref="A282" r:id="rId50" xr:uid="{A1755E63-EBAB-4478-8E95-A721B0B2387B}"/>
+    <hyperlink ref="A285" r:id="rId51" xr:uid="{5FE0A41A-BEB0-4963-AE20-2F2F496105E5}"/>
+    <hyperlink ref="A286" r:id="rId52" xr:uid="{A162107B-41F3-4860-9DB5-3DE0A8603686}"/>
+    <hyperlink ref="A287" r:id="rId53" xr:uid="{88C77D28-0BED-401C-8791-020CF421822B}"/>
+    <hyperlink ref="A288" r:id="rId54" location="/home" display="https://dailysoapupdate.com/mysale01/ - /home" xr:uid="{ED445AD5-69EE-441C-8862-4D810E52DEC5}"/>
+    <hyperlink ref="A289" r:id="rId55" xr:uid="{1D6F2C4D-7C9C-4683-92F5-01BEB8099356}"/>
+    <hyperlink ref="A292" r:id="rId56" xr:uid="{19A630BA-D6C2-4E67-AEDE-DE86D518D7D5}"/>
+    <hyperlink ref="A293" r:id="rId57" xr:uid="{78101AA3-5C2E-4F84-83FA-2CB98D6D6CFB}"/>
+    <hyperlink ref="A295" r:id="rId58" xr:uid="{2B4761C7-50C1-4EDD-B96F-4F1787E1CBC8}"/>
+    <hyperlink ref="A301" r:id="rId59" display="https://green-mantis-164394.hostingersite.com/" xr:uid="{2B34A4E4-9398-403A-90EE-D85B9CA16F25}"/>
+    <hyperlink ref="A302" r:id="rId60" xr:uid="{E4560E2B-C78E-41C3-957D-D2BF080E03BE}"/>
+    <hyperlink ref="A303" r:id="rId61" xr:uid="{88BF5337-E77C-401E-8BC2-18E9BF59341E}"/>
+    <hyperlink ref="A304" r:id="rId62" xr:uid="{580A7D3E-475D-4E0A-ADE4-8349A3E3BBF7}"/>
+    <hyperlink ref="A305" r:id="rId63" xr:uid="{2D85C088-CC59-4C3B-AC6D-B0BB778648DF}"/>
+    <hyperlink ref="A306" r:id="rId64" xr:uid="{E4174A7C-DDDC-4B6C-8C39-0BFC26F53C7F}"/>
+    <hyperlink ref="A307" r:id="rId65" display="https://meesho.onlinelehenga.com/" xr:uid="{99E9B889-84BA-4CD1-BDD1-2110E9D84A11}"/>
+    <hyperlink ref="A308" r:id="rId66" display="https://saddlebrown-koala-214922.hostingersite.com/" xr:uid="{E1D58D6D-CC15-40C2-8C83-B5D97520250B}"/>
+    <hyperlink ref="A309" r:id="rId67" xr:uid="{B3CA8362-172B-456D-8124-441D397572CC}"/>
+    <hyperlink ref="A310" r:id="rId68" xr:uid="{A85E772E-58E3-417C-A8C7-546B587A8CD7}"/>
+    <hyperlink ref="A311" r:id="rId69" xr:uid="{A436E5C8-0361-4819-B3AB-8624CFA890A0}"/>
+    <hyperlink ref="A312" r:id="rId70" xr:uid="{265D5089-7AFF-42BB-810C-3D0086B4C577}"/>
+    <hyperlink ref="A322" r:id="rId71" display="https://mediumturquoise-peafowl-207676.hostingersite.com/" xr:uid="{272F65DF-8C9B-40EB-832D-D1D568C5C95F}"/>
+    <hyperlink ref="A323" r:id="rId72" display="https://lightgrey-quail-699092.hostingersite.com/" xr:uid="{9D26575C-F7EE-4EB9-A8D6-0B3DF183BD17}"/>
+    <hyperlink ref="A324" r:id="rId73" xr:uid="{AFAE0A08-FD6C-4564-BAF4-5EBE6A761042}"/>
+    <hyperlink ref="A325" r:id="rId74" display="https://khaki-stinkbug-900591.hostingersite.com/" xr:uid="{02F8DE61-3E76-4D62-A3D7-8E5DE7BFED51}"/>
+    <hyperlink ref="A326" r:id="rId75" display="https://beige-scorpion-308566.hostingersite.com/" xr:uid="{680EC066-7949-4C62-8DBA-371DF624B69D}"/>
+    <hyperlink ref="A327" r:id="rId76" display="https://measho003.vercel.app/" xr:uid="{0CB320BA-83FC-42A0-BD43-530D7E1C786B}"/>
+    <hyperlink ref="A328" r:id="rId77" display="https://royalblue-hare-879414.hostingersite.com/" xr:uid="{AE6E1953-24D9-4881-B883-9CCF98D52420}"/>
+    <hyperlink ref="A329" r:id="rId78" display="https://lightpink-cheetah-375413.hostingersite.com/" xr:uid="{EDD8458A-09FD-434E-A114-A5DD42EFD5C8}"/>
+    <hyperlink ref="A330" r:id="rId79" xr:uid="{BABCF7E5-06BB-4024-9D50-7591DB5C2F66}"/>
+    <hyperlink ref="A331" r:id="rId80" xr:uid="{3AF9AB90-2C4D-455F-AB73-188B9B5C1765}"/>
+    <hyperlink ref="A334" r:id="rId81" xr:uid="{8E97EC4A-2BBC-4615-B9AE-5C97992268F7}"/>
+    <hyperlink ref="A335" r:id="rId82" xr:uid="{13288E77-41EE-4E13-8F6E-DA18ABA2353D}"/>
+    <hyperlink ref="A336" r:id="rId83" xr:uid="{B34C83F0-9CBC-4244-8527-6EDB22B40A63}"/>
+    <hyperlink ref="A347" r:id="rId84" xr:uid="{8D07D963-0F10-4C7D-AF3E-10838F031EC0}"/>
+    <hyperlink ref="A348" r:id="rId85" xr:uid="{0F171A6F-4697-4B15-B75F-5C5B28FD8EBF}"/>
+    <hyperlink ref="A349" r:id="rId86" xr:uid="{86816317-97A1-4F97-B212-EAEF22EA4A46}"/>
+    <hyperlink ref="A354" r:id="rId87" xr:uid="{39B53F48-B091-4FDC-81D5-4040E21911B5}"/>
+    <hyperlink ref="A370" r:id="rId88" display="https://darkseagreen-ibex-492354.hostingersite.com/" xr:uid="{05BFAF4E-1D3D-4F3A-AFD6-3005F392BE91}"/>
+    <hyperlink ref="A371" r:id="rId89" display="https://chocolate-starling-667762.hostingersite.com/" xr:uid="{4D7990B0-A29A-485E-AD19-57AA461B7BE1}"/>
+    <hyperlink ref="A372" r:id="rId90" xr:uid="{BF1DB468-4452-4635-9DB4-EF97DF2F0196}"/>
+    <hyperlink ref="A373" r:id="rId91" display="https://gray-reindeer-806195.hostingersite.com/" xr:uid="{19DB1B5A-1E0E-4594-8096-1E5664BD5E13}"/>
+    <hyperlink ref="A377" r:id="rId92" xr:uid="{837BEB80-5076-4CEE-8D70-5AB707037F54}"/>
+    <hyperlink ref="A378" r:id="rId93" xr:uid="{5093A6EB-E127-4496-BA54-6236FECA25E8}"/>
+    <hyperlink ref="A379" r:id="rId94" xr:uid="{D630EA1D-B9F9-44C6-874E-0BF01DC4F8F4}"/>
+    <hyperlink ref="A381" r:id="rId95" xr:uid="{A9290627-01F9-44B1-A392-DC3DEF07BA62}"/>
+    <hyperlink ref="A382" r:id="rId96" xr:uid="{CC2CBEDC-4223-4E73-BB9A-F9F9C7B42DB6}"/>
+    <hyperlink ref="A383" r:id="rId97" xr:uid="{5D811E40-F96F-44B6-9611-A8E4AFBEB75F}"/>
+    <hyperlink ref="A384" r:id="rId98" display="https://sienna-hyena-831771.hostingersite.com/" xr:uid="{B75933FC-FE72-4DE4-85F7-653B5AEDEA88}"/>
+    <hyperlink ref="A385" r:id="rId99" xr:uid="{F90BADA9-FA80-4F18-9BE5-683A897A4160}"/>
+    <hyperlink ref="A386" r:id="rId100" xr:uid="{83D2B7E0-12D5-471C-99CA-E847A7C6E3CE}"/>
+    <hyperlink ref="A387" r:id="rId101" xr:uid="{858504A4-8AB9-4CC7-AA93-6EFA272E914F}"/>
+    <hyperlink ref="A388" r:id="rId102" xr:uid="{2B447FFF-9B8C-4DAC-91D7-40ABD5900586}"/>
+    <hyperlink ref="A389" r:id="rId103" display="https://slategray-mandrill-919025.hostingersite.com/" xr:uid="{AFAA1FDC-23E8-4EDB-B8A6-EEC5C04F21BC}"/>
+    <hyperlink ref="A390" r:id="rId104" display="https://meeshom.sales-india.com/" xr:uid="{1ADD0AA0-545F-481A-AE74-072B14FBA8DC}"/>
+    <hyperlink ref="A391" r:id="rId105" xr:uid="{4955BF0E-FEE6-49A9-8A8C-B04D55598E83}"/>
+    <hyperlink ref="A392" r:id="rId106" xr:uid="{B05DFDC5-31C7-4424-93BB-96A9D5711259}"/>
+    <hyperlink ref="A393" r:id="rId107" display="https://gold-mink-565478.hostingersite.com/" xr:uid="{1EF925E2-DD85-48AD-B845-2748723D0F6D}"/>
+    <hyperlink ref="A394" r:id="rId108" display="https://yellowgreen-quail-835557.hostingersite.com/" xr:uid="{F8C6920F-1BE6-40BD-8C13-0337251BAFD7}"/>
+    <hyperlink ref="A395" r:id="rId109" xr:uid="{3BC060C3-D665-473D-AFD2-134A1B636098}"/>
+    <hyperlink ref="A396" r:id="rId110" xr:uid="{265E54A1-8E84-4B1E-954C-58729FF53ADE}"/>
+    <hyperlink ref="A397" r:id="rId111" xr:uid="{A9C37654-D78B-4067-B340-544416D25FB9}"/>
+    <hyperlink ref="A398" r:id="rId112" xr:uid="{2E1A8F80-5088-449E-8854-68BA06CF22F3}"/>
+    <hyperlink ref="A399" r:id="rId113" display="https://betary.online/" xr:uid="{13B27B5E-0249-49C2-ABF1-7EFAF84CA62E}"/>
+    <hyperlink ref="A400" r:id="rId114" xr:uid="{C60B6BBE-9153-4861-B083-4410F52E47BD}"/>
+    <hyperlink ref="A402" r:id="rId115" xr:uid="{A21EB6CD-8244-4AB4-9DC9-C59EE0579158}"/>
+    <hyperlink ref="A403" r:id="rId116" display="https://dodgerblue-dragonfly-520818.hostingersite.com/" xr:uid="{B7C5A4F4-56BA-42A9-8300-3C4319185262}"/>
+    <hyperlink ref="A404" r:id="rId117" xr:uid="{60481478-3062-4963-A96B-669A3705D799}"/>
+    <hyperlink ref="A405" r:id="rId118" display="https://blanchedalmond-kudu-912286.hostingersite.com/" xr:uid="{9E025F2A-EBBF-4264-B849-104D36A319B3}"/>
+    <hyperlink ref="A406" r:id="rId119" display="https://mesho.diziebook.shop/" xr:uid="{B527BCB8-ED00-41FD-B7BF-C873F9955C15}"/>
+    <hyperlink ref="A407" r:id="rId120" display="https://violet-fish-896843.hostingersite.com/" xr:uid="{6B77CF77-71BB-4AE6-945A-4A609C2DF7A7}"/>
+    <hyperlink ref="A408" r:id="rId121" display="https://ivory-okapi-964506.hostingersite.com/" xr:uid="{BD2F584B-E6C8-40BB-8281-AF3AAF43B155}"/>
+    <hyperlink ref="A409" r:id="rId122" xr:uid="{F935201D-6921-4D4C-A839-C1A4740FB122}"/>
+    <hyperlink ref="A410" r:id="rId123" display="https://fitshirt.store/" xr:uid="{655157C1-1463-4610-A1CE-BC91506AC59B}"/>
+    <hyperlink ref="A411" r:id="rId124" xr:uid="{4A653EA3-A56F-4612-A850-CEF323C97FD2}"/>
+    <hyperlink ref="A412" r:id="rId125" display="https://lightskyblue-quail-640026.hostingersite.com/" xr:uid="{2F421E40-D20D-4779-9F0A-B36600202033}"/>
+    <hyperlink ref="A413" r:id="rId126" display="https://aqua-guanaco-165107.hostingersite.com/" xr:uid="{4F02A28F-F315-48D3-9543-5F22AC4584E0}"/>
+    <hyperlink ref="A414" r:id="rId127" xr:uid="{44B2E1F3-6BDA-4611-B6B6-1DCFC567A78A}"/>
+    <hyperlink ref="A415" r:id="rId128" display="https://mistyrose-goshawk-231036.hostingersite.com/" xr:uid="{80F782E1-C019-4E0A-8996-06E0C4F05076}"/>
+    <hyperlink ref="A416" r:id="rId129" xr:uid="{84D53771-AA31-47F3-9B6E-10B34EAE07EB}"/>
+    <hyperlink ref="A417" r:id="rId130" xr:uid="{2C0C7C83-EE83-4F93-8791-ED56E1135CE9}"/>
+    <hyperlink ref="A418" r:id="rId131" display="https://phpstack-1593364-6254845.cloudwaysapps.com/" xr:uid="{AC1AE79A-32B2-43CA-9A47-451A4B229199}"/>
+    <hyperlink ref="A419" r:id="rId132" display="https://phpstack-1593364-6264999.cloudwaysapps.com/" xr:uid="{6A5B5E2F-66F7-4049-B8DA-60B77EFB39F5}"/>
+    <hyperlink ref="A420" r:id="rId133" xr:uid="{731A7782-6787-4E11-81B3-33A0F36DBF18}"/>
+    <hyperlink ref="A421" r:id="rId134" display="https://phpstack-1598224-6264971.cloudwaysapps.com/" xr:uid="{F7E37C8C-9436-48AB-A8B9-681375E0D9D9}"/>
+    <hyperlink ref="A422" r:id="rId135" display="https://buywear.online/" xr:uid="{3CE13E3F-A7B1-41B1-8C58-C63315B0F0FB}"/>
+    <hyperlink ref="A423" r:id="rId136" xr:uid="{FF2CAB0F-C32B-4402-8C0D-9957313869DE}"/>
+    <hyperlink ref="A424" r:id="rId137" xr:uid="{46E41F23-D317-4750-BB34-954DD9B02D0C}"/>
+    <hyperlink ref="A425" r:id="rId138" xr:uid="{24FC14A7-66DE-46B1-ABBB-7577B3A29580}"/>
+    <hyperlink ref="A426" r:id="rId139" display="https://firebrick-woodcock-735806.hostingersite.com/" xr:uid="{FB5A83CF-0EB1-47C3-9F0A-0813120DCA1E}"/>
+    <hyperlink ref="A427" r:id="rId140" xr:uid="{404AF3F9-710D-4784-877C-CF27CC2605A2}"/>
+    <hyperlink ref="A428" r:id="rId141" xr:uid="{A13682AD-69BF-4672-BB57-B7C4CAE56BAF}"/>
+    <hyperlink ref="A429" r:id="rId142" xr:uid="{42694ADB-0527-4ECB-820B-DB9CBF023394}"/>
+    <hyperlink ref="A437" r:id="rId143" xr:uid="{903E3CD7-2290-460A-AB98-DA9882E5A2E7}"/>
+    <hyperlink ref="A438" r:id="rId144" xr:uid="{22C76230-701D-4560-AB16-3858D1E6FE64}"/>
+    <hyperlink ref="A439" r:id="rId145" xr:uid="{5075D533-79C7-42B0-860F-ED51B85EF0FE}"/>
+    <hyperlink ref="A440" r:id="rId146" xr:uid="{96868CF8-4501-4D6A-A2BA-49ABB2904F00}"/>
+    <hyperlink ref="A441" r:id="rId147" xr:uid="{E181E12E-2ABE-4340-99F9-C064A7FE2B0F}"/>
+    <hyperlink ref="A442" r:id="rId148" xr:uid="{39E2B466-C829-4724-B8AB-B2E58455EBB5}"/>
+    <hyperlink ref="A443" r:id="rId149" xr:uid="{C2CE0306-0B8C-44BD-970C-0F207A06CBF3}"/>
+    <hyperlink ref="A449" r:id="rId150" display="https://betrady.online/" xr:uid="{1B9B1187-BE58-4AB6-AB58-E032E28ADEC2}"/>
+    <hyperlink ref="A450" r:id="rId151" display="https://fiipkart-summer.lovable.app/" xr:uid="{6D4BCADB-A456-440C-B244-61F3AC515CD7}"/>
+    <hyperlink ref="A452" r:id="rId152" xr:uid="{E198A9E9-F98A-4474-AECE-3016ED06D033}"/>
+    <hyperlink ref="A453" r:id="rId153" display="https://magenta-heron-153902.hostingersite.com/" xr:uid="{F04AC313-32A4-49F6-9735-B56B7053A1F8}"/>
+    <hyperlink ref="A454" r:id="rId154" xr:uid="{5A477327-F60A-4B1F-B201-985D79BD8775}"/>
+    <hyperlink ref="A455" r:id="rId155" xr:uid="{47158B01-1788-4192-8FB3-7A642C701780}"/>
+    <hyperlink ref="A456" r:id="rId156" display="https://www.flipkartmarchsale.in/" xr:uid="{66220ACB-1093-460E-8519-74761A1EE8DF}"/>
+    <hyperlink ref="A457" r:id="rId157" xr:uid="{40B37356-0F0E-4569-9A60-304ACDF5E8A9}"/>
+    <hyperlink ref="A464" r:id="rId158" xr:uid="{2246594F-0BFC-491A-8335-11CD82E66C33}"/>
+    <hyperlink ref="A465" r:id="rId159" xr:uid="{B6269A59-A82A-4306-A5C0-CBD5DB5A5FB9}"/>
+    <hyperlink ref="A467" r:id="rId160" xr:uid="{A15407B8-DE2D-4645-A5CF-EBDB2C3D2CFD}"/>
+    <hyperlink ref="A468" r:id="rId161" xr:uid="{50A935C0-2F94-447E-808F-C62582CFC903}"/>
+    <hyperlink ref="A469" r:id="rId162" xr:uid="{66AEAB67-754E-47D8-A494-F586E1829510}"/>
+    <hyperlink ref="A470" r:id="rId163" xr:uid="{98E3B68A-B453-4DC2-B479-E5AE0A00A948}"/>
+    <hyperlink ref="A471" r:id="rId164" display="https://mediumvioletred-rail-865467.hostingersite.com/" xr:uid="{99E68E58-217B-4B07-8846-6371FE797D0A}"/>
+    <hyperlink ref="A472" r:id="rId165" display="https://healthprime.fun/" xr:uid="{A9EF7D20-8E71-474A-B08A-B6511D70993E}"/>
+    <hyperlink ref="A473" r:id="rId166" display="https://plum-lobster-541291.hostingersite.com/" xr:uid="{9C48409B-A44C-41AE-9A3B-C5C3608FC8FD}"/>
+    <hyperlink ref="A474" r:id="rId167" xr:uid="{C83AEB37-67C2-4A5A-86EE-F382DE5AB006}"/>
+    <hyperlink ref="A475" r:id="rId168" xr:uid="{CBE2175F-9647-442F-B51F-0C361C71F97B}"/>
+    <hyperlink ref="A477" r:id="rId169" xr:uid="{02252EC6-FF65-4C04-9EB0-78BA914777F3}"/>
+    <hyperlink ref="A478" r:id="rId170" xr:uid="{A027763B-6966-4A9E-B434-73705A78E6E2}"/>
+    <hyperlink ref="A479" r:id="rId171" xr:uid="{12870190-F4E8-4ACC-B5CD-138A52774920}"/>
+    <hyperlink ref="A480" r:id="rId172" xr:uid="{DEEEF48B-486C-4467-9F0A-703940D111C2}"/>
+    <hyperlink ref="A481" r:id="rId173" xr:uid="{F6DFFAEE-62E9-484B-A82D-D05D9E0473EA}"/>
+    <hyperlink ref="A482" r:id="rId174" xr:uid="{2FAADB78-55BF-408D-A4F5-035D4491F8AA}"/>
+    <hyperlink ref="A483" r:id="rId175" xr:uid="{20E948BE-7EB3-41D3-99F2-FB061E2C655D}"/>
+    <hyperlink ref="A484" r:id="rId176" xr:uid="{F3BDF017-D2C3-4D8F-ADDD-419BC5E7D6F5}"/>
+    <hyperlink ref="A485" r:id="rId177" xr:uid="{AFD9F105-D09C-41D4-91FA-A1ADD6F83C5A}"/>
+    <hyperlink ref="A486" r:id="rId178" xr:uid="{2A0A0FE5-B9BD-418E-86DD-D2F425CC69AD}"/>
+    <hyperlink ref="A492" r:id="rId179" xr:uid="{D3582409-A6AC-4F71-8F92-E8C7883AB73A}"/>
+    <hyperlink ref="A493" r:id="rId180" xr:uid="{6D91B0E3-2F1B-49C0-8976-178186AF1A70}"/>
+    <hyperlink ref="A494" r:id="rId181" xr:uid="{08480B4A-B583-4D2A-9A92-0CA262A70CBE}"/>
+    <hyperlink ref="B337" r:id="rId182" display="https://myip.ms/view/countries/FRA/Internet_Usage_Statistics_France.html" xr:uid="{F2737594-B0B1-499C-9C64-78091118CFA5}"/>
+    <hyperlink ref="B340" r:id="rId183" display="https://myip.ms/view/countries/USA/Internet_Usage_Statistics_USA.html" xr:uid="{384CEC91-81BC-4D52-ADA5-6DFC320BB9BA}"/>
+    <hyperlink ref="B370" r:id="rId184" display="https://myip.ms/view/countries/DEU/Internet_Usage_Statistics_Germany.html" xr:uid="{C49C907F-14E8-414C-96AB-FD6ADD032D1C}"/>
+    <hyperlink ref="B371" r:id="rId185" display="https://myip.ms/view/countries/FRA/Internet_Usage_Statistics_France.html" xr:uid="{67204D82-5BF6-4BB8-8FB5-CFD5EBC0EDB5}"/>
+    <hyperlink ref="B372" r:id="rId186" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{78B1A8AA-423F-42D7-8447-1330B01412D1}"/>
+    <hyperlink ref="B373" r:id="rId187" display="https://myip.ms/view/countries/FRA/Internet_Usage_Statistics_France.html" xr:uid="{DD02A525-310A-4583-BE2D-405D08E5E12F}"/>
+    <hyperlink ref="B374" r:id="rId188" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{A13066FC-25B6-4351-BF2B-A87618F35853}"/>
+    <hyperlink ref="B375" r:id="rId189" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{5CF2DBA8-8FE4-4A82-85FB-7841BCE823F5}"/>
+    <hyperlink ref="B378" r:id="rId190" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{B25FA224-1524-4E9B-AE27-41143DF6223E}"/>
+    <hyperlink ref="B379" r:id="rId191" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{E8571A1D-2B16-4088-8D7C-5E6CB2018ECC}"/>
+    <hyperlink ref="B428" r:id="rId192" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{4BD7D44C-BEF7-47A4-99B5-16D6479FAC76}"/>
+    <hyperlink ref="B429" r:id="rId193" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{38D270BC-DEEE-468E-9B8A-ED46E9ECA658}"/>
+    <hyperlink ref="B430" r:id="rId194" display="https://myip.ms/view/countries/IND/Internet_Usage_Statistics_India.html" xr:uid="{FB8153D6-CBA3-48AF-8F83-1FB69AC94C53}"/>
+    <hyperlink ref="B542" r:id="rId195" display="https://myip.ms/view/countries/USA/Internet_Usage_Statistics_USA.html" xr:uid="{CB22E3D8-6CCC-44E6-B92C-A36783A5BC42}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId196"/>

--- a/excel_data/Website_mapping.xlsx
+++ b/excel_data/Website_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pixeltruth-my.sharepoint.com/personal/shubhankar_shukla_pixeltruth_com/Documents/Code_Hub/Testing_Code/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{AB1C9699-5AD3-4A07-AFFC-BDB08EC9955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E689FE5-3B36-4523-9D7F-92B3B6C62633}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{AB1C9699-5AD3-4A07-AFFC-BDB08EC9955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04842037-9109-43E3-9E58-FDF4B2716F34}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44ED9281-8F1E-4DBD-9F57-CE2FABFA19EC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="418">
   <si>
     <t>website_url</t>
   </si>
@@ -330,9 +330,6 @@
     <t>https://www.efficientcheckout.ru</t>
   </si>
   <si>
-    <t>https://windpower33.com</t>
-  </si>
-  <si>
     <t>https://smartfarming77.com</t>
   </si>
   <si>
@@ -456,9 +453,6 @@
     <t>https://measho003.vercel.app</t>
   </si>
   <si>
-    <t>https://bigbangdeal.xyz/scratch</t>
-  </si>
-  <si>
     <t>https://scrth-me-now.free.nf/?i=2</t>
   </si>
   <si>
@@ -546,9 +540,6 @@
     <t>Sweden</t>
   </si>
   <si>
-    <t>https://ttnamaksaaltpukch.us.cc</t>
-  </si>
-  <si>
     <t>https://www.hdappsjzbxbhsjjsbd.com</t>
   </si>
   <si>
@@ -573,9 +564,6 @@
     <t>https://www.dhdcexpress.com</t>
   </si>
   <si>
-    <t>https://aerochillx.com</t>
-  </si>
-  <si>
     <t>https://vishvbookpublishers.xy</t>
   </si>
   <si>
@@ -795,18 +783,12 @@
     <t>https://goldstrikee.top</t>
   </si>
   <si>
-    <t>https://ghadiqksaghadi.in</t>
-  </si>
-  <si>
     <t>https://xeno9.ru</t>
   </si>
   <si>
     <t>https://nelo9.ru</t>
   </si>
   <si>
-    <t>https://www.awerwourarmamxzwm.com</t>
-  </si>
-  <si>
     <t>Bangladesh</t>
   </si>
   <si>
@@ -828,9 +810,6 @@
     <t>https://summer.supersalepro.com/e09ee6afd6/OFFER/meesho</t>
   </si>
   <si>
-    <t>https://offer-sale.xyz/Predatorop/OFFER/scratch-tamil</t>
-  </si>
-  <si>
     <t>https://bio.golynk.in/8e2a02</t>
   </si>
   <si>
@@ -999,9 +978,6 @@
     <t>https://zivo9.ru</t>
   </si>
   <si>
-    <t>https://www.tucchemu-gj206.com</t>
-  </si>
-  <si>
     <t>https://www.ssyou-999.org</t>
   </si>
   <si>
@@ -1026,9 +1002,6 @@
     <t>https://www.e1utr-v6ianw8ds.com</t>
   </si>
   <si>
-    <t>https://www.bundabergvn88.com</t>
-  </si>
-  <si>
     <t>https://www.bazmoterscngzt22.cam</t>
   </si>
   <si>
@@ -1227,7 +1200,97 @@
     <t>https://new.deals-offer-india.org/944186c8</t>
   </si>
   <si>
-    <t xml:space="preserve">France </t>
+    <t>https://futuretrades.co.in</t>
+  </si>
+  <si>
+    <t>https://kkingffisher017hs.us.cc</t>
+  </si>
+  <si>
+    <t>https://merce.longnetwork17promax.com</t>
+  </si>
+  <si>
+    <t>https://www.f8haribo9fc.com</t>
+  </si>
+  <si>
+    <t>https://www.zonlasglk.com</t>
+  </si>
+  <si>
+    <t>https://www.tnelnsco.com</t>
+  </si>
+  <si>
+    <t>https://ikeavuwxzkkww2028.com</t>
+  </si>
+  <si>
+    <t>https://vellshab-neww2026.netlify.app</t>
+  </si>
+  <si>
+    <t>https://air472-cooler.com</t>
+  </si>
+  <si>
+    <t>https://myfanindia-loot.shop/newshop</t>
+  </si>
+  <si>
+    <t>https://summer.supersalepro.com/0cfb7b1dca/OFFER/fk99</t>
+  </si>
+  <si>
+    <t>https://flipkartbigsavings.shop/offersale</t>
+  </si>
+  <si>
+    <t>https://kitchen.summardelzs.shop</t>
+  </si>
+  <si>
+    <t>https://akkitchenstov.vercel.app/#/home</t>
+  </si>
+  <si>
+    <t>https://greenyellow-swallow-599623.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://blanchedalmond-squirrel-812394.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://lightsteelblue-kudu-753881.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://lightblue-aardvark-659062.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://bisque-wren-162501hostingersitecom.vercel.app</t>
+  </si>
+  <si>
+    <t>https://new.deals-offer-india.org/6c35880d</t>
+  </si>
+  <si>
+    <t>https://lightsteelblue-swallow-231434.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://flipkart-sale-2.myshopify.com</t>
+  </si>
+  <si>
+    <t>https://big-sale-offer.com/eN4N3V/OFFER/mamypoko</t>
+  </si>
+  <si>
+    <t>https://big-sale-offer.live/c5qYE/OFFER/oneplus11r</t>
+  </si>
+  <si>
+    <t>https://lightcoral-sheep-855345.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://stircrazy.live</t>
+  </si>
+  <si>
+    <t>https://darkgreen-dinosaur-470838.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://fiilpkerrtbiigsel.shop/offersale</t>
+  </si>
+  <si>
+    <t>https://darkesttorquoise-ratatoi-3462938.vercel.app</t>
+  </si>
+  <si>
+    <t>https://new.sale-start.com/Nbbvv/OFFER/fk99-allupi</t>
+  </si>
+  <si>
+    <t>https://dhamaka-offer.com/Unique/OFFER/meesho99</t>
   </si>
 </sst>
 </file>
@@ -1325,7 +1388,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1351,11 +1414,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1372,10 +1434,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1742,10 +1800,10 @@
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1753,10 +1811,10 @@
       <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1764,10 +1822,10 @@
       <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1775,10 +1833,10 @@
       <c r="A9" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1786,10 +1844,10 @@
       <c r="A10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1797,10 +1855,10 @@
       <c r="A11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1808,10 +1866,10 @@
       <c r="A12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="B12" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1819,10 +1877,10 @@
       <c r="A13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1830,10 +1888,10 @@
       <c r="A14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1841,10 +1899,10 @@
       <c r="A15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1852,10 +1910,10 @@
       <c r="A16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1863,10 +1921,10 @@
       <c r="A17" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1874,10 +1932,10 @@
       <c r="A18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1885,10 +1943,10 @@
       <c r="A19" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="B19" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1896,10 +1954,10 @@
       <c r="A20" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="B20" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1907,10 +1965,10 @@
       <c r="A21" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="B21" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1918,10 +1976,10 @@
       <c r="A22" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1929,10 +1987,10 @@
       <c r="A23" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="B23" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1940,10 +1998,10 @@
       <c r="A24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B24" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1951,10 +2009,10 @@
       <c r="A25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1962,10 +2020,10 @@
       <c r="A26" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="B26" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1973,10 +2031,10 @@
       <c r="A27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="B27" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1984,10 +2042,10 @@
       <c r="A28" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="10" t="s">
+      <c r="B28" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1995,10 +2053,10 @@
       <c r="A29" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" s="10" t="s">
+      <c r="B29" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2006,10 +2064,10 @@
       <c r="A30" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="10" t="s">
+      <c r="B30" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2017,10 +2075,10 @@
       <c r="A31" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" s="10" t="s">
+      <c r="B31" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2028,10 +2086,10 @@
       <c r="A32" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="10" t="s">
+      <c r="B32" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2039,10 +2097,10 @@
       <c r="A33" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="10" t="s">
+      <c r="B33" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2050,10 +2108,10 @@
       <c r="A34" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="10" t="s">
+      <c r="B34" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2061,10 +2119,10 @@
       <c r="A35" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="10" t="s">
+      <c r="B35" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2072,10 +2130,10 @@
       <c r="A36" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="10" t="s">
+      <c r="B36" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2083,10 +2141,10 @@
       <c r="A37" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="10" t="s">
+      <c r="B37" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2094,10 +2152,10 @@
       <c r="A38" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="10" t="s">
+      <c r="B38" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2105,10 +2163,10 @@
       <c r="A39" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="10" t="s">
+      <c r="B39" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2116,10 +2174,10 @@
       <c r="A40" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="10" t="s">
+      <c r="B40" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2127,10 +2185,10 @@
       <c r="A41" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="10" t="s">
+      <c r="B41" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2138,10 +2196,10 @@
       <c r="A42" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="10" t="s">
+      <c r="B42" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2149,10 +2207,10 @@
       <c r="A43" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="10" t="s">
+      <c r="B43" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2160,10 +2218,10 @@
       <c r="A44" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2171,10 +2229,10 @@
       <c r="A45" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2182,10 +2240,10 @@
       <c r="A46" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="10" t="s">
+      <c r="B46" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2193,10 +2251,10 @@
       <c r="A47" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="10" t="s">
+      <c r="B47" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="12" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2204,10 +2262,10 @@
       <c r="A48" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" s="10" t="s">
+      <c r="B48" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2215,10 +2273,10 @@
       <c r="A49" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="10" t="s">
+      <c r="B49" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2226,10 +2284,10 @@
       <c r="A50" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="10" t="s">
+      <c r="B50" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2237,10 +2295,10 @@
       <c r="A51" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C51" s="10" t="s">
+      <c r="B51" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2248,10 +2306,10 @@
       <c r="A52" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="10" t="s">
+      <c r="B52" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="12" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2259,10 +2317,10 @@
       <c r="A53" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C53" s="10" t="s">
+      <c r="B53" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C53" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2270,10 +2328,10 @@
       <c r="A54" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="10" t="s">
+      <c r="B54" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2281,10 +2339,10 @@
       <c r="A55" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="10" t="s">
+      <c r="B55" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2292,10 +2350,10 @@
       <c r="A56" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B56" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C56" s="10" t="s">
+      <c r="B56" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2303,10 +2361,10 @@
       <c r="A57" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B57" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="10" t="s">
+      <c r="B57" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2314,10 +2372,10 @@
       <c r="A58" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C58" s="10" t="s">
+      <c r="B58" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C58" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2325,10 +2383,10 @@
       <c r="A59" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C59" s="10" t="s">
+      <c r="B59" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C59" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2336,10 +2394,10 @@
       <c r="A60" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C60" s="10" t="s">
+      <c r="B60" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C60" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2347,10 +2405,10 @@
       <c r="A61" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="10" t="s">
+      <c r="B61" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2358,10 +2416,10 @@
       <c r="A62" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C62" s="10" t="s">
+      <c r="B62" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2369,10 +2427,10 @@
       <c r="A63" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" s="10" t="s">
+      <c r="B63" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2380,10 +2438,10 @@
       <c r="A64" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="10" t="s">
+      <c r="B64" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2391,10 +2449,10 @@
       <c r="A65" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C65" s="10" t="s">
+      <c r="B65" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2402,10 +2460,10 @@
       <c r="A66" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B66" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C66" s="10" t="s">
+      <c r="B66" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2413,10 +2471,10 @@
       <c r="A67" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B67" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C67" s="10" t="s">
+      <c r="B67" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C67" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2424,10 +2482,10 @@
       <c r="A68" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C68" s="10" t="s">
+      <c r="B68" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2435,10 +2493,10 @@
       <c r="A69" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C69" s="10" t="s">
+      <c r="B69" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C69" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2446,10 +2504,10 @@
       <c r="A70" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="10" t="s">
+      <c r="B70" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2457,10 +2515,10 @@
       <c r="A71" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C71" s="10" t="s">
+      <c r="B71" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2468,10 +2526,10 @@
       <c r="A72" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C72" s="10" t="s">
+      <c r="B72" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2479,10 +2537,10 @@
       <c r="A73" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C73" s="10" t="s">
+      <c r="B73" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2490,10 +2548,10 @@
       <c r="A74" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C74" s="10" t="s">
+      <c r="B74" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2501,8 +2559,8 @@
       <c r="A75" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>217</v>
+      <c r="B75" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C75" s="9" t="s">
         <v>58</v>
@@ -2512,7 +2570,7 @@
       <c r="A76" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B76" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C76" s="9" t="s">
@@ -2523,10 +2581,10 @@
       <c r="A77" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B77" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C77" s="10" t="s">
+      <c r="B77" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C77" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2534,7 +2592,7 @@
       <c r="A78" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C78" s="9" t="s">
@@ -2545,7 +2603,7 @@
       <c r="A79" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C79" s="9" t="s">
@@ -2556,7 +2614,7 @@
       <c r="A80" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C80" s="9" t="s">
@@ -2567,7 +2625,7 @@
       <c r="A81" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C81" s="9" t="s">
@@ -2578,8 +2636,8 @@
       <c r="A82" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B82" s="10" t="s">
-        <v>217</v>
+      <c r="B82" s="12" t="s">
+        <v>3</v>
       </c>
       <c r="C82" s="9" t="s">
         <v>58</v>
@@ -2587,9 +2645,9 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B83" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C83" s="9" t="s">
@@ -2598,10 +2656,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B84" s="10" t="s">
-        <v>3</v>
+        <v>98</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>58</v>
@@ -2611,8 +2669,8 @@
       <c r="A85" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B85" s="10" t="s">
-        <v>217</v>
+      <c r="B85" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="C85" s="9" t="s">
         <v>58</v>
@@ -2622,8 +2680,8 @@
       <c r="A86" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B86" s="10" t="s">
-        <v>55</v>
+      <c r="B86" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C86" s="9" t="s">
         <v>58</v>
@@ -2631,10 +2689,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B87" s="10" t="s">
-        <v>217</v>
+        <v>167</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C87" s="9" t="s">
         <v>58</v>
@@ -2642,10 +2700,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>176</v>
+        <v>168</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C88" s="9" t="s">
         <v>58</v>
@@ -2653,10 +2711,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="B89" s="10" t="s">
-        <v>217</v>
+        <v>169</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>58</v>
@@ -2664,10 +2722,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B90" s="10" t="s">
-        <v>217</v>
+        <v>170</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>58</v>
@@ -2675,10 +2733,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>217</v>
+        <v>171</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>58</v>
@@ -2686,10 +2744,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B92" s="10" t="s">
-        <v>217</v>
+        <v>172</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>58</v>
@@ -2699,987 +2757,987 @@
       <c r="A93" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B93" s="10" t="s">
-        <v>217</v>
+      <c r="B93" s="12" t="s">
+        <v>3</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B94" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C94" s="9" t="s">
-        <v>58</v>
+      <c r="B94" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="9" t="s">
+      <c r="B97" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C120" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B96" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B97" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="B98" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B99" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B100" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="B101" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C101" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B102" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C102" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B103" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C103" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B104" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C104" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="B105" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C105" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="B107" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="B108" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C109" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="B110" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="B111" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C111" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="B112" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C112" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="B113" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C113" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="B114" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C114" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B115" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C115" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C116" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="B117" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C117" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="B118" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C118" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C119" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="B120" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C120" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B121" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C121" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="B122" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C122" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="B123" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C123" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B124" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C124" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="B125" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C125" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="10" t="s">
+      <c r="B130" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C134" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B138" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="B126" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C126" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C127" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B128" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C128" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="B129" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C129" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C130" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="B131" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C131" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="B132" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C132" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="B133" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C133" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="10" t="s">
+      <c r="C138" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="B134" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C134" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="B135" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="C135" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B136" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C136" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="B137" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C137" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="B138" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C138" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="B139" s="10" t="s">
-        <v>217</v>
+      <c r="B139" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C139" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="B140" s="10" t="s">
-        <v>217</v>
+      <c r="A140" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="C140" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="B141" s="10" t="s">
-        <v>217</v>
+      <c r="A141" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C141" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="B142" s="10" t="s">
-        <v>334</v>
+      <c r="A142" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C142" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="B143" s="10" t="s">
-        <v>217</v>
+      <c r="A143" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="B143" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C143" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="B144" s="10" t="s">
-        <v>323</v>
+      <c r="A144" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>3</v>
       </c>
       <c r="C144" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="B145" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C145" s="9" t="s">
+      <c r="A145" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C145" s="12" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B146" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C146" s="10" t="s">
-        <v>59</v>
+      <c r="A146" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B147" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C147" s="10" t="s">
-        <v>59</v>
+      <c r="A147" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B148" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C148" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B149" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C149" s="10" t="s">
+      <c r="A149" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C149" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B151" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B150" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C150" s="10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="B151" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C151" s="10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" s="13" t="s">
+      <c r="B154" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B152" s="10" t="s">
+      <c r="B155" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C152" s="10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B153" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C153" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B154" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C154" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B155" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C155" s="10" t="s">
+      <c r="C155" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B156" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C156" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C156" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B157" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C157" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C157" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B158" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C158" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C158" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B159" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C159" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B159" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C159" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B160" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C160" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C160" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B161" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C161" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C161" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B162" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C162" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B162" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C162" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B163" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C163" s="10" t="s">
+      <c r="A163" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B163" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C163" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B164" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C164" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B164" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C164" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B165" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C165" s="10" t="s">
+      <c r="A165" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C165" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B166" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C166" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C166" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B167" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C167" s="10" t="s">
+      <c r="A167" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C167" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B168" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C168" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C168" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B169" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C169" s="10" t="s">
+      <c r="A169" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C169" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B170" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C170" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C170" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B171" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C171" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C171" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="B172" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C172" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C172" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="B173" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C173" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" s="13" t="s">
+      <c r="B176" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B174" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C174" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" s="13" t="s">
+      <c r="B177" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B175" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C175" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" s="13" t="s">
+      <c r="B178" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B176" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C176" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A177" s="9" t="s">
+      <c r="B179" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C179" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B177" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C177" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178" s="13" t="s">
+      <c r="B180" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C180" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B178" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C178" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A179" s="13" t="s">
+      <c r="B181" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B179" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C179" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A180" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B180" s="10" t="s">
+      <c r="B182" s="12" t="s">
         <v>52</v>
-      </c>
-      <c r="C180" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B181" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C181" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="B182" s="10" t="s">
-        <v>3</v>
       </c>
       <c r="C182" s="9" t="s">
         <v>59</v>
@@ -3687,186 +3745,186 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B183" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C183" s="10" t="s">
-        <v>218</v>
+        <v>136</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A184" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B184" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C184" s="10" t="s">
-        <v>218</v>
+      <c r="A184" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C184" s="9" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="B185" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C185" s="10" t="s">
-        <v>59</v>
+      <c r="A185" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B186" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C186" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C186" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A187" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="B187" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C187" s="10" t="s">
+      <c r="A187" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C187" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B188" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C188" s="10" t="s">
+      <c r="A188" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C188" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B189" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C189" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" s="13" t="s">
+      <c r="B192" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C192" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B190" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C190" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" s="13" t="s">
+      <c r="B193" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B191" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C191" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" s="13" t="s">
+      <c r="B194" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B192" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C192" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" s="13" t="s">
+      <c r="B195" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B193" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C193" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194" s="13" t="s">
+      <c r="B196" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B194" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C194" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" s="13" t="s">
+      <c r="B197" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B195" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C195" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" s="9" t="s">
+      <c r="B198" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B196" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C196" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B197" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C197" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B198" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C198" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="B199" s="10" t="s">
-        <v>102</v>
+      <c r="B199" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C199" s="9" t="s">
         <v>59</v>
@@ -3874,153 +3932,153 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B200" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C202" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B200" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C200" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A201" s="13" t="s">
+      <c r="B203" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B201" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C201" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A202" s="9" t="s">
+      <c r="B204" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C204" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B202" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C202" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A203" s="13" t="s">
+      <c r="B205" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B203" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C203" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A204" s="13" t="s">
+      <c r="B206" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C206" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B204" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C204" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A205" s="9" t="s">
+      <c r="B207" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B205" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C205" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A206" s="13" t="s">
+      <c r="B208" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C208" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B206" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C206" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A207" s="13" t="s">
+      <c r="B209" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B207" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C207" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A208" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="B208" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C208" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A209" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B209" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C209" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A210" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B210" s="10" t="s">
-        <v>217</v>
+      <c r="B210" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C210" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A211" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="B211" s="10" t="s">
-        <v>217</v>
+      <c r="A211" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C211" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A212" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B212" s="10" t="s">
-        <v>217</v>
+      <c r="A212" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B212" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C212" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="B213" s="10" t="s">
-        <v>217</v>
+      <c r="A213" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C213" s="9" t="s">
         <v>59</v>
@@ -4028,32 +4086,32 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="B214" s="10" t="s">
-        <v>102</v>
+        <v>183</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C214" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A215" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="B215" s="10" t="s">
-        <v>102</v>
+      <c r="A215" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C215" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A216" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B216" s="10" t="s">
-        <v>217</v>
+      <c r="A216" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C216" s="9" t="s">
         <v>59</v>
@@ -4061,10 +4119,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B217" s="10" t="s">
-        <v>102</v>
+        <v>186</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C217" s="9" t="s">
         <v>59</v>
@@ -4072,32 +4130,32 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B218" s="10" t="s">
-        <v>217</v>
+        <v>187</v>
+      </c>
+      <c r="B218" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C218" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A219" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B219" s="10" t="s">
+      <c r="A219" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B219" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B220" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="C219" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A220" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="B220" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="C220" s="9" t="s">
         <v>59</v>
@@ -4105,439 +4163,439 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B221" s="10" t="s">
-        <v>102</v>
+        <v>190</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C221" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A222" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="B222" s="10" t="s">
-        <v>217</v>
+      <c r="A222" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B222" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C222" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A223" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B223" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C223" s="10" t="s">
+      <c r="A223" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C223" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="B224" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C224" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B224" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C224" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A225" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B225" s="10" t="s">
+      <c r="A225" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B225" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B226" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C225" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A226" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="B226" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C226" s="10" t="s">
+      <c r="C226" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="B227" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C227" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B227" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C227" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B228" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C228" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B228" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C228" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B229" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C229" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B229" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C229" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A230" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="B230" s="9" t="s">
+      <c r="A230" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B231" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C230" s="10" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A231" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B231" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C231" s="10" t="s">
-        <v>216</v>
+      <c r="C231" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A232" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B232" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C232" s="10" t="s">
-        <v>59</v>
+      <c r="A232" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B232" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B233" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C233" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C233" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="B234" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C234" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B234" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C234" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B235" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C235" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B235" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C235" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="B236" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C236" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B236" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C236" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B237" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C237" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B237" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C237" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B238" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B239" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B240" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C240" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B238" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C238" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A239" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="B239" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C239" s="10" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A240" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="B240" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C240" s="10" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A241" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="B241" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C241" s="10" t="s">
+      <c r="A241" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B241" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C241" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A242" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="B242" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C242" s="10" t="s">
+      <c r="A242" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="B242" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C242" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="B243" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C243" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B243" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C243" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="B244" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="C244" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B244" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C244" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B246" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B247" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C247" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B248" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C248" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B249" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C249" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="B245" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C245" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A246" s="13" t="s">
+      <c r="B250" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C250" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B246" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C246" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A247" s="13" t="s">
+      <c r="B251" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C251" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="B247" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C247" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A248" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B248" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C248" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A249" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="B249" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C249" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A250" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="B250" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C250" s="10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A251" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="B251" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C251" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A252" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="B252" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C252" s="10" t="s">
+      <c r="B252" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C252" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="B253" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C253" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B253" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C253" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A254" s="13" t="s">
+      <c r="A254" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B254" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C254" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B255" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C255" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B256" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C256" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B257" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C257" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B258" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="B259" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B254" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C254" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A255" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="B255" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C255" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A256" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="B256" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C256" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A257" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="B257" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C257" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A258" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="B258" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C258" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A259" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="B259" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C259" s="10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A260" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="B260" s="10" t="s">
-        <v>102</v>
+      <c r="B260" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C260" s="9" t="s">
         <v>59</v>
@@ -4545,10 +4603,10 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="B261" s="10" t="s">
-        <v>219</v>
+        <v>258</v>
+      </c>
+      <c r="B261" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C261" s="9" t="s">
         <v>59</v>
@@ -4556,10 +4614,10 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="B262" s="10" t="s">
-        <v>217</v>
+        <v>256</v>
+      </c>
+      <c r="B262" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C262" s="9" t="s">
         <v>59</v>
@@ -4567,10 +4625,10 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="B263" s="10" t="s">
-        <v>217</v>
+        <v>259</v>
+      </c>
+      <c r="B263" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C263" s="9" t="s">
         <v>59</v>
@@ -4578,10 +4636,10 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="B264" s="10" t="s">
-        <v>217</v>
+        <v>260</v>
+      </c>
+      <c r="B264" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C264" s="9" t="s">
         <v>59</v>
@@ -4589,21 +4647,21 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="B265" s="10" t="s">
-        <v>102</v>
+        <v>261</v>
+      </c>
+      <c r="B265" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C265" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A266" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="B266" s="10" t="s">
-        <v>217</v>
+      <c r="A266" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B266" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C266" s="9" t="s">
         <v>59</v>
@@ -4611,10 +4669,10 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="B267" s="10" t="s">
-        <v>102</v>
+        <v>263</v>
+      </c>
+      <c r="B267" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C267" s="9" t="s">
         <v>59</v>
@@ -4622,10 +4680,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="B268" s="10" t="s">
-        <v>217</v>
+        <v>264</v>
+      </c>
+      <c r="B268" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C268" s="9" t="s">
         <v>59</v>
@@ -4633,21 +4691,21 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="B269" s="10" t="s">
-        <v>217</v>
+        <v>265</v>
+      </c>
+      <c r="B269" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C269" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A270" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="B270" s="10" t="s">
-        <v>217</v>
+      <c r="A270" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="B270" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C270" s="9" t="s">
         <v>59</v>
@@ -4655,10 +4713,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="B271" s="10" t="s">
-        <v>217</v>
+        <v>267</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C271" s="9" t="s">
         <v>59</v>
@@ -4666,10 +4724,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="B272" s="10" t="s">
-        <v>102</v>
+        <v>268</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C272" s="9" t="s">
         <v>59</v>
@@ -4677,10 +4735,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="B273" s="10" t="s">
-        <v>102</v>
+        <v>271</v>
+      </c>
+      <c r="B273" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C273" s="9" t="s">
         <v>59</v>
@@ -4688,10 +4746,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="B274" s="10" t="s">
-        <v>217</v>
+        <v>272</v>
+      </c>
+      <c r="B274" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C274" s="9" t="s">
         <v>59</v>
@@ -4699,10 +4757,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="B275" s="10" t="s">
-        <v>102</v>
+        <v>273</v>
+      </c>
+      <c r="B275" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C275" s="9" t="s">
         <v>59</v>
@@ -4710,21 +4768,21 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="B276" s="10" t="s">
-        <v>102</v>
+        <v>274</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C276" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A277" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="B277" s="10" t="s">
-        <v>217</v>
+      <c r="A277" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="B277" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C277" s="9" t="s">
         <v>59</v>
@@ -4732,10 +4790,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="B278" s="10" t="s">
-        <v>217</v>
+        <v>276</v>
+      </c>
+      <c r="B278" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C278" s="9" t="s">
         <v>59</v>
@@ -4743,21 +4801,21 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B279" s="10" t="s">
-        <v>217</v>
+        <v>277</v>
+      </c>
+      <c r="B279" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C279" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A280" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="B280" s="10" t="s">
-        <v>102</v>
+      <c r="A280" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C280" s="9" t="s">
         <v>59</v>
@@ -4765,10 +4823,10 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="B281" s="10" t="s">
-        <v>217</v>
+        <v>279</v>
+      </c>
+      <c r="B281" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C281" s="9" t="s">
         <v>59</v>
@@ -4776,10 +4834,10 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="B282" s="10" t="s">
-        <v>217</v>
+        <v>280</v>
+      </c>
+      <c r="B282" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C282" s="9" t="s">
         <v>59</v>
@@ -4787,10 +4845,10 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="B283" s="10" t="s">
-        <v>217</v>
+        <v>281</v>
+      </c>
+      <c r="B283" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C283" s="9" t="s">
         <v>59</v>
@@ -4798,10 +4856,10 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="B284" s="10" t="s">
-        <v>217</v>
+        <v>282</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C284" s="9" t="s">
         <v>59</v>
@@ -4809,10 +4867,10 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="B285" s="10" t="s">
-        <v>217</v>
+        <v>283</v>
+      </c>
+      <c r="B285" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C285" s="9" t="s">
         <v>59</v>
@@ -4820,10 +4878,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="B286" s="10" t="s">
-        <v>217</v>
+        <v>284</v>
+      </c>
+      <c r="B286" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C286" s="9" t="s">
         <v>59</v>
@@ -4831,10 +4889,10 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="B287" s="10" t="s">
-        <v>102</v>
+        <v>285</v>
+      </c>
+      <c r="B287" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C287" s="9" t="s">
         <v>59</v>
@@ -4842,32 +4900,32 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="B288" s="10" t="s">
-        <v>217</v>
+        <v>286</v>
+      </c>
+      <c r="B288" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C288" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A289" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="B289" s="10" t="s">
-        <v>217</v>
+      <c r="A289" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C289" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A290" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="B290" s="10" t="s">
-        <v>217</v>
+      <c r="A290" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C290" s="9" t="s">
         <v>59</v>
@@ -4875,10 +4933,10 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="B291" s="10" t="s">
-        <v>217</v>
+        <v>289</v>
+      </c>
+      <c r="B291" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C291" s="9" t="s">
         <v>59</v>
@@ -4886,10 +4944,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="B292" s="10" t="s">
-        <v>217</v>
+        <v>290</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C292" s="9" t="s">
         <v>59</v>
@@ -4897,32 +4955,32 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="B293" s="10" t="s">
-        <v>217</v>
+        <v>291</v>
+      </c>
+      <c r="B293" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C293" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A294" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="B294" s="10" t="s">
-        <v>102</v>
+      <c r="A294" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C294" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A295" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="B295" s="10" t="s">
-        <v>217</v>
+      <c r="A295" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="B295" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C295" s="9" t="s">
         <v>59</v>
@@ -4930,10 +4988,10 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="B296" s="10" t="s">
-        <v>102</v>
+        <v>294</v>
+      </c>
+      <c r="B296" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C296" s="9" t="s">
         <v>59</v>
@@ -4941,10 +4999,10 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="B297" s="10" t="s">
-        <v>217</v>
+        <v>295</v>
+      </c>
+      <c r="B297" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C297" s="9" t="s">
         <v>59</v>
@@ -4952,10 +5010,10 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="B298" s="10" t="s">
-        <v>217</v>
+        <v>296</v>
+      </c>
+      <c r="B298" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C298" s="9" t="s">
         <v>59</v>
@@ -4963,10 +5021,10 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="B299" s="10" t="s">
-        <v>217</v>
+        <v>297</v>
+      </c>
+      <c r="B299" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C299" s="9" t="s">
         <v>59</v>
@@ -4974,10 +5032,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="B300" s="10" t="s">
-        <v>217</v>
+        <v>298</v>
+      </c>
+      <c r="B300" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C300" s="9" t="s">
         <v>59</v>
@@ -4985,10 +5043,10 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="B301" s="10" t="s">
-        <v>102</v>
+        <v>299</v>
+      </c>
+      <c r="B301" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C301" s="9" t="s">
         <v>59</v>
@@ -4996,10 +5054,10 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="B302" s="10" t="s">
-        <v>217</v>
+        <v>300</v>
+      </c>
+      <c r="B302" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C302" s="9" t="s">
         <v>59</v>
@@ -5007,10 +5065,10 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="B303" s="10" t="s">
-        <v>217</v>
+        <v>301</v>
+      </c>
+      <c r="B303" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C303" s="9" t="s">
         <v>59</v>
@@ -5018,10 +5076,10 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="B304" s="10" t="s">
-        <v>102</v>
+        <v>302</v>
+      </c>
+      <c r="B304" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C304" s="9" t="s">
         <v>59</v>
@@ -5029,10 +5087,10 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="B305" s="10" t="s">
-        <v>217</v>
+        <v>303</v>
+      </c>
+      <c r="B305" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C305" s="9" t="s">
         <v>59</v>
@@ -5040,10 +5098,10 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="B306" s="10" t="s">
-        <v>102</v>
+        <v>304</v>
+      </c>
+      <c r="B306" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C306" s="9" t="s">
         <v>59</v>
@@ -5051,9 +5109,9 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="B307" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B307" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C307" s="9" t="s">
@@ -5061,22 +5119,22 @@
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A308" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="B308" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C308" s="10" t="s">
-        <v>218</v>
+      <c r="A308" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="B308" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C308" s="12" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="B309" s="10" t="s">
-        <v>217</v>
+        <v>326</v>
+      </c>
+      <c r="B309" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C309" s="9" t="s">
         <v>59</v>
@@ -5084,9 +5142,9 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="B310" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="B310" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C310" s="9" t="s">
@@ -5095,9 +5153,9 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="B311" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B311" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C311" s="9" t="s">
@@ -5105,10 +5163,10 @@
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A312" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="B312" s="10" t="s">
+      <c r="A312" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="B312" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C312" s="9" t="s">
@@ -5116,10 +5174,10 @@
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A313" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="B313" s="10" t="s">
+      <c r="A313" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="B313" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C313" s="9" t="s">
@@ -5127,22 +5185,22 @@
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A314" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="B314" s="10" t="s">
-        <v>102</v>
+      <c r="A314" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="B314" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C314" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A315" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="B315" s="10" t="s">
-        <v>217</v>
+      <c r="A315" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="B315" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C315" s="9" t="s">
         <v>59</v>
@@ -5150,10 +5208,10 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="B316" s="10" t="s">
-        <v>217</v>
+        <v>333</v>
+      </c>
+      <c r="B316" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C316" s="9" t="s">
         <v>59</v>
@@ -5161,9 +5219,9 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="B317" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="B317" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C317" s="9" t="s">
@@ -5172,9 +5230,9 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="B318" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="B318" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C318" s="9" t="s">
@@ -5182,33 +5240,33 @@
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A319" s="13" t="s">
-        <v>345</v>
+      <c r="A319" s="11" t="s">
+        <v>336</v>
       </c>
       <c r="B319" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C319" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A320" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="B320" s="10" t="s">
-        <v>219</v>
+      <c r="A320" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="B320" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C320" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A321" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="B321" s="10" t="s">
-        <v>219</v>
+      <c r="A321" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="B321" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C321" s="9" t="s">
         <v>59</v>
@@ -5216,10 +5274,10 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="B322" s="10" t="s">
-        <v>102</v>
+        <v>339</v>
+      </c>
+      <c r="B322" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C322" s="9" t="s">
         <v>59</v>
@@ -5227,10 +5285,10 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="B323" s="10" t="s">
-        <v>217</v>
+        <v>340</v>
+      </c>
+      <c r="B323" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C323" s="9" t="s">
         <v>59</v>
@@ -5238,9 +5296,9 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="B324" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="B324" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C324" s="9" t="s">
@@ -5249,9 +5307,9 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="B325" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B325" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C325" s="9" t="s">
@@ -5260,10 +5318,10 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="B326" s="10" t="s">
-        <v>219</v>
+        <v>343</v>
+      </c>
+      <c r="B326" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C326" s="9" t="s">
         <v>59</v>
@@ -5271,10 +5329,10 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="B327" s="10" t="s">
-        <v>219</v>
+        <v>344</v>
+      </c>
+      <c r="B327" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C327" s="9" t="s">
         <v>59</v>
@@ -5282,10 +5340,10 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="B328" s="10" t="s">
-        <v>396</v>
+        <v>345</v>
+      </c>
+      <c r="B328" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C328" s="9" t="s">
         <v>59</v>
@@ -5293,9 +5351,9 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="B329" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B329" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C329" s="9" t="s">
@@ -5304,9 +5362,9 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="B330" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="B330" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C330" s="9" t="s">
@@ -5315,10 +5373,10 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="B331" s="10" t="s">
-        <v>217</v>
+        <v>348</v>
+      </c>
+      <c r="B331" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C331" s="9" t="s">
         <v>59</v>
@@ -5326,21 +5384,21 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="B332" s="10" t="s">
-        <v>217</v>
+        <v>349</v>
+      </c>
+      <c r="B332" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C332" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A333" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="B333" s="10" t="s">
-        <v>102</v>
+      <c r="A333" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="B333" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C333" s="9" t="s">
         <v>59</v>
@@ -5348,10 +5406,10 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="B334" s="10" t="s">
-        <v>102</v>
+        <v>351</v>
+      </c>
+      <c r="B334" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C334" s="9" t="s">
         <v>59</v>
@@ -5359,10 +5417,10 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="B335" s="10" t="s">
-        <v>217</v>
+        <v>352</v>
+      </c>
+      <c r="B335" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C335" s="9" t="s">
         <v>59</v>
@@ -5370,10 +5428,10 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="B336" s="10" t="s">
-        <v>217</v>
+        <v>353</v>
+      </c>
+      <c r="B336" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C336" s="9" t="s">
         <v>59</v>
@@ -5381,10 +5439,10 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="B337" s="10" t="s">
-        <v>217</v>
+        <v>354</v>
+      </c>
+      <c r="B337" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C337" s="9" t="s">
         <v>59</v>
@@ -5392,20 +5450,20 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="B338" s="10" t="s">
-        <v>102</v>
+        <v>355</v>
+      </c>
+      <c r="B338" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C338" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A339" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="B339" s="10" t="s">
+      <c r="A339" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="B339" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C339" s="9" t="s">
@@ -5414,10 +5472,10 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="B340" s="10" t="s">
-        <v>102</v>
+        <v>357</v>
+      </c>
+      <c r="B340" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C340" s="9" t="s">
         <v>59</v>
@@ -5425,10 +5483,10 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="B341" s="10" t="s">
-        <v>217</v>
+        <v>358</v>
+      </c>
+      <c r="B341" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C341" s="9" t="s">
         <v>59</v>
@@ -5436,10 +5494,10 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="B342" s="10" t="s">
-        <v>217</v>
+        <v>359</v>
+      </c>
+      <c r="B342" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C342" s="9" t="s">
         <v>59</v>
@@ -5447,10 +5505,10 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="B343" s="10" t="s">
-        <v>217</v>
+        <v>360</v>
+      </c>
+      <c r="B343" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C343" s="9" t="s">
         <v>59</v>
@@ -5458,9 +5516,9 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="B344" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B344" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C344" s="9" t="s">
@@ -5469,10 +5527,10 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="B345" s="10" t="s">
-        <v>219</v>
+        <v>362</v>
+      </c>
+      <c r="B345" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C345" s="9" t="s">
         <v>59</v>
@@ -5480,9 +5538,9 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="B346" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="B346" s="12" t="s">
         <v>56</v>
       </c>
       <c r="C346" s="9" t="s">
@@ -5491,10 +5549,10 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="B347" s="10" t="s">
-        <v>219</v>
+        <v>364</v>
+      </c>
+      <c r="B347" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C347" s="9" t="s">
         <v>59</v>
@@ -5502,10 +5560,10 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="B348" s="10" t="s">
-        <v>102</v>
+        <v>365</v>
+      </c>
+      <c r="B348" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C348" s="9" t="s">
         <v>59</v>
@@ -5513,10 +5571,10 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="B349" s="10" t="s">
-        <v>219</v>
+        <v>366</v>
+      </c>
+      <c r="B349" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C349" s="9" t="s">
         <v>59</v>
@@ -5524,10 +5582,10 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="B350" s="10" t="s">
-        <v>217</v>
+        <v>367</v>
+      </c>
+      <c r="B350" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C350" s="9" t="s">
         <v>59</v>
@@ -5535,10 +5593,10 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="B351" s="10" t="s">
-        <v>217</v>
+        <v>368</v>
+      </c>
+      <c r="B351" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C351" s="9" t="s">
         <v>59</v>
@@ -5546,10 +5604,10 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="B352" s="10" t="s">
-        <v>102</v>
+        <v>369</v>
+      </c>
+      <c r="B352" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C352" s="9" t="s">
         <v>59</v>
@@ -5557,10 +5615,10 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B353" s="10" t="s">
-        <v>217</v>
+        <v>270</v>
+      </c>
+      <c r="B353" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C353" s="9" t="s">
         <v>59</v>
@@ -5568,10 +5626,10 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="B354" s="10" t="s">
-        <v>102</v>
+        <v>370</v>
+      </c>
+      <c r="B354" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C354" s="9" t="s">
         <v>59</v>
@@ -5579,10 +5637,10 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="B355" s="10" t="s">
-        <v>219</v>
+        <v>371</v>
+      </c>
+      <c r="B355" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C355" s="9" t="s">
         <v>59</v>
@@ -5590,109 +5648,109 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="B356" s="10" t="s">
-        <v>102</v>
+        <v>372</v>
+      </c>
+      <c r="B356" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C356" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A357" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="B357" s="10" t="s">
+      <c r="A357" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B357" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C357" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="B358" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="B358" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C358" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="B359" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B359" s="12" t="s">
         <v>3</v>
       </c>
       <c r="C359" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A360" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="B360" s="10" t="s">
-        <v>217</v>
+      <c r="A360" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="B360" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C360" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A361" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="B361" s="10" t="s">
-        <v>102</v>
+      <c r="A361" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="B361" s="12" t="s">
+        <v>101</v>
       </c>
       <c r="C361" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A362" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="B362" s="10" t="s">
-        <v>217</v>
+      <c r="A362" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="B362" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C362" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A363" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="B363" s="10" t="s">
-        <v>217</v>
+      <c r="A363" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="B363" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C363" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A364" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="B364" s="10" t="s">
-        <v>217</v>
+      <c r="A364" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="B364" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C364" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="B365" s="10" t="s">
-        <v>217</v>
+        <v>381</v>
+      </c>
+      <c r="B365" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C365" s="9" t="s">
         <v>59</v>
@@ -5700,10 +5758,10 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="B366" s="10" t="s">
-        <v>217</v>
+        <v>382</v>
+      </c>
+      <c r="B366" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C366" s="9" t="s">
         <v>59</v>
@@ -5711,10 +5769,10 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="B367" s="10" t="s">
-        <v>217</v>
+        <v>383</v>
+      </c>
+      <c r="B367" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C367" s="9" t="s">
         <v>59</v>
@@ -5722,10 +5780,10 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="B368" s="10" t="s">
-        <v>217</v>
+        <v>384</v>
+      </c>
+      <c r="B368" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C368" s="9" t="s">
         <v>59</v>
@@ -5733,10 +5791,10 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="B369" s="10" t="s">
-        <v>217</v>
+        <v>385</v>
+      </c>
+      <c r="B369" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C369" s="9" t="s">
         <v>59</v>
@@ -5744,124 +5802,256 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="B370" s="10" t="s">
-        <v>217</v>
+        <v>386</v>
+      </c>
+      <c r="B370" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C370" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A371" s="1"/>
-      <c r="B371" s="1"/>
-      <c r="C371" s="1"/>
+      <c r="A371" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B371" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C371" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A372" s="1"/>
-      <c r="B372" s="1"/>
-      <c r="C372" s="1"/>
+      <c r="A372" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="B372" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C372" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A373" s="1"/>
-      <c r="B373" s="1"/>
-      <c r="C373" s="1"/>
+      <c r="A373" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="B373" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C373" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A374" s="1"/>
-      <c r="B374" s="1"/>
-      <c r="C374" s="1"/>
+      <c r="A374" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="B374" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C374" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A375" s="1"/>
-      <c r="B375" s="1"/>
-      <c r="C375" s="1"/>
+      <c r="A375" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="B375" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C375" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A376" s="1"/>
-      <c r="B376" s="1"/>
-      <c r="C376" s="1"/>
+      <c r="A376" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="B376" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C376" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A377" s="1"/>
-      <c r="B377" s="1"/>
-      <c r="C377" s="1"/>
+      <c r="A377" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B377" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C377" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A378" s="1"/>
-      <c r="B378" s="1"/>
-      <c r="C378" s="1"/>
+      <c r="A378" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C378" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A379" s="1"/>
-      <c r="B379" s="1"/>
-      <c r="C379" s="1"/>
+      <c r="A379" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B379" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C379" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A380" s="1"/>
-      <c r="B380" s="1"/>
-      <c r="C380" s="1"/>
+      <c r="A380" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="B380" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C380" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A381" s="1"/>
-      <c r="B381" s="1"/>
-      <c r="C381" s="1"/>
+      <c r="A381" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="B381" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C381" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A382" s="1"/>
-      <c r="B382" s="1"/>
-      <c r="C382" s="1"/>
+      <c r="A382" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="B382" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C382" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A383" s="1"/>
-      <c r="B383" s="1"/>
-      <c r="C383" s="1"/>
+      <c r="A383" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="B383" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C383" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A384" s="1"/>
-      <c r="B384" s="1"/>
-      <c r="C384" s="1"/>
+      <c r="A384" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B384" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C384" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A385" s="1"/>
-      <c r="B385" s="1"/>
-      <c r="C385" s="1"/>
+      <c r="A385" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="B385" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C385" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A386" s="1"/>
-      <c r="B386" s="1"/>
-      <c r="C386" s="1"/>
+      <c r="A386" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B386" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C386" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A387" s="1"/>
-      <c r="B387" s="1"/>
-      <c r="C387" s="1"/>
+      <c r="A387" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B387" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C387" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A388" s="1"/>
-      <c r="B388" s="1"/>
-      <c r="C388" s="1"/>
+      <c r="A388" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B388" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C388" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A389" s="1"/>
-      <c r="B389" s="1"/>
-      <c r="C389" s="1"/>
+      <c r="A389" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B389" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C389" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A390" s="1"/>
-      <c r="B390" s="1"/>
-      <c r="C390" s="1"/>
+      <c r="A390" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B390" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C390" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A391" s="1"/>
-      <c r="B391" s="1"/>
-      <c r="C391" s="1"/>
+      <c r="A391" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="B391" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C391" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A392" s="1"/>
-      <c r="B392" s="1"/>
-      <c r="C392" s="1"/>
+      <c r="A392" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="B392" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C392" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" s="1"/>
@@ -6888,93 +7078,94 @@
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{1742F09F-6D1A-4CDA-BB14-8BC64089397B}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{BD7EE5DE-FD8F-4CCD-BE03-23430A5C36F0}"/>
-    <hyperlink ref="A98" r:id="rId3" display="https://happilo.hemnthapp.shop/" xr:uid="{6A729D91-1B60-417D-B4E5-70658740D343}"/>
-    <hyperlink ref="A99" r:id="rId4" display="https://flm777.cc/" xr:uid="{138AA387-8C3E-4153-AD63-189DC08C02EE}"/>
-    <hyperlink ref="A101" r:id="rId5" display="https://derymilk72.com/" xr:uid="{093CC132-EDE0-4371-A469-EA307389403F}"/>
-    <hyperlink ref="A109" r:id="rId6" display="https://husqvarna-vip.shop/" xr:uid="{584BBD0E-D996-4DD3-B9A7-0A7528236CFB}"/>
-    <hyperlink ref="A147" r:id="rId7" xr:uid="{9C12B207-AC6E-438B-BD43-E2FDF0ED557B}"/>
-    <hyperlink ref="A149" r:id="rId8" xr:uid="{DC000E81-AC24-4839-8DF0-6CF4CA3A1921}"/>
-    <hyperlink ref="A151" r:id="rId9" xr:uid="{B5D69F36-CDDE-464A-A716-02A9861620D9}"/>
-    <hyperlink ref="A152" r:id="rId10" xr:uid="{BDD9358C-6FD3-4BA1-9B5F-596A5C4C543C}"/>
-    <hyperlink ref="A153" r:id="rId11" display="https://me-esho.netlify.app/" xr:uid="{2A8378B9-4DC2-443A-90BC-3E1F27D0BD95}"/>
-    <hyperlink ref="A163" r:id="rId12" xr:uid="{BBCCB2D1-C08F-40F1-AE92-1EE221F00C76}"/>
-    <hyperlink ref="A167" r:id="rId13" xr:uid="{139CDE3F-EFA2-4E91-AD50-1E0F0896D875}"/>
-    <hyperlink ref="A174" r:id="rId14" xr:uid="{7A393D79-A935-4742-AEDA-80A44CAD6F10}"/>
-    <hyperlink ref="A175" r:id="rId15" xr:uid="{B74E9E38-5EBC-4D28-BF31-56E1EE2B049F}"/>
-    <hyperlink ref="A176" r:id="rId16" display="https://flipcart-limited-offer.myshopify.com/" xr:uid="{0351EF3D-6084-409B-B5B7-F6139EB73266}"/>
-    <hyperlink ref="A178" r:id="rId17" xr:uid="{D31771FB-EA91-4E94-957C-6A03019D57FC}"/>
-    <hyperlink ref="A179" r:id="rId18" xr:uid="{D6CA42BC-4E99-456C-96A4-D45712E47A7F}"/>
-    <hyperlink ref="A180" r:id="rId19" display="https://meesho.onlinelehenga.com/" xr:uid="{8AB1DB3F-BA03-4B0C-AAC7-A5C0701BA08D}"/>
-    <hyperlink ref="A182" r:id="rId20" display="https://measho003.vercel.app/" xr:uid="{1B5E7EE9-AFE8-4F24-AF86-8B90CA92CF74}"/>
-    <hyperlink ref="A184" r:id="rId21" xr:uid="{625A9EE8-3BFB-4E7D-B829-11FC25662E0B}"/>
-    <hyperlink ref="A187" r:id="rId22" xr:uid="{25E5CCE7-F9FE-44B1-93B3-42D3CEE276A7}"/>
-    <hyperlink ref="A190" r:id="rId23" xr:uid="{105C081F-48DA-41AC-A2A3-E243DAC39D14}"/>
-    <hyperlink ref="A191" r:id="rId24" xr:uid="{0470C068-0381-4BAC-AED1-89A88636ABE0}"/>
-    <hyperlink ref="A192" r:id="rId25" display="https://meeshom.sales-india.com/" xr:uid="{418A3B96-4D00-499C-956D-DEAC48A45542}"/>
-    <hyperlink ref="A193" r:id="rId26" xr:uid="{89722EEB-92CF-4A28-A9C0-29368CE0DF9C}"/>
-    <hyperlink ref="A194" r:id="rId27" xr:uid="{8495AF55-6045-4393-A6C6-DE1A1BCA9054}"/>
-    <hyperlink ref="A195" r:id="rId28" display="https://mesho.diziebook.shop/" xr:uid="{0BC0E840-2E76-4665-8D3F-AF1BCC2B02D8}"/>
-    <hyperlink ref="A197" r:id="rId29" xr:uid="{4DFF97A0-EF37-400B-AA69-5922E2DD6530}"/>
-    <hyperlink ref="A198" r:id="rId30" xr:uid="{EA98A7C4-29B4-444D-B9DA-ED51A24F2B09}"/>
-    <hyperlink ref="A201" r:id="rId31" display="https://fiipkart-summer.lovable.app/" xr:uid="{099A427C-BB02-4F01-92DB-CFC48801646A}"/>
-    <hyperlink ref="A203" r:id="rId32" xr:uid="{0FE200CC-1EA6-441C-A217-FC786804E409}"/>
-    <hyperlink ref="A204" r:id="rId33" xr:uid="{927EE4B7-B8CB-4E51-9DDF-CF8C4C3FF996}"/>
-    <hyperlink ref="A206" r:id="rId34" xr:uid="{5BBDF787-7FCD-4265-A54F-23E8571C5B7C}"/>
-    <hyperlink ref="A207" r:id="rId35" xr:uid="{0D04D992-1384-4E80-B38C-B61B75202128}"/>
-    <hyperlink ref="A208" r:id="rId36" xr:uid="{AF194AB3-4860-49FD-8701-A8215478A607}"/>
-    <hyperlink ref="A209" r:id="rId37" xr:uid="{1826BD0C-F50E-477B-A18C-9C92807992AE}"/>
-    <hyperlink ref="A210" r:id="rId38" xr:uid="{D9245371-BC2E-4FE8-AAAA-F19F5E4E4062}"/>
-    <hyperlink ref="A211" r:id="rId39" xr:uid="{788EC0FB-01CB-44E1-B3CB-AD9332F3FE66}"/>
-    <hyperlink ref="A212" r:id="rId40" xr:uid="{A4A83EC2-8B1C-404E-A389-8A167FABD223}"/>
-    <hyperlink ref="A215" r:id="rId41" xr:uid="{C78D1B84-837F-4FAD-84AE-E567E007C7BB}"/>
-    <hyperlink ref="A219" r:id="rId42" xr:uid="{26466434-A6DC-43C9-AD96-819076E61210}"/>
-    <hyperlink ref="A222" r:id="rId43" xr:uid="{A7EEA9F1-388A-44F3-ABD5-7FC7A1B4350F}"/>
-    <hyperlink ref="A225" r:id="rId44" xr:uid="{6DC04966-4348-4801-B8C5-3CABB212FA7F}"/>
-    <hyperlink ref="A230" r:id="rId45" display="https://gas-booking-start.online/" xr:uid="{7E7B62BB-2B51-482D-9431-608B5B88780D}"/>
-    <hyperlink ref="A231" r:id="rId46" xr:uid="{F99E544F-E19F-445B-AD01-AACA358A6A8D}"/>
-    <hyperlink ref="A239" r:id="rId47" xr:uid="{912D333C-B93C-4476-8C88-934B92DCDC42}"/>
-    <hyperlink ref="A241" r:id="rId48" xr:uid="{A0D41BE7-806A-4E6E-8270-C966D334B9D8}"/>
-    <hyperlink ref="A246" r:id="rId49" xr:uid="{18006AFA-47C9-47E8-BEB6-14F8DB648B50}"/>
-    <hyperlink ref="A247" r:id="rId50" xr:uid="{4F804854-6C3A-4AAB-9BE4-463F32BDB7ED}"/>
-    <hyperlink ref="A248" r:id="rId51" display="https://biggest-dhamaka-sale.com/35d08b206d" xr:uid="{154094EA-87F7-431A-BC4F-7CF7AE857D7E}"/>
-    <hyperlink ref="A249" r:id="rId52" display="https://summer.supersalepro.com/5359e914a4/OFFER/fk99" xr:uid="{EC2AC14C-F432-4930-B511-B36EDD795C0E}"/>
-    <hyperlink ref="A250" r:id="rId53" display="https://govtyojna.online/" xr:uid="{B5CC380B-B897-415B-AE03-81DB31AA00B8}"/>
-    <hyperlink ref="A251" r:id="rId54" xr:uid="{39247586-0DB9-434E-9CD0-92651CADDF39}"/>
-    <hyperlink ref="A254" r:id="rId55" display="https://lightyellow-pig-224973.hostingersite.com/" xr:uid="{436C74C7-7D78-4AAC-A8A2-43F939B5E042}"/>
-    <hyperlink ref="A255" r:id="rId56" xr:uid="{9D0DE02D-1C1B-4FAC-A703-E5721CAA22A6}"/>
-    <hyperlink ref="A256" r:id="rId57" xr:uid="{6E050CAA-E7E8-44BC-8953-CB72D63C506E}"/>
-    <hyperlink ref="A257" r:id="rId58" xr:uid="{9E15B222-A0CD-4A68-9CA5-B37E48A13D3E}"/>
-    <hyperlink ref="A258" r:id="rId59" xr:uid="{6A4E8273-EF95-4CB0-8288-F25BC7FD1831}"/>
-    <hyperlink ref="A259" r:id="rId60" display="https://summer.supersalepro.com/e09ee6afd6/OFFER/meesho" xr:uid="{001430DC-63C7-476A-96C4-0316E2287A63}"/>
-    <hyperlink ref="A260" r:id="rId61" xr:uid="{55576AA3-5DEC-452F-838E-533666A7FCE5}"/>
-    <hyperlink ref="A266" r:id="rId62" xr:uid="{2DF3C542-8562-479B-99BD-E84EB6ED3568}"/>
-    <hyperlink ref="A270" r:id="rId63" xr:uid="{CA3F6523-C40A-49AA-94ED-7E3CDD2C43F1}"/>
-    <hyperlink ref="A277" r:id="rId64" xr:uid="{1ED10EAE-244A-44E7-81E2-050F9599CD48}"/>
-    <hyperlink ref="A280" r:id="rId65" xr:uid="{58AAE832-0E57-4DB1-AFA6-A67FE9334E55}"/>
-    <hyperlink ref="A289" r:id="rId66" xr:uid="{5696400C-2BA9-43C1-B7C8-136A85D2CAE9}"/>
-    <hyperlink ref="A290" r:id="rId67" xr:uid="{A51A055D-E50F-4A00-A3E6-AA86B0229E94}"/>
-    <hyperlink ref="A294" r:id="rId68" display="https://shelgo.in/" xr:uid="{5376F282-8E70-4E85-AC47-B4F855EBF5B6}"/>
-    <hyperlink ref="A295" r:id="rId69" xr:uid="{9FDC6578-3F6F-4E0D-9044-570F28F72CA7}"/>
-    <hyperlink ref="A308" r:id="rId70" xr:uid="{3EF40258-75A1-4AB6-B9F9-AB57F59B60EF}"/>
-    <hyperlink ref="A312" r:id="rId71" display="https://momuain.in/" xr:uid="{E1258E1F-480C-47DC-AA54-DD35AA214197}"/>
-    <hyperlink ref="A313" r:id="rId72" xr:uid="{FD0B5EC9-CF29-4B16-9D18-55B68622EA91}"/>
-    <hyperlink ref="A314" r:id="rId73" display="https://kurtij.salesoffers.online/" xr:uid="{3FDAE0DA-2A21-4C2D-8064-0BFF33EE6205}"/>
-    <hyperlink ref="A315" r:id="rId74" xr:uid="{EC618BF0-74A8-43DB-9F61-039B96571B0E}"/>
-    <hyperlink ref="A319" r:id="rId75" display="https://mylpg.coinapl.com/" xr:uid="{F12B2451-3768-4474-8AF1-39F3A39222DD}"/>
-    <hyperlink ref="A320" r:id="rId76" display="https://purple-donkey-641161.hostingersite.com/" xr:uid="{1C09288D-CBD9-4BFA-A63B-27CE089BC0BF}"/>
-    <hyperlink ref="A321" r:id="rId77" display="https://snow-echidna-664511.hostingersite.com/" xr:uid="{AC8BCBEA-9604-4A56-AB64-8EBF1B096F2A}"/>
-    <hyperlink ref="A333" r:id="rId78" xr:uid="{94C9FF8F-72E4-48D7-A381-2A79F8A51F09}"/>
-    <hyperlink ref="A339" r:id="rId79" xr:uid="{1739F645-B332-4EFA-9477-25BE19595912}"/>
-    <hyperlink ref="A357" r:id="rId80" xr:uid="{85A1DE7C-BD5C-4789-B5EE-2AC8F012920F}"/>
-    <hyperlink ref="A360" r:id="rId81" xr:uid="{A788B9BF-631F-4FE0-88E3-C2D226AE0801}"/>
-    <hyperlink ref="A361" r:id="rId82" xr:uid="{C8725BB0-F47B-41A5-9F4E-B37E44FA26F1}"/>
-    <hyperlink ref="A362" r:id="rId83" xr:uid="{B5B102C5-918E-42A5-A3F2-D84AE13B7716}"/>
-    <hyperlink ref="A363" r:id="rId84" xr:uid="{A78EDA0A-57F9-4472-9CA4-B41C14F18ABC}"/>
-    <hyperlink ref="A364" r:id="rId85" xr:uid="{DF223EDE-0BB4-4525-924D-594740619FE3}"/>
-    <hyperlink ref="B242" r:id="rId86" display="https://myip.ms/view/countries/CYP/Internet_Usage_Statistics_Cyprus.html" xr:uid="{0E6C1719-F8E6-4010-B4A4-4977671ED547}"/>
-    <hyperlink ref="B246" r:id="rId87" display="https://myip.ms/view/cities/6/IP_Addresses_Singapore.html" xr:uid="{79922463-31D7-4762-9E4A-F6BB4A868A28}"/>
+    <hyperlink ref="A95" r:id="rId3" display="https://happilo.hemnthapp.shop/" xr:uid="{CB638B65-BF79-4926-B526-6767B443D242}"/>
+    <hyperlink ref="A96" r:id="rId4" display="https://flm777.cc/" xr:uid="{8B4F26D4-D729-4B44-9B01-AFA06226712C}"/>
+    <hyperlink ref="A98" r:id="rId5" display="https://derymilk72.com/" xr:uid="{22000813-63CC-4915-8AE0-66F30865C69C}"/>
+    <hyperlink ref="A106" r:id="rId6" display="https://husqvarna-vip.shop/" xr:uid="{243E5F23-7396-4D88-AFBA-3F7A102266D0}"/>
+    <hyperlink ref="A149" r:id="rId7" xr:uid="{00D7AD9D-6310-486E-AAA1-8E8C7B1CBBBF}"/>
+    <hyperlink ref="A151" r:id="rId8" xr:uid="{42E525FE-89F8-49E6-A47F-2EEB1378F3D1}"/>
+    <hyperlink ref="A153" r:id="rId9" xr:uid="{831EED30-F30B-4688-AFB0-0F580BC3799B}"/>
+    <hyperlink ref="A154" r:id="rId10" xr:uid="{1B8F0F65-AB29-4F7B-92D3-C0C082C59768}"/>
+    <hyperlink ref="A155" r:id="rId11" display="https://me-esho.netlify.app/" xr:uid="{594B4E5A-8010-4A0A-91DF-DDF988DEF3DB}"/>
+    <hyperlink ref="A165" r:id="rId12" xr:uid="{6EA4C942-7CA8-446C-AEE2-676B1D2CE5D3}"/>
+    <hyperlink ref="A169" r:id="rId13" xr:uid="{566CFCD5-D349-4470-B9D5-AC3D167A1276}"/>
+    <hyperlink ref="A176" r:id="rId14" xr:uid="{9102341C-CE84-462D-8516-C288D0A61E12}"/>
+    <hyperlink ref="A177" r:id="rId15" xr:uid="{2F8417D3-8A35-4907-9295-719AB7F350AA}"/>
+    <hyperlink ref="A178" r:id="rId16" display="https://flipcart-limited-offer.myshopify.com/" xr:uid="{4DE891C7-2D45-40E8-B4CC-EF3341520379}"/>
+    <hyperlink ref="A180" r:id="rId17" xr:uid="{081CF97A-C46B-4E36-A9D9-E11E318830DE}"/>
+    <hyperlink ref="A181" r:id="rId18" xr:uid="{B835557C-7699-45B7-A14C-A00E8AE57B3B}"/>
+    <hyperlink ref="A182" r:id="rId19" display="https://meesho.onlinelehenga.com/" xr:uid="{E01D5768-6AB9-4A1E-9ABD-1D4BC56613DC}"/>
+    <hyperlink ref="A184" r:id="rId20" display="https://measho003.vercel.app/" xr:uid="{9BD859EB-7C46-4BD6-A728-40033E2FCDA6}"/>
+    <hyperlink ref="A185" r:id="rId21" xr:uid="{582A4629-4222-4044-AA8C-A9495B222C7B}"/>
+    <hyperlink ref="A188" r:id="rId22" xr:uid="{C1EF0110-5C31-4E98-A2BC-2853657C2D65}"/>
+    <hyperlink ref="A191" r:id="rId23" xr:uid="{3CEC482C-7E40-4E99-AF56-6030CC42E66B}"/>
+    <hyperlink ref="A192" r:id="rId24" xr:uid="{12B4C7FF-C946-4D62-B16E-2E37D4A99523}"/>
+    <hyperlink ref="A193" r:id="rId25" display="https://meeshom.sales-india.com/" xr:uid="{232942E4-2AE9-4F05-AA23-AF9A9772E2DB}"/>
+    <hyperlink ref="A194" r:id="rId26" xr:uid="{C85EE451-A7A9-409F-BC52-734A801D06F0}"/>
+    <hyperlink ref="A195" r:id="rId27" xr:uid="{8009E0CB-C786-4094-8A4F-340F217DEE58}"/>
+    <hyperlink ref="A196" r:id="rId28" display="https://mesho.diziebook.shop/" xr:uid="{9B9AD9D5-E180-44AE-A961-079A64718C0A}"/>
+    <hyperlink ref="A198" r:id="rId29" xr:uid="{66A9E23E-5A00-46A6-ADA4-411D05BFED9F}"/>
+    <hyperlink ref="A199" r:id="rId30" xr:uid="{4AAD5784-00D0-4F26-B31F-F8322B135611}"/>
+    <hyperlink ref="A202" r:id="rId31" display="https://fiipkart-summer.lovable.app/" xr:uid="{4789CD7C-A0CE-4CD4-8958-870902CC8923}"/>
+    <hyperlink ref="A204" r:id="rId32" xr:uid="{A0BCD7D4-35CD-4053-9FC2-72F7EC1D4AC4}"/>
+    <hyperlink ref="A205" r:id="rId33" xr:uid="{A2718DA6-D080-4484-84B6-F1D64128441C}"/>
+    <hyperlink ref="A207" r:id="rId34" xr:uid="{237371A3-02E4-47CD-BB05-3CEF2C40F5AF}"/>
+    <hyperlink ref="A208" r:id="rId35" xr:uid="{D1C55EC7-0946-40F6-A599-F644A4617CF5}"/>
+    <hyperlink ref="A209" r:id="rId36" xr:uid="{13F6105F-3D0E-49C9-B805-203910CFB0A0}"/>
+    <hyperlink ref="A210" r:id="rId37" xr:uid="{4452B044-6233-4301-9098-F396A854C1F9}"/>
+    <hyperlink ref="A211" r:id="rId38" xr:uid="{1920F1EC-2B35-4B05-B551-DBFF236419BC}"/>
+    <hyperlink ref="A212" r:id="rId39" xr:uid="{98804432-D44D-4EC4-935B-B0D92677A1B0}"/>
+    <hyperlink ref="A213" r:id="rId40" xr:uid="{627BA045-9A98-4033-B2A0-7F75FFE48CB3}"/>
+    <hyperlink ref="A216" r:id="rId41" xr:uid="{1B220CBC-8169-4064-95D8-EFEC7559B298}"/>
+    <hyperlink ref="A220" r:id="rId42" xr:uid="{F1B92489-30B1-4AC5-9BEF-58F459533193}"/>
+    <hyperlink ref="A223" r:id="rId43" xr:uid="{96993776-6D0E-464A-87A9-9F9D35FFD6A8}"/>
+    <hyperlink ref="A226" r:id="rId44" xr:uid="{19133496-704A-4F64-8118-8D971C8A0300}"/>
+    <hyperlink ref="A231" r:id="rId45" display="https://gas-booking-start.online/" xr:uid="{3D608857-C013-4CC3-B277-AD82D54BB82E}"/>
+    <hyperlink ref="A232" r:id="rId46" xr:uid="{33BB4F5E-D2BA-45AE-B295-BCD5657AE76C}"/>
+    <hyperlink ref="A240" r:id="rId47" xr:uid="{4D38DF0F-35DA-45AA-B55C-733771D6EDE6}"/>
+    <hyperlink ref="A242" r:id="rId48" xr:uid="{1A66AD11-D85B-449B-9F84-E9A0FDCD0B35}"/>
+    <hyperlink ref="A247" r:id="rId49" xr:uid="{45595E76-D5DA-4E04-8103-A133CF77C018}"/>
+    <hyperlink ref="A248" r:id="rId50" xr:uid="{B2C592ED-02B4-4483-8BDA-BD284CC7BF87}"/>
+    <hyperlink ref="A249" r:id="rId51" display="https://biggest-dhamaka-sale.com/35d08b206d" xr:uid="{0880FF49-5476-48CE-AE29-FBD94FAF81A5}"/>
+    <hyperlink ref="A250" r:id="rId52" display="https://summer.supersalepro.com/5359e914a4/OFFER/fk99" xr:uid="{C69E5C8D-C159-468C-9100-47F272DB10A6}"/>
+    <hyperlink ref="A251" r:id="rId53" display="https://govtyojna.online/" xr:uid="{122E0F39-CBDE-4FF6-9F80-D56C2E2C72C7}"/>
+    <hyperlink ref="A252" r:id="rId54" xr:uid="{11E2EEF0-AB72-4E36-A4D1-96F9DC6905CE}"/>
+    <hyperlink ref="A255" r:id="rId55" display="https://lightyellow-pig-224973.hostingersite.com/" xr:uid="{6D185BA0-6867-487C-88D0-CFC60E66730B}"/>
+    <hyperlink ref="A256" r:id="rId56" xr:uid="{288AAA4F-A666-48BB-97A6-7DAD58057B80}"/>
+    <hyperlink ref="A257" r:id="rId57" xr:uid="{8DC91811-29EB-4E18-9293-37F71CABA3A3}"/>
+    <hyperlink ref="A258" r:id="rId58" xr:uid="{88C24D52-1C31-4719-9F32-6F215D687CA6}"/>
+    <hyperlink ref="A259" r:id="rId59" xr:uid="{20AF9E79-9042-4D37-9586-8FE53AAA9429}"/>
+    <hyperlink ref="A260" r:id="rId60" xr:uid="{10674B19-8F1C-46CB-991F-F3282DA6C3D3}"/>
+    <hyperlink ref="A266" r:id="rId61" xr:uid="{ACCA3422-8D96-46C5-9109-739DC93A4152}"/>
+    <hyperlink ref="A270" r:id="rId62" xr:uid="{E8F9B85A-DEC0-49D8-809F-78A1A47F2663}"/>
+    <hyperlink ref="A277" r:id="rId63" xr:uid="{747F0DBC-9BF4-470B-A607-3AF984CCEB0B}"/>
+    <hyperlink ref="A280" r:id="rId64" xr:uid="{D1CCA9FA-C15A-4BBB-8F9A-CBADFCE4DBBA}"/>
+    <hyperlink ref="A289" r:id="rId65" xr:uid="{73F6653D-B9F9-4329-9629-0ED2A98D636D}"/>
+    <hyperlink ref="A290" r:id="rId66" xr:uid="{8A96FB4F-C4A6-4836-B3CF-A8A4CCD2F010}"/>
+    <hyperlink ref="A294" r:id="rId67" display="https://shelgo.in/" xr:uid="{B753FD3A-8725-4AA1-A7D1-FBDEA8071215}"/>
+    <hyperlink ref="A295" r:id="rId68" xr:uid="{6B21BB60-7ABC-4786-99A6-16C8D3FC8CF0}"/>
+    <hyperlink ref="A308" r:id="rId69" xr:uid="{78E66784-9148-40F4-A089-FC2FBC7FBDE6}"/>
+    <hyperlink ref="A312" r:id="rId70" display="https://momuain.in/" xr:uid="{9DAC4759-ADD0-4723-986A-0C6E5469D31C}"/>
+    <hyperlink ref="A313" r:id="rId71" xr:uid="{95E49459-A370-4EB7-BACB-17B13DC6E23D}"/>
+    <hyperlink ref="A314" r:id="rId72" display="https://kurtij.salesoffers.online/" xr:uid="{B3CB0C7D-7ACC-4086-88AF-96FCD0569EC4}"/>
+    <hyperlink ref="A315" r:id="rId73" xr:uid="{E3EE8976-1AAB-406B-A06A-4C7229896C51}"/>
+    <hyperlink ref="A319" r:id="rId74" display="https://mylpg.coinapl.com/" xr:uid="{0BBE3652-D363-475D-9005-57B7418FD44A}"/>
+    <hyperlink ref="A320" r:id="rId75" display="https://purple-donkey-641161.hostingersite.com/" xr:uid="{8250B95F-6E32-44FD-A6CF-8886E1130D0B}"/>
+    <hyperlink ref="A321" r:id="rId76" display="https://snow-echidna-664511.hostingersite.com/" xr:uid="{1ADBA554-49FF-449E-BE95-95BE23F1B897}"/>
+    <hyperlink ref="A333" r:id="rId77" xr:uid="{E32A5784-8FAC-406D-855E-B79E82655BF8}"/>
+    <hyperlink ref="A339" r:id="rId78" xr:uid="{0588CAD5-B1D0-40B1-A57E-94D6254A26A3}"/>
+    <hyperlink ref="A357" r:id="rId79" xr:uid="{8EF02C8D-E8CE-4186-9E6E-907AD9D7F007}"/>
+    <hyperlink ref="A360" r:id="rId80" xr:uid="{03AC454A-9CE2-4D0F-AD3E-26F7BDF35BA6}"/>
+    <hyperlink ref="A361" r:id="rId81" xr:uid="{4858D4DC-6AF2-4DBB-AEAE-E7FBBEBB1EC3}"/>
+    <hyperlink ref="A362" r:id="rId82" xr:uid="{51FCAA06-8FB3-402D-83D9-EDBD029BCF4E}"/>
+    <hyperlink ref="A363" r:id="rId83" xr:uid="{0B9176BD-BF4D-46CE-9F5A-59321A564DE9}"/>
+    <hyperlink ref="A364" r:id="rId84" xr:uid="{66FDCEB6-8B8E-4C95-A4FE-B0C0641C1DA5}"/>
+    <hyperlink ref="A387" r:id="rId85" display="https://stircrazy.live/" xr:uid="{507B5295-F051-48DA-B109-C93F86B7F27E}"/>
+    <hyperlink ref="A392" r:id="rId86" xr:uid="{ED9B648D-E744-4474-B823-5E7A46D5C7ED}"/>
+    <hyperlink ref="B243" r:id="rId87" display="https://myip.ms/view/countries/CYP/Internet_Usage_Statistics_Cyprus.html" xr:uid="{6330A49D-101F-4874-961C-D10C489DA683}"/>
+    <hyperlink ref="B247" r:id="rId88" display="https://myip.ms/view/cities/6/IP_Addresses_Singapore.html" xr:uid="{794C5DF6-D69A-4443-A7E2-3B3D77D2C1FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId88"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId89"/>
 </worksheet>
 </file>
--- a/excel_data/Website_mapping.xlsx
+++ b/excel_data/Website_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pixeltruth-my.sharepoint.com/personal/shubhankar_shukla_pixeltruth_com/Documents/Code_Hub/Testing_Code/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{AB1C9699-5AD3-4A07-AFFC-BDB08EC9955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95486142-810D-4192-B480-CD8B2D5BBCCC}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{AB1C9699-5AD3-4A07-AFFC-BDB08EC9955D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D3DA986-57D8-442B-A838-3E35037C5CEE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44ED9281-8F1E-4DBD-9F57-CE2FABFA19EC}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="453">
   <si>
     <t>website_url</t>
   </si>
@@ -507,9 +507,6 @@
     <t>https://samsung-45electronic.com</t>
   </si>
   <si>
-    <t>https://nexoraopai.live</t>
-  </si>
-  <si>
     <t>https://www.zongzi-timi-001.org</t>
   </si>
   <si>
@@ -804,9 +801,6 @@
     <t>https://happilo.hemnthapp.shop</t>
   </si>
   <si>
-    <t>https://tng-26drink.biz</t>
-  </si>
-  <si>
     <t>https://ai-artificial88.com</t>
   </si>
   <si>
@@ -831,15 +825,9 @@
     <t>https://www.kskxjihqjeubgbvooocn.com</t>
   </si>
   <si>
-    <t>https://www.tucchemu-gj206.top</t>
-  </si>
-  <si>
     <t>https://www.e1utr-v6ianw8ds.com</t>
   </si>
   <si>
-    <t>https://www.bazmoterscngzt22.cam</t>
-  </si>
-  <si>
     <t>https://www.qqkk8.ru</t>
   </si>
   <si>
@@ -849,9 +837,6 @@
     <t>https://wz8cyn.colm3-bues.xyz</t>
   </si>
   <si>
-    <t xml:space="preserve">Finland </t>
-  </si>
-  <si>
     <t>https://new.deals-offer-india.org/c6470f44</t>
   </si>
   <si>
@@ -1041,9 +1026,6 @@
     <t>https://merce.longnetwork17promax.com</t>
   </si>
   <si>
-    <t>https://www.f8haribo9fc.com</t>
-  </si>
-  <si>
     <t>https://www.zonlasglk.com</t>
   </si>
   <si>
@@ -1053,9 +1035,6 @@
     <t>https://ikeavuwxzkkww2028.com</t>
   </si>
   <si>
-    <t>https://vellshab-neww2026.netlify.app</t>
-  </si>
-  <si>
     <t>https://air472-cooler.com</t>
   </si>
   <si>
@@ -1378,13 +1357,52 @@
   </si>
   <si>
     <t>https://khandelwalbookpublishers.xy</t>
+  </si>
+  <si>
+    <t>https://khaki-shrew-414555.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://biggest-dhamaka-sale.com/26vbnlce/OFFER/99-EXPUPI</t>
+  </si>
+  <si>
+    <t>https://dhamaka-offer.com/aOmEy3/OFFER/budscod59</t>
+  </si>
+  <si>
+    <t>https://new.deals-offer-india.org/48b0e874</t>
+  </si>
+  <si>
+    <t>https://darkviolet-pelican-267817.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://mediumseagreen-gaur-970253.hostingersite.com</t>
+  </si>
+  <si>
+    <t>https://zarivaa.in</t>
+  </si>
+  <si>
+    <t>https://big-sale-offer.com/gw2E7v/OFFER/phone-buds</t>
+  </si>
+  <si>
+    <t>http://flipkartsummersalebo.shop/offersale</t>
+  </si>
+  <si>
+    <t>https://burgggkibgzoon.shop</t>
+  </si>
+  <si>
+    <t>https://www.dsgjcnklvk-sfdgkuiyradw.com</t>
+  </si>
+  <si>
+    <t>https://www.msydhdjxiijxbaasdow.com</t>
+  </si>
+  <si>
+    <t>https://dh22.trynex.live</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1400,51 +1418,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1471,11 +1451,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1483,27 +1462,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1517,10 +1477,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1820,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0B11C6-F16C-4224-840C-73479EB5E1E4}">
-  <dimension ref="A1:C596"/>
+  <dimension ref="A1:C425"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="61.33203125" customWidth="1"/>
@@ -1899,7 +1855,7 @@
         <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>59</v>
@@ -1910,7 +1866,7 @@
         <v>93</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>59</v>
@@ -1935,18 +1891,18 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1957,7 +1913,7 @@
         <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -1976,7 +1932,7 @@
         <v>98</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>59</v>
@@ -2031,7 +1987,7 @@
         <v>103</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>59</v>
@@ -2174,7 +2130,7 @@
         <v>116</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>59</v>
@@ -2243,7 +2199,7 @@
         <v>90</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -2306,7 +2262,7 @@
         <v>129</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>59</v>
@@ -2317,7 +2273,7 @@
         <v>130</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>59</v>
@@ -2328,7 +2284,7 @@
         <v>131</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>59</v>
@@ -2361,7 +2317,7 @@
         <v>134</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>59</v>
@@ -2405,7 +2361,7 @@
         <v>138</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>59</v>
@@ -2449,7 +2405,7 @@
         <v>142</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>59</v>
@@ -2457,10 +2413,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>59</v>
@@ -2468,10 +2424,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>59</v>
@@ -2479,10 +2435,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>59</v>
@@ -2490,7 +2446,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>90</v>
@@ -2501,10 +2457,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>59</v>
@@ -2512,7 +2468,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>90</v>
@@ -2523,10 +2479,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>59</v>
@@ -2534,7 +2490,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>56</v>
@@ -2545,7 +2501,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>90</v>
@@ -2556,7 +2512,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>90</v>
@@ -2567,10 +2523,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>59</v>
@@ -2578,10 +2534,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>59</v>
@@ -2589,7 +2545,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>56</v>
@@ -2600,10 +2556,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>59</v>
@@ -2611,10 +2567,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>59</v>
@@ -2622,32 +2578,32 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>59</v>
@@ -2655,10 +2611,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>59</v>
@@ -2666,10 +2622,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>59</v>
@@ -2677,7 +2633,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>90</v>
@@ -2688,10 +2644,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>59</v>
@@ -2699,21 +2655,21 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>59</v>
@@ -2721,10 +2677,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>59</v>
@@ -2732,7 +2688,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>3</v>
@@ -2743,7 +2699,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>55</v>
@@ -2754,7 +2710,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>3</v>
@@ -2765,7 +2721,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>3</v>
@@ -2776,21 +2732,21 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>59</v>
@@ -2798,10 +2754,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>59</v>
@@ -2809,10 +2765,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>59</v>
@@ -2820,7 +2776,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>56</v>
@@ -2831,10 +2787,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>59</v>
@@ -2842,7 +2798,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>90</v>
@@ -2853,10 +2809,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>59</v>
@@ -2864,7 +2820,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>90</v>
@@ -2875,10 +2831,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>59</v>
@@ -2886,10 +2842,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>59</v>
@@ -2897,10 +2853,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>59</v>
@@ -2908,10 +2864,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>59</v>
@@ -2919,7 +2875,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>90</v>
@@ -2930,10 +2886,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>59</v>
@@ -2941,10 +2897,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>59</v>
@@ -2952,10 +2908,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>59</v>
@@ -2963,10 +2919,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>59</v>
@@ -2974,10 +2930,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>59</v>
@@ -2985,10 +2941,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>59</v>
@@ -2996,10 +2952,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>59</v>
@@ -3007,7 +2963,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>90</v>
@@ -3018,10 +2974,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>59</v>
@@ -3029,10 +2985,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>59</v>
@@ -3040,10 +2996,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>59</v>
@@ -3051,10 +3007,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>59</v>
@@ -3062,10 +3018,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>59</v>
@@ -3073,7 +3029,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>90</v>
@@ -3084,10 +3040,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>59</v>
@@ -3095,10 +3051,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>59</v>
@@ -3106,10 +3062,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>59</v>
@@ -3117,10 +3073,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>59</v>
@@ -3128,10 +3084,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>59</v>
@@ -3139,7 +3095,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>90</v>
@@ -3150,10 +3106,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>59</v>
@@ -3161,10 +3117,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>59</v>
@@ -3172,7 +3128,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>90</v>
@@ -3183,7 +3139,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>90</v>
@@ -3194,7 +3150,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>52</v>
@@ -3205,21 +3161,21 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B126" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>59</v>
@@ -3227,7 +3183,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>56</v>
@@ -3238,7 +3194,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>56</v>
@@ -3249,7 +3205,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>52</v>
@@ -3260,7 +3216,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>90</v>
@@ -3271,10 +3227,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>59</v>
@@ -3282,10 +3238,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>59</v>
@@ -3293,7 +3249,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>3</v>
@@ -3304,7 +3260,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>3</v>
@@ -3315,21 +3271,21 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>59</v>
@@ -3337,10 +3293,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>59</v>
@@ -3348,7 +3304,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>90</v>
@@ -3359,10 +3315,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>59</v>
@@ -3370,7 +3326,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>56</v>
@@ -3381,7 +3337,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>56</v>
@@ -3392,10 +3348,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>59</v>
@@ -3403,10 +3359,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>59</v>
@@ -3414,10 +3370,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>59</v>
@@ -3425,7 +3381,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>52</v>
@@ -3436,7 +3392,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>52</v>
@@ -3447,10 +3403,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>59</v>
@@ -3458,10 +3414,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>59</v>
@@ -3469,7 +3425,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>90</v>
@@ -3480,7 +3436,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>90</v>
@@ -3491,10 +3447,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>59</v>
@@ -3502,10 +3458,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>59</v>
@@ -3513,10 +3469,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>59</v>
@@ -3524,7 +3480,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>90</v>
@@ -3535,7 +3491,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>3</v>
@@ -3546,7 +3502,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>90</v>
@@ -3557,10 +3513,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>59</v>
@@ -3568,10 +3524,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>59</v>
@@ -3579,10 +3535,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>59</v>
@@ -3590,7 +3546,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>56</v>
@@ -3601,10 +3557,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>59</v>
@@ -3612,7 +3568,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>56</v>
@@ -3623,10 +3579,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>59</v>
@@ -3634,7 +3590,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>90</v>
@@ -3645,10 +3601,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>59</v>
@@ -3656,10 +3612,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>59</v>
@@ -3667,10 +3623,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>59</v>
@@ -3678,7 +3634,7 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>90</v>
@@ -3689,10 +3645,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>59</v>
@@ -3700,7 +3656,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>90</v>
@@ -3711,10 +3667,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>59</v>
@@ -3722,7 +3678,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>90</v>
@@ -3733,43 +3689,43 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>59</v>
@@ -3777,7 +3733,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>90</v>
@@ -3788,10 +3744,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>59</v>
@@ -3799,32 +3755,32 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B180" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B181" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C181" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>59</v>
@@ -3832,10 +3788,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>59</v>
@@ -3843,10 +3799,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>59</v>
@@ -3854,10 +3810,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>59</v>
@@ -3865,10 +3821,10 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>59</v>
@@ -3876,10 +3832,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>59</v>
@@ -3887,10 +3843,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>59</v>
@@ -3898,10 +3854,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>59</v>
@@ -3909,10 +3865,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>59</v>
@@ -3920,7 +3876,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>3</v>
@@ -3931,7 +3887,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>3</v>
@@ -3942,10 +3898,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>59</v>
@@ -3953,10 +3909,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>59</v>
@@ -3964,10 +3920,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>59</v>
@@ -3975,10 +3931,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>59</v>
@@ -3986,7 +3942,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>3</v>
@@ -3997,10 +3953,10 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>59</v>
@@ -4008,10 +3964,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>59</v>
@@ -4019,10 +3975,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>59</v>
@@ -4030,7 +3986,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>90</v>
@@ -4041,7 +3997,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>90</v>
@@ -4052,10 +4008,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>59</v>
@@ -4063,10 +4019,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>59</v>
@@ -4074,10 +4030,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>59</v>
@@ -4085,10 +4041,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>59</v>
@@ -4096,7 +4052,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>3</v>
@@ -4107,10 +4063,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>59</v>
@@ -4118,7 +4074,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>90</v>
@@ -4129,7 +4085,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>90</v>
@@ -4143,7 +4099,7 @@
         <v>119</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>59</v>
@@ -4151,10 +4107,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>59</v>
@@ -4162,10 +4118,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>59</v>
@@ -4173,7 +4129,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>56</v>
@@ -4184,7 +4140,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>56</v>
@@ -4195,10 +4151,10 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>59</v>
@@ -4206,10 +4162,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>59</v>
@@ -4217,7 +4173,7 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>90</v>
@@ -4228,10 +4184,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>59</v>
@@ -4239,7 +4195,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>90</v>
@@ -4250,10 +4206,10 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>59</v>
@@ -4261,7 +4217,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>90</v>
@@ -4272,10 +4228,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>59</v>
@@ -4283,7 +4239,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>90</v>
@@ -4294,10 +4250,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>59</v>
@@ -4305,7 +4261,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>90</v>
@@ -4316,7 +4272,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>90</v>
@@ -4327,10 +4283,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>59</v>
@@ -4338,10 +4294,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>59</v>
@@ -4349,7 +4305,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>90</v>
@@ -4360,7 +4316,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>90</v>
@@ -4371,10 +4327,10 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>59</v>
@@ -4382,10 +4338,10 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>59</v>
@@ -4393,10 +4349,10 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>59</v>
@@ -4404,10 +4360,10 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>59</v>
@@ -4415,10 +4371,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>59</v>
@@ -4426,10 +4382,10 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>59</v>
@@ -4437,10 +4393,10 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>184</v>
+        <v>406</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>59</v>
@@ -4448,10 +4404,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>59</v>
@@ -4459,10 +4415,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>59</v>
@@ -4470,10 +4426,10 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>59</v>
@@ -4481,10 +4437,10 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>59</v>
@@ -4492,10 +4448,10 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>415</v>
+        <v>183</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>59</v>
@@ -4503,10 +4459,10 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>59</v>
@@ -4514,32 +4470,32 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B245" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C245" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C245" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>415</v>
+        <v>185</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>59</v>
@@ -4547,10 +4503,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>59</v>
@@ -4558,10 +4514,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>184</v>
+        <v>408</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>59</v>
@@ -4569,10 +4525,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>59</v>
@@ -4580,10 +4536,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>415</v>
+        <v>183</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>59</v>
@@ -4591,32 +4547,32 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B252" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C252" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>184</v>
+        <v>56</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>59</v>
@@ -4624,10 +4580,10 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>59</v>
@@ -4635,10 +4591,10 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>186</v>
+        <v>3</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>59</v>
@@ -4646,10 +4602,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>59</v>
@@ -4657,10 +4613,10 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>59</v>
@@ -4668,10 +4624,10 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>59</v>
@@ -4679,10 +4635,10 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>59</v>
@@ -4690,40 +4646,40 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B261" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C261" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B262" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C262" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>415</v>
+        <v>3</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>3</v>
@@ -4734,10 +4690,10 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>59</v>
@@ -4745,10 +4701,10 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>59</v>
@@ -4756,7 +4712,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>3</v>
@@ -4767,7 +4723,7 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>3</v>
@@ -4778,10 +4734,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>59</v>
@@ -4789,10 +4745,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>59</v>
@@ -4800,10 +4756,10 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>59</v>
@@ -4811,10 +4767,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>59</v>
@@ -4822,10 +4778,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>59</v>
@@ -4833,10 +4789,10 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>59</v>
@@ -4844,10 +4800,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>186</v>
+        <v>406</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>59</v>
@@ -4855,10 +4811,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>413</v>
+        <v>183</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>59</v>
@@ -4866,10 +4822,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>59</v>
@@ -4877,10 +4833,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>59</v>
@@ -4888,10 +4844,10 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>59</v>
@@ -4899,106 +4855,106 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>4</v>
+        <v>441</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
-        <v>5</v>
+        <v>442</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>6</v>
+        <v>443</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
-        <v>7</v>
+        <v>444</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>8</v>
+        <v>445</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>9</v>
+        <v>446</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>10</v>
+        <v>447</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>11</v>
+        <v>448</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>12</v>
+        <v>391</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>3</v>
+        <v>408</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>3</v>
@@ -5009,7 +4965,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>3</v>
@@ -5020,7 +4976,7 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>3</v>
@@ -5031,7 +4987,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>3</v>
@@ -5042,7 +4998,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>3</v>
@@ -5053,7 +5009,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>3</v>
@@ -5064,7 +5020,7 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>3</v>
@@ -5075,7 +5031,7 @@
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>3</v>
@@ -5086,7 +5042,7 @@
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>3</v>
@@ -5097,7 +5053,7 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>3</v>
@@ -5108,7 +5064,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>3</v>
@@ -5119,10 +5075,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>57</v>
@@ -5130,7 +5086,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>3</v>
@@ -5141,7 +5097,7 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>3</v>
@@ -5152,7 +5108,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>3</v>
@@ -5163,7 +5119,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>3</v>
@@ -5174,7 +5130,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>3</v>
@@ -5185,7 +5141,7 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>3</v>
@@ -5196,7 +5152,7 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>3</v>
@@ -5207,7 +5163,7 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>3</v>
@@ -5218,10 +5174,10 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>57</v>
@@ -5229,7 +5185,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>3</v>
@@ -5240,7 +5196,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>3</v>
@@ -5251,7 +5207,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>3</v>
@@ -5262,7 +5218,7 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>3</v>
@@ -5273,7 +5229,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>3</v>
@@ -5284,7 +5240,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>3</v>
@@ -5295,7 +5251,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>3</v>
@@ -5306,7 +5262,7 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B317" s="1" t="s">
         <v>3</v>
@@ -5317,10 +5273,10 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>57</v>
@@ -5328,10 +5284,10 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>57</v>
@@ -5339,7 +5295,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B320" s="1" t="s">
         <v>3</v>
@@ -5350,18 +5306,18 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>3</v>
@@ -5372,7 +5328,7 @@
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>3</v>
@@ -5383,7 +5339,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>3</v>
@@ -5394,7 +5350,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>3</v>
@@ -5405,120 +5361,120 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>184</v>
+        <v>54</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>186</v>
+        <v>3</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>58</v>
@@ -5526,7 +5482,7 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>3</v>
@@ -5537,10 +5493,10 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>58</v>
@@ -5548,10 +5504,10 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>58</v>
@@ -5559,10 +5515,10 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>58</v>
@@ -5570,10 +5526,10 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>58</v>
@@ -5581,10 +5537,10 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>58</v>
@@ -5592,10 +5548,10 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>58</v>
@@ -5603,10 +5559,10 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>58</v>
@@ -5614,7 +5570,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>3</v>
@@ -5625,7 +5581,7 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>3</v>
@@ -5636,10 +5592,10 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>58</v>
@@ -5647,10 +5603,10 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>55</v>
+        <v>183</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>58</v>
@@ -5658,10 +5614,10 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>58</v>
@@ -5669,10 +5625,10 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>58</v>
@@ -5680,10 +5636,10 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>58</v>
@@ -5691,10 +5647,10 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>58</v>
@@ -5702,10 +5658,10 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>58</v>
@@ -5713,10 +5669,10 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>58</v>
@@ -5724,10 +5680,10 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>58</v>
@@ -5735,21 +5691,21 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
-        <v>254</v>
+        <v>88</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>152</v>
+        <v>55</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>58</v>
@@ -5757,10 +5713,10 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>58</v>
@@ -5768,10 +5724,10 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>58</v>
@@ -5779,10 +5735,10 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>58</v>
@@ -5790,10 +5746,10 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>58</v>
@@ -5801,10 +5757,10 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>58</v>
@@ -5812,10 +5768,10 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>58</v>
@@ -5823,10 +5779,10 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>58</v>
@@ -5834,21 +5790,21 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>58</v>
@@ -5856,10 +5812,10 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>58</v>
@@ -5867,10 +5823,10 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>58</v>
@@ -5878,10 +5834,10 @@
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>58</v>
@@ -5889,10 +5845,10 @@
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>54</v>
+        <v>183</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>58</v>
@@ -5900,10 +5856,10 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>58</v>
@@ -5911,10 +5867,10 @@
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>54</v>
+        <v>183</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>58</v>
@@ -5922,10 +5878,10 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>58</v>
@@ -5933,10 +5889,10 @@
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>58</v>
@@ -5944,10 +5900,10 @@
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>58</v>
@@ -5955,10 +5911,10 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>58</v>
@@ -5966,10 +5922,10 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>58</v>
@@ -5977,10 +5933,10 @@
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>58</v>
@@ -5988,10 +5944,10 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>184</v>
+        <v>54</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>58</v>
@@ -5999,10 +5955,10 @@
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>255</v>
+        <v>204</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>58</v>
@@ -6010,10 +5966,10 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>58</v>
@@ -6021,10 +5977,10 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>256</v>
+        <v>206</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>58</v>
@@ -6032,10 +5988,10 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
-        <v>257</v>
+        <v>207</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>184</v>
+        <v>54</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>58</v>
@@ -6043,10 +5999,10 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>258</v>
+        <v>208</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>58</v>
@@ -6054,10 +6010,10 @@
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
-        <v>259</v>
+        <v>209</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>58</v>
@@ -6065,10 +6021,10 @@
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>58</v>
@@ -6076,10 +6032,10 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>262</v>
+        <v>183</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>58</v>
@@ -6087,10 +6043,10 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>58</v>
@@ -6098,10 +6054,10 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>184</v>
+        <v>90</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>58</v>
@@ -6109,10 +6065,10 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>58</v>
@@ -6120,10 +6076,10 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>58</v>
@@ -6131,10 +6087,10 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>270</v>
+        <v>152</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>58</v>
@@ -6142,10 +6098,10 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
-        <v>331</v>
+        <v>257</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>58</v>
@@ -6153,10 +6109,10 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>58</v>
@@ -6164,10 +6120,10 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>58</v>
@@ -6175,10 +6131,10 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>58</v>
@@ -6186,10 +6142,10 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
-        <v>332</v>
+        <v>262</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>58</v>
@@ -6197,7 +6153,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B398" s="1" t="s">
         <v>90</v>
@@ -6208,10 +6164,10 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
-        <v>334</v>
+        <v>263</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>58</v>
@@ -6219,10 +6175,10 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>335</v>
+        <v>264</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>184</v>
+        <v>260</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>58</v>
@@ -6230,10 +6186,10 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
-        <v>336</v>
+        <v>265</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>3</v>
+        <v>183</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>58</v>
@@ -6241,10 +6197,10 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>58</v>
@@ -6252,10 +6208,10 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>58</v>
@@ -6263,10 +6219,10 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>58</v>
@@ -6274,10 +6230,10 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>58</v>
@@ -6285,7 +6241,7 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>370</v>
+        <v>331</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>3</v>
@@ -6296,10 +6252,10 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>58</v>
@@ -6307,10 +6263,10 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>58</v>
@@ -6318,10 +6274,10 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>58</v>
@@ -6329,10 +6285,10 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>58</v>
@@ -6340,10 +6296,10 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>58</v>
@@ -6351,10 +6307,10 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>58</v>
@@ -6362,10 +6318,10 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>58</v>
@@ -6373,10 +6329,10 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>58</v>
@@ -6384,10 +6340,10 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>58</v>
@@ -6395,10 +6351,10 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>444</v>
+        <v>370</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>58</v>
@@ -6406,10 +6362,10 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
-        <v>445</v>
+        <v>371</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>58</v>
@@ -6417,1005 +6373,199 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>446</v>
+        <v>372</v>
       </c>
       <c r="B418" s="1" t="s">
         <v>152</v>
       </c>
       <c r="C418" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A419" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A420" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A421" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C421" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A419" s="1"/>
-      <c r="B419" s="1"/>
-      <c r="C419" s="1"/>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A420" s="1"/>
-      <c r="B420" s="1"/>
-      <c r="C420" s="1"/>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A421" s="1"/>
-      <c r="B421" s="1"/>
-      <c r="C421" s="1"/>
-    </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A422" s="1"/>
-      <c r="B422" s="1"/>
-      <c r="C422" s="1"/>
+      <c r="A422" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A423" s="1"/>
-      <c r="B423" s="1"/>
-      <c r="C423" s="1"/>
+      <c r="A423" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A424" s="1"/>
-      <c r="B424" s="1"/>
-      <c r="C424" s="1"/>
+      <c r="A424" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A425" s="1"/>
-      <c r="B425" s="1"/>
-      <c r="C425" s="1"/>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A426" s="1"/>
-      <c r="B426" s="1"/>
-      <c r="C426" s="1"/>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A427" s="1"/>
-      <c r="B427" s="1"/>
-      <c r="C427" s="1"/>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A428" s="1"/>
-      <c r="B428" s="1"/>
-      <c r="C428" s="1"/>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A429" s="1"/>
-      <c r="B429" s="1"/>
-      <c r="C429" s="1"/>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A430" s="1"/>
-      <c r="B430" s="1"/>
-      <c r="C430" s="1"/>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A431" s="1"/>
-      <c r="B431" s="1"/>
-      <c r="C431" s="1"/>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A432" s="1"/>
-      <c r="B432" s="1"/>
-      <c r="C432" s="1"/>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A433" s="1"/>
-      <c r="B433" s="1"/>
-      <c r="C433" s="1"/>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A434" s="1"/>
-      <c r="B434" s="1"/>
-      <c r="C434" s="1"/>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A435" s="1"/>
-      <c r="B435" s="1"/>
-      <c r="C435" s="1"/>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A436" s="1"/>
-      <c r="B436" s="1"/>
-      <c r="C436" s="1"/>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A437" s="1"/>
-      <c r="B437" s="1"/>
-      <c r="C437" s="1"/>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A438" s="1"/>
-      <c r="B438" s="1"/>
-      <c r="C438" s="1"/>
-    </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A439" s="1"/>
-      <c r="B439" s="1"/>
-      <c r="C439" s="1"/>
-    </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A440" s="1"/>
-      <c r="B440" s="1"/>
-      <c r="C440" s="1"/>
-    </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A441" s="1"/>
-      <c r="B441" s="1"/>
-      <c r="C441" s="1"/>
-    </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A442" s="1"/>
-      <c r="B442" s="1"/>
-      <c r="C442" s="1"/>
-    </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A443" s="1"/>
-      <c r="B443" s="1"/>
-      <c r="C443" s="1"/>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A444" s="1"/>
-      <c r="B444" s="1"/>
-      <c r="C444" s="1"/>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A445" s="1"/>
-      <c r="B445" s="1"/>
-      <c r="C445" s="1"/>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A446" s="1"/>
-      <c r="B446" s="1"/>
-      <c r="C446" s="1"/>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A447" s="1"/>
-      <c r="B447" s="1"/>
-      <c r="C447" s="1"/>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A448" s="1"/>
-      <c r="B448" s="1"/>
-      <c r="C448" s="1"/>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A449" s="1"/>
-      <c r="B449" s="1"/>
-      <c r="C449" s="1"/>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A450" s="1"/>
-      <c r="B450" s="1"/>
-      <c r="C450" s="1"/>
-    </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A451" s="1"/>
-      <c r="B451" s="1"/>
-      <c r="C451" s="1"/>
-    </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A452" s="1"/>
-      <c r="B452" s="1"/>
-      <c r="C452" s="1"/>
-    </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A453" s="1"/>
-      <c r="B453" s="1"/>
-      <c r="C453" s="1"/>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A454" s="1"/>
-      <c r="B454" s="1"/>
-      <c r="C454" s="1"/>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A455" s="1"/>
-      <c r="B455" s="1"/>
-      <c r="C455" s="1"/>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A456" s="1"/>
-      <c r="B456" s="1"/>
-      <c r="C456" s="1"/>
-    </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A457" s="1"/>
-      <c r="B457" s="1"/>
-      <c r="C457" s="1"/>
-    </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A458" s="1"/>
-      <c r="B458" s="1"/>
-      <c r="C458" s="1"/>
-    </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A459" s="1"/>
-      <c r="B459" s="1"/>
-      <c r="C459" s="1"/>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A460" s="1"/>
-      <c r="B460" s="1"/>
-      <c r="C460" s="1"/>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A461" s="1"/>
-      <c r="B461" s="1"/>
-      <c r="C461" s="1"/>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A462" s="1"/>
-      <c r="B462" s="1"/>
-      <c r="C462" s="1"/>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A463" s="1"/>
-      <c r="B463" s="1"/>
-      <c r="C463" s="1"/>
-    </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A464" s="1"/>
-      <c r="B464" s="1"/>
-      <c r="C464" s="1"/>
-    </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A465" s="1"/>
-      <c r="B465" s="1"/>
-      <c r="C465" s="1"/>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A466" s="1"/>
-      <c r="B466" s="1"/>
-      <c r="C466" s="1"/>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A467" s="1"/>
-      <c r="B467" s="1"/>
-      <c r="C467" s="1"/>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A468" s="1"/>
-      <c r="B468" s="1"/>
-      <c r="C468" s="1"/>
-    </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A469" s="1"/>
-      <c r="B469" s="1"/>
-      <c r="C469" s="1"/>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A470" s="1"/>
-      <c r="B470" s="1"/>
-      <c r="C470" s="1"/>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A471" s="1"/>
-      <c r="B471" s="1"/>
-      <c r="C471" s="1"/>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A472" s="1"/>
-      <c r="B472" s="1"/>
-      <c r="C472" s="1"/>
-    </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A473" s="1"/>
-      <c r="B473" s="1"/>
-      <c r="C473" s="1"/>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A474" s="1"/>
-      <c r="B474" s="1"/>
-      <c r="C474" s="1"/>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A475" s="1"/>
-      <c r="B475" s="1"/>
-      <c r="C475" s="1"/>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A476" s="1"/>
-      <c r="B476" s="1"/>
-      <c r="C476" s="1"/>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A477" s="1"/>
-      <c r="B477" s="1"/>
-      <c r="C477" s="1"/>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A478" s="1"/>
-      <c r="B478" s="1"/>
-      <c r="C478" s="1"/>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A479" s="1"/>
-      <c r="B479" s="1"/>
-      <c r="C479" s="1"/>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A480" s="1"/>
-      <c r="B480" s="1"/>
-      <c r="C480" s="1"/>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A481" s="1"/>
-      <c r="B481" s="1"/>
-      <c r="C481" s="1"/>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A482" s="1"/>
-      <c r="B482" s="1"/>
-      <c r="C482" s="1"/>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A483" s="1"/>
-      <c r="B483" s="1"/>
-      <c r="C483" s="1"/>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A484" s="1"/>
-      <c r="B484" s="1"/>
-      <c r="C484" s="1"/>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A485" s="1"/>
-      <c r="B485" s="1"/>
-      <c r="C485" s="1"/>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A486" s="1"/>
-      <c r="B486" s="1"/>
-      <c r="C486" s="1"/>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A487" s="1"/>
-      <c r="B487" s="1"/>
-      <c r="C487" s="1"/>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A488" s="1"/>
-      <c r="B488" s="1"/>
-      <c r="C488" s="1"/>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A489" s="1"/>
-      <c r="B489" s="1"/>
-      <c r="C489" s="1"/>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A490" s="1"/>
-      <c r="B490" s="1"/>
-      <c r="C490" s="1"/>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A491" s="1"/>
-      <c r="B491" s="1"/>
-      <c r="C491" s="1"/>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A492" s="1"/>
-      <c r="B492" s="1"/>
-      <c r="C492" s="1"/>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A493" s="1"/>
-      <c r="B493" s="1"/>
-      <c r="C493" s="1"/>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A494" s="1"/>
-      <c r="B494" s="1"/>
-      <c r="C494" s="1"/>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A495" s="3"/>
-      <c r="B495" s="5"/>
-      <c r="C495" s="5"/>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A496" s="3"/>
-      <c r="B496" s="5"/>
-      <c r="C496" s="5"/>
-    </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A497" s="3"/>
-      <c r="B497" s="5"/>
-      <c r="C497" s="5"/>
-    </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A498" s="3"/>
-      <c r="B498" s="5"/>
-      <c r="C498" s="5"/>
-    </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A499" s="3"/>
-      <c r="B499" s="5"/>
-      <c r="C499" s="5"/>
-    </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A500" s="3"/>
-      <c r="B500" s="5"/>
-      <c r="C500" s="5"/>
-    </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A501" s="3"/>
-      <c r="B501" s="5"/>
-      <c r="C501" s="5"/>
-    </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A502" s="3"/>
-      <c r="B502" s="5"/>
-      <c r="C502" s="5"/>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A503" s="3"/>
-      <c r="B503" s="5"/>
-      <c r="C503" s="5"/>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A504" s="3"/>
-      <c r="B504" s="5"/>
-      <c r="C504" s="5"/>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A505" s="3"/>
-      <c r="B505" s="5"/>
-      <c r="C505" s="5"/>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A506" s="3"/>
-      <c r="B506" s="5"/>
-      <c r="C506" s="5"/>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A507" s="3"/>
-      <c r="B507" s="5"/>
-      <c r="C507" s="5"/>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A508" s="3"/>
-      <c r="B508" s="5"/>
-      <c r="C508" s="5"/>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A509" s="3"/>
-      <c r="B509" s="5"/>
-      <c r="C509" s="5"/>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A510" s="3"/>
-      <c r="B510" s="5"/>
-      <c r="C510" s="5"/>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A511" s="3"/>
-      <c r="B511" s="5"/>
-      <c r="C511" s="5"/>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A512" s="3"/>
-      <c r="B512" s="5"/>
-      <c r="C512" s="5"/>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A513" s="3"/>
-      <c r="B513" s="5"/>
-      <c r="C513" s="5"/>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A514" s="3"/>
-      <c r="B514" s="5"/>
-      <c r="C514" s="5"/>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A515" s="3"/>
-      <c r="B515" s="5"/>
-      <c r="C515" s="5"/>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A516" s="3"/>
-      <c r="B516" s="5"/>
-      <c r="C516" s="5"/>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A517" s="3"/>
-      <c r="B517" s="5"/>
-      <c r="C517" s="5"/>
-    </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A518" s="3"/>
-      <c r="B518" s="5"/>
-      <c r="C518" s="5"/>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A519" s="3"/>
-      <c r="B519" s="5"/>
-      <c r="C519" s="5"/>
-    </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A520" s="3"/>
-      <c r="B520" s="5"/>
-      <c r="C520" s="5"/>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A521" s="3"/>
-      <c r="B521" s="5"/>
-      <c r="C521" s="5"/>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A522" s="3"/>
-      <c r="B522" s="5"/>
-      <c r="C522" s="5"/>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A523" s="3"/>
-      <c r="B523" s="5"/>
-      <c r="C523" s="5"/>
-    </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A524" s="3"/>
-      <c r="B524" s="5"/>
-      <c r="C524" s="5"/>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A525" s="3"/>
-      <c r="B525" s="5"/>
-      <c r="C525" s="5"/>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A526" s="3"/>
-      <c r="B526" s="5"/>
-      <c r="C526" s="5"/>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A527" s="3"/>
-      <c r="B527" s="5"/>
-      <c r="C527" s="5"/>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A528" s="3"/>
-      <c r="B528" s="5"/>
-      <c r="C528" s="5"/>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A529" s="3"/>
-      <c r="B529" s="5"/>
-      <c r="C529" s="5"/>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A530" s="3"/>
-      <c r="B530" s="5"/>
-      <c r="C530" s="5"/>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A531" s="3"/>
-      <c r="B531" s="5"/>
-      <c r="C531" s="5"/>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A532" s="3"/>
-      <c r="B532" s="5"/>
-      <c r="C532" s="5"/>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A533" s="3"/>
-      <c r="B533" s="5"/>
-      <c r="C533" s="5"/>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A534" s="3"/>
-      <c r="B534" s="5"/>
-      <c r="C534" s="5"/>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A535" s="3"/>
-      <c r="B535" s="5"/>
-      <c r="C535" s="5"/>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A536" s="3"/>
-      <c r="B536" s="5"/>
-      <c r="C536" s="5"/>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A537" s="3"/>
-      <c r="B537" s="5"/>
-      <c r="C537" s="5"/>
-    </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A538" s="3"/>
-      <c r="B538" s="5"/>
-      <c r="C538" s="3"/>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A539" s="3"/>
-      <c r="B539" s="5"/>
-      <c r="C539" s="3"/>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A540" s="3"/>
-      <c r="B540" s="5"/>
-      <c r="C540" s="3"/>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A541" s="3"/>
-      <c r="B541" s="5"/>
-      <c r="C541" s="3"/>
-    </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A542" s="3"/>
-      <c r="B542" s="6"/>
-      <c r="C542" s="3"/>
-    </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A543" s="3"/>
-      <c r="B543" s="5"/>
-      <c r="C543" s="5"/>
-    </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A544" s="3"/>
-      <c r="B544" s="5"/>
-      <c r="C544" s="3"/>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A545" s="3"/>
-      <c r="B545" s="5"/>
-      <c r="C545" s="3"/>
-    </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A546" s="3"/>
-      <c r="B546" s="5"/>
-      <c r="C546" s="3"/>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A547" s="3"/>
-      <c r="B547" s="5"/>
-      <c r="C547" s="3"/>
-    </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A548" s="4"/>
-      <c r="B548" s="5"/>
-      <c r="C548" s="4"/>
-    </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A549" s="3"/>
-      <c r="B549" s="5"/>
-      <c r="C549" s="3"/>
-    </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A550" s="3"/>
-      <c r="B550" s="5"/>
-      <c r="C550" s="3"/>
-    </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A551" s="3"/>
-      <c r="B551" s="5"/>
-      <c r="C551" s="3"/>
-    </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A552" s="3"/>
-      <c r="B552" s="5"/>
-      <c r="C552" s="3"/>
-    </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A553" s="3"/>
-      <c r="B553" s="5"/>
-      <c r="C553" s="3"/>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A554" s="3"/>
-      <c r="B554" s="5"/>
-      <c r="C554" s="3"/>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A555" s="3"/>
-      <c r="B555" s="5"/>
-      <c r="C555" s="3"/>
-    </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A556" s="3"/>
-      <c r="B556" s="5"/>
-      <c r="C556" s="3"/>
-    </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A557" s="3"/>
-      <c r="B557" s="5"/>
-      <c r="C557" s="3"/>
-    </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A558" s="3"/>
-      <c r="B558" s="5"/>
-      <c r="C558" s="3"/>
-    </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A559" s="3"/>
-      <c r="B559" s="5"/>
-      <c r="C559" s="3"/>
-    </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A560" s="3"/>
-      <c r="B560" s="5"/>
-      <c r="C560" s="3"/>
-    </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A561" s="3"/>
-      <c r="B561" s="5"/>
-      <c r="C561" s="3"/>
-    </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A562" s="3"/>
-      <c r="B562" s="5"/>
-      <c r="C562" s="3"/>
-    </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A563" s="3"/>
-      <c r="B563" s="5"/>
-      <c r="C563" s="3"/>
-    </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A564" s="3"/>
-      <c r="B564" s="5"/>
-      <c r="C564" s="3"/>
-    </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A565" s="3"/>
-      <c r="B565" s="5"/>
-      <c r="C565" s="3"/>
-    </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A566" s="3"/>
-      <c r="B566" s="5"/>
-      <c r="C566" s="3"/>
-    </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A567" s="3"/>
-      <c r="B567" s="5"/>
-      <c r="C567" s="3"/>
-    </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A568" s="3"/>
-      <c r="B568" s="5"/>
-      <c r="C568" s="3"/>
-    </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A569" s="3"/>
-      <c r="B569" s="5"/>
-      <c r="C569" s="3"/>
-    </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A570" s="3"/>
-      <c r="B570" s="5"/>
-      <c r="C570" s="3"/>
-    </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A571" s="3"/>
-      <c r="B571" s="5"/>
-      <c r="C571" s="3"/>
-    </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A572" s="3"/>
-      <c r="B572" s="5"/>
-      <c r="C572" s="3"/>
-    </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A573" s="3"/>
-      <c r="B573" s="5"/>
-      <c r="C573" s="3"/>
-    </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A574" s="3"/>
-      <c r="B574" s="5"/>
-      <c r="C574" s="3"/>
-    </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A575" s="3"/>
-      <c r="B575" s="5"/>
-      <c r="C575" s="3"/>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A576" s="3"/>
-      <c r="B576" s="5"/>
-      <c r="C576" s="3"/>
-    </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A577" s="3"/>
-      <c r="B577" s="5"/>
-      <c r="C577" s="3"/>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A578" s="3"/>
-      <c r="B578" s="5"/>
-      <c r="C578" s="3"/>
-    </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A579" s="3"/>
-      <c r="B579" s="7"/>
-      <c r="C579" s="3"/>
-    </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A580" s="3"/>
-      <c r="B580" s="7"/>
-      <c r="C580" s="3"/>
-    </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A581" s="3"/>
-      <c r="B581" s="7"/>
-      <c r="C581" s="3"/>
-    </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A582" s="3"/>
-      <c r="B582" s="7"/>
-      <c r="C582" s="3"/>
-    </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A583" s="3"/>
-      <c r="B583" s="7"/>
-      <c r="C583" s="8"/>
-    </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A584" s="3"/>
-      <c r="B584" s="7"/>
-      <c r="C584" s="3"/>
-    </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A585" s="3"/>
-      <c r="B585" s="7"/>
-      <c r="C585" s="3"/>
-    </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A586" s="3"/>
-      <c r="B586" s="7"/>
-      <c r="C586" s="3"/>
-    </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A587" s="3"/>
-      <c r="B587" s="7"/>
-      <c r="C587" s="3"/>
-    </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A588" s="3"/>
-      <c r="B588" s="7"/>
-      <c r="C588" s="3"/>
-    </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A589" s="3"/>
-      <c r="B589" s="7"/>
-      <c r="C589" s="3"/>
-    </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A590" s="3"/>
-      <c r="B590" s="5"/>
-      <c r="C590" s="3"/>
-    </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A591" s="3"/>
-      <c r="B591" s="5"/>
-      <c r="C591" s="3"/>
-    </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A592" s="3"/>
-      <c r="B592" s="5"/>
-      <c r="C592" s="3"/>
-    </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A593" s="3"/>
-      <c r="B593" s="5"/>
-      <c r="C593" s="3"/>
-    </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A594" s="3"/>
-      <c r="B594" s="5"/>
-      <c r="C594" s="3"/>
-    </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A595" s="3"/>
-      <c r="B595" s="5"/>
-      <c r="C595" s="3"/>
-    </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A596" s="3"/>
-      <c r="B596" s="5"/>
-      <c r="C596" s="3"/>
+      <c r="A425" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C494" xr:uid="{BD0B11C6-F16C-4224-840C-73479EB5E1E4}"/>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{1742F09F-6D1A-4CDA-BB14-8BC64089397B}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{BD7EE5DE-FD8F-4CCD-BE03-23430A5C36F0}"/>
-    <hyperlink ref="A7" r:id="rId3" xr:uid="{4DCE15D6-190A-4A19-A1F0-96573C757660}"/>
-    <hyperlink ref="A9" r:id="rId4" xr:uid="{DF5FDEC2-C7C4-4088-A260-4D2E4B0E7C79}"/>
-    <hyperlink ref="A11" r:id="rId5" xr:uid="{759CD201-796E-4F28-9079-119D9DC45E91}"/>
-    <hyperlink ref="A12" r:id="rId6" xr:uid="{383E6395-A3EE-4462-BA88-9783B4623042}"/>
-    <hyperlink ref="A13" r:id="rId7" display="https://me-esho.netlify.app/" xr:uid="{3AF43C42-3C93-463F-9B1B-1FA73BD8E7CF}"/>
-    <hyperlink ref="A21" r:id="rId8" xr:uid="{089B22CB-BF72-4C0B-B105-1B800021856A}"/>
-    <hyperlink ref="A25" r:id="rId9" xr:uid="{856FFCD1-1F22-45E1-9C8D-DF9D6033049B}"/>
-    <hyperlink ref="A30" r:id="rId10" xr:uid="{7F4C06CC-A176-4E2C-B405-456912AFE35F}"/>
-    <hyperlink ref="A31" r:id="rId11" xr:uid="{3CDDDC9D-2847-498F-BDC1-6A5CCBDE204F}"/>
-    <hyperlink ref="A32" r:id="rId12" display="https://flipcart-limited-offer.myshopify.com/" xr:uid="{53ADA34F-519A-4D5C-A3BB-BBD5133AB572}"/>
-    <hyperlink ref="A34" r:id="rId13" xr:uid="{C99EC05B-3647-48F0-A7D6-2F5966B8C842}"/>
-    <hyperlink ref="A35" r:id="rId14" display="https://meesho.onlinelehenga.com/" xr:uid="{85132DBF-C62D-4CB5-8447-1128D872537D}"/>
-    <hyperlink ref="A37" r:id="rId15" display="https://measho003.vercel.app/" xr:uid="{205B1F49-567C-4793-BBCC-B4E3EA80D231}"/>
-    <hyperlink ref="A38" r:id="rId16" xr:uid="{6DEE1967-DD99-46B8-B0C2-C4D86A410F6C}"/>
-    <hyperlink ref="A41" r:id="rId17" xr:uid="{A505DD5E-90FE-4B32-AC37-BBCDFBD7054A}"/>
-    <hyperlink ref="A42" r:id="rId18" xr:uid="{111DB401-C540-49FE-9159-C9A9A6AC0138}"/>
-    <hyperlink ref="A43" r:id="rId19" xr:uid="{77C63F70-14A4-46DC-BC91-1BA181D2587A}"/>
-    <hyperlink ref="A44" r:id="rId20" xr:uid="{88388579-A838-4255-A209-94E4A0C9A883}"/>
-    <hyperlink ref="A45" r:id="rId21" display="https://mesho.diziebook.shop/" xr:uid="{708BBEE3-9361-40AE-9B62-0C92E8CF6BA1}"/>
-    <hyperlink ref="A47" r:id="rId22" xr:uid="{EF58A059-375E-42D6-BA94-ECC3AA451F04}"/>
-    <hyperlink ref="A50" r:id="rId23" display="https://fiipkart-summer.lovable.app/" xr:uid="{156D380F-ED4A-4B5E-A10F-F57632898CDF}"/>
-    <hyperlink ref="A52" r:id="rId24" xr:uid="{760CD9B0-BAA2-492C-8518-F448C215EABE}"/>
-    <hyperlink ref="A54" r:id="rId25" xr:uid="{BC2C578F-4F21-4404-9F13-D1D13558E626}"/>
-    <hyperlink ref="A55" r:id="rId26" xr:uid="{AAB22935-3CC1-486A-A866-FB117E927105}"/>
-    <hyperlink ref="A56" r:id="rId27" xr:uid="{A21FF91A-8D2D-4A11-B1C7-CB31FA09A542}"/>
-    <hyperlink ref="A57" r:id="rId28" xr:uid="{5D2AE06F-B69C-4C89-8768-3297392945D0}"/>
-    <hyperlink ref="A58" r:id="rId29" xr:uid="{493568B0-C89F-4CAB-A4E9-63432D8D8B65}"/>
-    <hyperlink ref="A59" r:id="rId30" xr:uid="{8D9E61D6-B8E5-4B0F-BF55-302C6567673A}"/>
-    <hyperlink ref="A65" r:id="rId31" xr:uid="{1223A976-84F2-4A06-84D8-4EB697107013}"/>
-    <hyperlink ref="A68" r:id="rId32" xr:uid="{2842F13B-9FE8-4254-8E00-2EC42C26CF9C}"/>
-    <hyperlink ref="A70" r:id="rId33" xr:uid="{26D7C9CA-E428-4F5F-850D-36BC3BFA73FA}"/>
-    <hyperlink ref="A73" r:id="rId34" display="https://gas-booking-start.online/" xr:uid="{C73E0287-78C6-4417-9AD2-964DBE71EFE2}"/>
-    <hyperlink ref="A74" r:id="rId35" xr:uid="{6630732E-20D0-44F8-827E-7CA46F79D7AA}"/>
-    <hyperlink ref="A80" r:id="rId36" xr:uid="{FB3C8127-59BD-4A8E-BF24-EAA4E6A7FE5C}"/>
-    <hyperlink ref="A82" r:id="rId37" xr:uid="{DD466CD5-B53E-411B-A239-E89CA226E18D}"/>
-    <hyperlink ref="A84" r:id="rId38" xr:uid="{A2FD774B-F6B9-4058-9884-180E3F6A717D}"/>
-    <hyperlink ref="A85" r:id="rId39" xr:uid="{145CB283-682B-4D4F-A3A2-84C8E12769E3}"/>
-    <hyperlink ref="A86" r:id="rId40" display="https://biggest-dhamaka-sale.com/35d08b206d" xr:uid="{1B555346-49AF-46FE-9DB6-4C76C2A70A62}"/>
-    <hyperlink ref="A87" r:id="rId41" display="https://govtyojna.online/" xr:uid="{4A943724-1800-4361-9EC9-06BB1E0446DA}"/>
-    <hyperlink ref="A88" r:id="rId42" xr:uid="{99852F56-DE48-4890-9852-817D967A6EA4}"/>
-    <hyperlink ref="A91" r:id="rId43" display="https://lightyellow-pig-224973.hostingersite.com/" xr:uid="{7D4A0F2E-C8B2-4F78-9FE4-AD939006619D}"/>
-    <hyperlink ref="A92" r:id="rId44" xr:uid="{FBBCAE02-78A8-43C6-9C93-7A8A3DFC7999}"/>
-    <hyperlink ref="A93" r:id="rId45" xr:uid="{F30AD151-40C6-47DF-BE57-E10373C84284}"/>
-    <hyperlink ref="A94" r:id="rId46" xr:uid="{CD8F980D-D950-448D-B098-5A8FFC191FAF}"/>
-    <hyperlink ref="A95" r:id="rId47" xr:uid="{A00AF850-0B3B-47B5-B903-3B627E08EC8C}"/>
-    <hyperlink ref="A97" r:id="rId48" xr:uid="{172C29C5-FEC8-4C27-8E89-955443598968}"/>
-    <hyperlink ref="A99" r:id="rId49" xr:uid="{8E7DEAEC-53E2-48C5-9364-1EF04294DB72}"/>
-    <hyperlink ref="A102" r:id="rId50" xr:uid="{8172A851-6C80-4AB2-8F14-298A364EE756}"/>
-    <hyperlink ref="A110" r:id="rId51" xr:uid="{F7B8BF49-BF99-4C66-A3FC-E919245C8F67}"/>
-    <hyperlink ref="A114" r:id="rId52" display="https://shelgo.in/" xr:uid="{5554E564-65A1-47D4-8F8C-07E539E2731F}"/>
-    <hyperlink ref="A115" r:id="rId53" xr:uid="{4C3D8235-96D9-4B08-AF19-608A3A9B1628}"/>
-    <hyperlink ref="A121" r:id="rId54" xr:uid="{BD470B07-4541-45A2-879B-5EA8476F9559}"/>
-    <hyperlink ref="A126" r:id="rId55" xr:uid="{1F29B0D6-089E-4052-B4B0-D89541159AFD}"/>
-    <hyperlink ref="A129" r:id="rId56" display="https://momuain.in/" xr:uid="{505BC453-EC5C-40FB-93C3-501F2250B1E3}"/>
-    <hyperlink ref="A130" r:id="rId57" xr:uid="{C81C8863-0319-40DF-BEAA-83239BB27D8D}"/>
-    <hyperlink ref="A131" r:id="rId58" display="https://kurtij.salesoffers.online/" xr:uid="{07E0B77E-FBB9-4C3E-9ACA-253E4FFB7E23}"/>
-    <hyperlink ref="A132" r:id="rId59" xr:uid="{FD1300FA-F29D-4381-9A14-D34A2DA06496}"/>
-    <hyperlink ref="A136" r:id="rId60" display="https://mylpg.coinapl.com/" xr:uid="{FDB5E2DD-E3AA-4F83-95E0-8875018F14F7}"/>
-    <hyperlink ref="A137" r:id="rId61" display="https://purple-donkey-641161.hostingersite.com/" xr:uid="{B8EE2A1B-C2F5-4216-9AAF-4C5B22D36E80}"/>
-    <hyperlink ref="A138" r:id="rId62" display="https://snow-echidna-664511.hostingersite.com/" xr:uid="{F36044FA-B645-4A26-99F8-DFB6A3E970FD}"/>
-    <hyperlink ref="A150" r:id="rId63" xr:uid="{7112F7E6-A87C-4DA8-9DFF-285B148923DD}"/>
-    <hyperlink ref="A156" r:id="rId64" xr:uid="{C79A5799-41C8-4F32-BC39-9BBCA4A39457}"/>
-    <hyperlink ref="A174" r:id="rId65" xr:uid="{59C82310-EC38-47AA-8527-933DCD556E0F}"/>
-    <hyperlink ref="A177" r:id="rId66" xr:uid="{519BA36E-3E7B-4680-A038-8A3D3D995BAC}"/>
-    <hyperlink ref="A178" r:id="rId67" xr:uid="{BF7F6F18-00FC-4B16-8B44-6E745F59DA21}"/>
-    <hyperlink ref="A179" r:id="rId68" xr:uid="{CB9E1F10-B00A-4065-A1C8-D060B3B7634F}"/>
-    <hyperlink ref="A180" r:id="rId69" xr:uid="{DF81768C-3C6D-4B37-92B0-19A66A912CA8}"/>
-    <hyperlink ref="A181" r:id="rId70" xr:uid="{B76DB50C-D947-4E95-BCDF-61B422BEA60D}"/>
-    <hyperlink ref="A185" r:id="rId71" xr:uid="{EA70170D-F685-499F-8766-C78A453FE8C1}"/>
-    <hyperlink ref="A204" r:id="rId72" display="https://stircrazy.live/" xr:uid="{5E201552-3BFC-48E7-B761-1567861D4532}"/>
-    <hyperlink ref="A209" r:id="rId73" xr:uid="{BEF47D98-1A1B-493D-B298-581E89B0D08E}"/>
-    <hyperlink ref="A218" r:id="rId74" xr:uid="{AE74BAF0-9119-40D0-8D86-7BE9470F56D2}"/>
-    <hyperlink ref="A224" r:id="rId75" xr:uid="{0AC190F2-31F0-4A1F-96D9-6642C0F05017}"/>
-    <hyperlink ref="A241" r:id="rId76" xr:uid="{33057E6B-D6E6-4BE8-A61F-9E8367DAE549}"/>
-    <hyperlink ref="A244" r:id="rId77" xr:uid="{ECAC4CAE-4B4C-41BD-A0AA-C18D7F7FE5B2}"/>
-    <hyperlink ref="A246" r:id="rId78" xr:uid="{D6325B8E-AE41-4407-8198-6E4CAEF9C70D}"/>
-    <hyperlink ref="A247" r:id="rId79" display="https://blue-rhinoceros-712109.hostingersite.com/" xr:uid="{05F83503-34F6-4F15-B86F-58744E016795}"/>
-    <hyperlink ref="A250" r:id="rId80" xr:uid="{34A7B60A-E654-4D3A-85B6-225783B0AE78}"/>
-    <hyperlink ref="A251" r:id="rId81" xr:uid="{1EE39D2F-6A12-4C67-8E80-8EBB1742F24F}"/>
-    <hyperlink ref="A253" r:id="rId82" xr:uid="{89617A5E-83FE-4D33-9651-42A8B41A5A9B}"/>
-    <hyperlink ref="A262" r:id="rId83" xr:uid="{51574DF1-5F74-47C0-A00E-6E89029687A4}"/>
-    <hyperlink ref="A263" r:id="rId84" xr:uid="{B0581C7C-F835-4ED3-AFD9-D30C024A6945}"/>
-    <hyperlink ref="A269" r:id="rId85" display="https://www.bookmyshowiplt20.com/" xr:uid="{5B4C45AD-286B-4B69-BF88-897BCB0302A0}"/>
-    <hyperlink ref="A270" r:id="rId86" xr:uid="{B9F13FED-B7DE-4877-8043-CCCC75485AAC}"/>
-    <hyperlink ref="A271" r:id="rId87" display="https://ticket-booking-2026.lovable.app/" xr:uid="{51ADE736-EE7D-4FD0-95EF-03803B60051E}"/>
-    <hyperlink ref="A272" r:id="rId88" display="https://polon.kalasalelive.shop/" xr:uid="{47524E85-0C4C-44C5-A3BD-3683E7F4817F}"/>
-    <hyperlink ref="A273" r:id="rId89" display="https://brown-ostrich-366780.hostingersite.com/" xr:uid="{FD52EE7F-2578-493D-8C37-53DD773566EF}"/>
-    <hyperlink ref="A279" r:id="rId90" xr:uid="{90F003D8-DF48-4607-BDC1-286C6EBB0F26}"/>
-    <hyperlink ref="B84" r:id="rId91" display="https://myip.ms/view/cities/6/IP_Addresses_Singapore.html" xr:uid="{45F3A7E4-A804-433A-BD0C-E8E76C78B406}"/>
-    <hyperlink ref="A357" r:id="rId92" display="https://happilo.hemnthapp.shop/" xr:uid="{07570788-9DB1-496D-9726-99D22F15B581}"/>
-    <hyperlink ref="A358" r:id="rId93" display="https://flm777.cc/" xr:uid="{CB5FD026-CD7C-45DE-89D7-8350CFD820B1}"/>
-    <hyperlink ref="A360" r:id="rId94" display="https://derymilk72.com/" xr:uid="{A8EF8D65-FA09-469F-893E-84133B9FB71B}"/>
-    <hyperlink ref="A368" r:id="rId95" display="https://husqvarna-vip.shop/" xr:uid="{AC0791B6-839E-436F-B047-7A8D740AC0C4}"/>
+    <hyperlink ref="A7" r:id="rId3" xr:uid="{8300F8AE-3848-4980-86D7-6F8EFEC67C7C}"/>
+    <hyperlink ref="A9" r:id="rId4" xr:uid="{9D68C072-95D5-4A69-A471-A11C33779193}"/>
+    <hyperlink ref="A11" r:id="rId5" xr:uid="{06AFF8F4-AA68-4E80-942F-A2E013C44990}"/>
+    <hyperlink ref="A12" r:id="rId6" xr:uid="{344598CD-332B-40DC-A626-FDC1FAC55621}"/>
+    <hyperlink ref="A13" r:id="rId7" display="https://me-esho.netlify.app/" xr:uid="{99D159E2-0CA2-4A7B-A5BC-585B2735693C}"/>
+    <hyperlink ref="A21" r:id="rId8" xr:uid="{C9D6D8AB-5619-4E06-ABB0-A89D96CAD47B}"/>
+    <hyperlink ref="A25" r:id="rId9" xr:uid="{DAC8CE5F-3048-4B59-946F-96BC659D8522}"/>
+    <hyperlink ref="A30" r:id="rId10" xr:uid="{01877D76-E1A9-4564-8F9C-79E929633FA9}"/>
+    <hyperlink ref="A31" r:id="rId11" xr:uid="{564D8FD8-3B59-4954-86EE-110FE590919C}"/>
+    <hyperlink ref="A32" r:id="rId12" display="https://flipcart-limited-offer.myshopify.com/" xr:uid="{9BAEB75B-AE71-4C60-9E88-DB13EFFBB2DB}"/>
+    <hyperlink ref="A34" r:id="rId13" xr:uid="{0DD9DE89-2E5E-493F-A03C-6F3A2B7EE03C}"/>
+    <hyperlink ref="A35" r:id="rId14" display="https://meesho.onlinelehenga.com/" xr:uid="{4804CB70-846E-4F0F-A98E-2F7DCD3302A6}"/>
+    <hyperlink ref="A37" r:id="rId15" display="https://measho003.vercel.app/" xr:uid="{EAEE562D-60EF-49B8-8FB5-1AB15B6B4AB0}"/>
+    <hyperlink ref="A38" r:id="rId16" xr:uid="{679E21F6-C9DE-41A7-8221-2A82E61DA00E}"/>
+    <hyperlink ref="A41" r:id="rId17" xr:uid="{CB983D0B-345A-4C2D-99E6-E456376F2C11}"/>
+    <hyperlink ref="A42" r:id="rId18" xr:uid="{9073027A-B18B-4DBF-AE14-AF5AEA8C819F}"/>
+    <hyperlink ref="A43" r:id="rId19" xr:uid="{A6682229-3D3D-4667-A226-D1FAC8711070}"/>
+    <hyperlink ref="A44" r:id="rId20" xr:uid="{24C837ED-B364-475A-90C7-FB7ED796DF6A}"/>
+    <hyperlink ref="A45" r:id="rId21" display="https://mesho.diziebook.shop/" xr:uid="{F78A468B-3972-43B2-ABF6-DE2151CD044D}"/>
+    <hyperlink ref="A47" r:id="rId22" xr:uid="{99869A3F-037B-4D90-A1C5-A3B88FD4C21D}"/>
+    <hyperlink ref="A50" r:id="rId23" display="https://fiipkart-summer.lovable.app/" xr:uid="{9378DA2B-68DE-4A2B-90D4-3055A84111A5}"/>
+    <hyperlink ref="A52" r:id="rId24" xr:uid="{4082379B-7C5C-4169-B5F8-0F27B78B845B}"/>
+    <hyperlink ref="A54" r:id="rId25" xr:uid="{29267E57-C603-453A-8AB4-2F1E8BB71F68}"/>
+    <hyperlink ref="A55" r:id="rId26" xr:uid="{930B6746-BA73-44BB-BF32-F009B3D494AE}"/>
+    <hyperlink ref="A56" r:id="rId27" xr:uid="{05422AC3-3118-444A-8094-B82AD816DDF3}"/>
+    <hyperlink ref="A57" r:id="rId28" xr:uid="{E01D1B40-50DE-4863-9D8F-7D30EBEE3DE6}"/>
+    <hyperlink ref="A58" r:id="rId29" xr:uid="{E4597695-ED3E-42DB-921F-BCC0180ED42F}"/>
+    <hyperlink ref="A59" r:id="rId30" xr:uid="{F3B83BAF-94D5-46BF-AAAF-E720D0E2FA99}"/>
+    <hyperlink ref="A65" r:id="rId31" xr:uid="{3862E236-2DB9-4CEB-882D-B7C711306271}"/>
+    <hyperlink ref="A68" r:id="rId32" xr:uid="{D8A2A213-DD5B-463D-A5B2-55FDF9046F81}"/>
+    <hyperlink ref="A70" r:id="rId33" xr:uid="{2EA1336D-645D-4A61-9E15-BBC7D720E534}"/>
+    <hyperlink ref="A73" r:id="rId34" display="https://gas-booking-start.online/" xr:uid="{D071C8CB-D018-4952-A325-AE15301C7586}"/>
+    <hyperlink ref="A74" r:id="rId35" xr:uid="{BF9842B2-20F2-4460-BF41-3279DEBDC317}"/>
+    <hyperlink ref="A80" r:id="rId36" xr:uid="{CCD3DA51-2FB9-4930-8BDA-F05C316C7532}"/>
+    <hyperlink ref="A82" r:id="rId37" xr:uid="{36AEDBF8-9533-4ACD-9528-337661CE3E5E}"/>
+    <hyperlink ref="A84" r:id="rId38" xr:uid="{FDFB29B9-4E73-4A16-8DF4-67D62FC77908}"/>
+    <hyperlink ref="A85" r:id="rId39" xr:uid="{059C1E74-47A6-45FF-972D-A040B0335430}"/>
+    <hyperlink ref="A86" r:id="rId40" display="https://biggest-dhamaka-sale.com/35d08b206d" xr:uid="{0A5C3480-7B8B-4288-9C8C-930341BA0756}"/>
+    <hyperlink ref="A87" r:id="rId41" display="https://govtyojna.online/" xr:uid="{F0DA7E47-F4EC-48BE-A22D-14A2547849E6}"/>
+    <hyperlink ref="A88" r:id="rId42" xr:uid="{8CFCBB7C-3963-464E-B908-56EC50278EA9}"/>
+    <hyperlink ref="A91" r:id="rId43" display="https://lightyellow-pig-224973.hostingersite.com/" xr:uid="{E1816203-0350-48BF-8510-6E61681D2752}"/>
+    <hyperlink ref="A92" r:id="rId44" xr:uid="{5E337DEC-D739-4873-97B5-C5E4AC55DBB8}"/>
+    <hyperlink ref="A93" r:id="rId45" xr:uid="{5466D7F9-E5F2-4269-84F3-CCD35D1F2996}"/>
+    <hyperlink ref="A94" r:id="rId46" xr:uid="{11B657C0-4A03-461C-8963-B85DE1990C0D}"/>
+    <hyperlink ref="A95" r:id="rId47" xr:uid="{6C4FFA04-7518-4779-AE69-57A52C981A2D}"/>
+    <hyperlink ref="A97" r:id="rId48" xr:uid="{A42A31C0-1798-48B5-8B67-E4C046C1EA0C}"/>
+    <hyperlink ref="A99" r:id="rId49" xr:uid="{8235B6BF-E625-4E4A-84B6-FF0BE3570E11}"/>
+    <hyperlink ref="A102" r:id="rId50" xr:uid="{1DB1ABDC-D17D-45BF-861A-C777A5A52D65}"/>
+    <hyperlink ref="A110" r:id="rId51" xr:uid="{A507A488-BD40-401B-A6C7-76815DCE0A8D}"/>
+    <hyperlink ref="A114" r:id="rId52" display="https://shelgo.in/" xr:uid="{A7F83E4E-1AE0-445B-AD54-31556F7AE05A}"/>
+    <hyperlink ref="A115" r:id="rId53" xr:uid="{055C9B13-9956-4A4C-B226-5FBF4405EFFB}"/>
+    <hyperlink ref="A121" r:id="rId54" xr:uid="{B9604392-ACA0-4A65-B17D-D3107ECFB536}"/>
+    <hyperlink ref="A126" r:id="rId55" xr:uid="{F700780B-F687-4604-A756-49FC7ED51F57}"/>
+    <hyperlink ref="A129" r:id="rId56" display="https://momuain.in/" xr:uid="{329100DD-72C9-4D13-ADB0-3BA2B47D642D}"/>
+    <hyperlink ref="A130" r:id="rId57" xr:uid="{84181BD1-7C52-440D-AC36-FC82983677D1}"/>
+    <hyperlink ref="A131" r:id="rId58" display="https://kurtij.salesoffers.online/" xr:uid="{407DBC4E-E9F4-4EE8-A131-3B35505A59C2}"/>
+    <hyperlink ref="A132" r:id="rId59" xr:uid="{EA3272EB-D82D-4C5D-A596-06307FBC5100}"/>
+    <hyperlink ref="A136" r:id="rId60" display="https://mylpg.coinapl.com/" xr:uid="{C344B3E3-6F66-4AEC-8A73-D1B78D733C56}"/>
+    <hyperlink ref="A137" r:id="rId61" display="https://purple-donkey-641161.hostingersite.com/" xr:uid="{132ADB45-92D5-4B8D-8A62-5F8B28B8E58C}"/>
+    <hyperlink ref="A138" r:id="rId62" display="https://snow-echidna-664511.hostingersite.com/" xr:uid="{C7295CBA-527C-4166-ACA7-38F30F691C10}"/>
+    <hyperlink ref="A150" r:id="rId63" xr:uid="{ED3053C9-D974-4CDF-8A1F-DF80C73D0CFE}"/>
+    <hyperlink ref="A156" r:id="rId64" xr:uid="{DD55DD4D-CAFA-46D4-A025-83A95638D199}"/>
+    <hyperlink ref="A174" r:id="rId65" xr:uid="{58E5C2FE-4BBA-415A-9A33-D687E447E68E}"/>
+    <hyperlink ref="A177" r:id="rId66" xr:uid="{FE6BFD7A-2FDA-4896-812C-D6CD06E9A446}"/>
+    <hyperlink ref="A178" r:id="rId67" xr:uid="{8F7CA872-A682-4153-AB62-E93DC2A9C2F7}"/>
+    <hyperlink ref="A179" r:id="rId68" xr:uid="{3B4283F1-AF86-43FE-BCDE-188F3A4B65D4}"/>
+    <hyperlink ref="A180" r:id="rId69" xr:uid="{3E3539B6-9B17-4B24-A334-1C7750629824}"/>
+    <hyperlink ref="A181" r:id="rId70" xr:uid="{CF177619-BC24-4E39-A5F3-CB3586E28F5C}"/>
+    <hyperlink ref="A185" r:id="rId71" xr:uid="{3C88CF4F-39AB-43A5-B854-9F5C53D3F90E}"/>
+    <hyperlink ref="A204" r:id="rId72" display="https://stircrazy.live/" xr:uid="{781A95FC-D851-4B03-B0EA-95E6BB88DC88}"/>
+    <hyperlink ref="A209" r:id="rId73" xr:uid="{5B5D48FA-EF95-4D5C-8DA1-B2F50910B9CF}"/>
+    <hyperlink ref="A218" r:id="rId74" xr:uid="{78117D3C-2BB2-4CE8-A255-DDC50D848B6F}"/>
+    <hyperlink ref="A224" r:id="rId75" xr:uid="{D21C9D32-490C-45F5-BF06-CF91755C345F}"/>
+    <hyperlink ref="A240" r:id="rId76" xr:uid="{03787078-C7A1-4B0F-AD38-718333EA15AF}"/>
+    <hyperlink ref="A243" r:id="rId77" xr:uid="{A7E90E6E-E145-4276-A477-E81093B36364}"/>
+    <hyperlink ref="A245" r:id="rId78" xr:uid="{103E6936-8873-4D9C-B0BE-CE661DB619ED}"/>
+    <hyperlink ref="A246" r:id="rId79" display="https://blue-rhinoceros-712109.hostingersite.com/" xr:uid="{B9FD3E60-8755-4845-A250-5A3A495B3C2C}"/>
+    <hyperlink ref="A247" r:id="rId80" xr:uid="{E9617E13-E2E3-40AC-986C-A169BC021F23}"/>
+    <hyperlink ref="A249" r:id="rId81" xr:uid="{E7EA9E47-1377-429A-9745-ACA1F768919A}"/>
+    <hyperlink ref="A250" r:id="rId82" xr:uid="{5CD29137-A768-477B-ABAD-C8F2905F3DE8}"/>
+    <hyperlink ref="A252" r:id="rId83" xr:uid="{20275522-B46E-42FA-9110-2B686E6A0F15}"/>
+    <hyperlink ref="A261" r:id="rId84" xr:uid="{2B883049-8313-4FE4-A7F4-81AFF0590229}"/>
+    <hyperlink ref="A262" r:id="rId85" xr:uid="{615BBF8F-C200-4444-AEA3-6D550C059FE7}"/>
+    <hyperlink ref="A268" r:id="rId86" display="https://www.bookmyshowiplt20.com/" xr:uid="{E8DAC616-A075-4D5D-B1BD-16CCA0A29FDD}"/>
+    <hyperlink ref="A269" r:id="rId87" xr:uid="{B684A58E-1551-4F7E-B899-81DCAFD82415}"/>
+    <hyperlink ref="A270" r:id="rId88" display="https://ticket-booking-2026.lovable.app/" xr:uid="{D371AB84-6DFF-4393-A1E1-A4FB05C7134A}"/>
+    <hyperlink ref="A271" r:id="rId89" display="https://polon.kalasalelive.shop/" xr:uid="{3A3230CF-69B7-474B-95B4-4F279DB5AD5D}"/>
+    <hyperlink ref="A272" r:id="rId90" display="https://brown-ostrich-366780.hostingersite.com/" xr:uid="{0FBC60CF-6A43-472C-BD71-FAE6F3D37C6F}"/>
+    <hyperlink ref="A278" r:id="rId91" xr:uid="{E80B10C0-E3BD-4CBE-9F88-DB005E337214}"/>
+    <hyperlink ref="A279" r:id="rId92" display="https://khaki-shrew-414555.hostingersite.com/" xr:uid="{B6AFC363-D7F8-4F7A-9859-9294F7DE3E9D}"/>
+    <hyperlink ref="A280" r:id="rId93" xr:uid="{CA289E9C-B4F1-4382-8753-4C24C1DBD827}"/>
+    <hyperlink ref="A281" r:id="rId94" xr:uid="{FAE52DD6-9525-4E01-95D9-ADDB6199F219}"/>
+    <hyperlink ref="A282" r:id="rId95" xr:uid="{790FB6B7-D9CB-4E4D-8C4B-B2CE30B90E96}"/>
+    <hyperlink ref="A287" r:id="rId96" xr:uid="{AA73351D-CC9B-4BFC-B0AA-7B14251593F3}"/>
+    <hyperlink ref="A288" r:id="rId97" xr:uid="{BC08F121-B370-4B55-8467-406FD9D00D53}"/>
+    <hyperlink ref="B84" r:id="rId98" display="https://myip.ms/view/cities/6/IP_Addresses_Singapore.html" xr:uid="{A94AA970-466C-4F27-B5A3-78C45C66E65E}"/>
+    <hyperlink ref="A366" r:id="rId99" display="https://happilo.hemnthapp.shop/" xr:uid="{9202AAAF-D654-4334-9D22-099DA92EEDB5}"/>
+    <hyperlink ref="A367" r:id="rId100" display="https://flm777.cc/" xr:uid="{9719DC13-1BD9-43BA-A917-8F055B4253A4}"/>
+    <hyperlink ref="A369" r:id="rId101" display="https://derymilk72.com/" xr:uid="{BCE2D4A0-54AD-4E6A-A51D-2A7944D95E15}"/>
+    <hyperlink ref="A377" r:id="rId102" display="https://husqvarna-vip.shop/" xr:uid="{3509AB49-1ACF-469E-954B-6D75AA2B03F0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId96"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId103"/>
 </worksheet>
 </file>